--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I106"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -820,10 +820,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B15" t="str">
-        <v>Teoria gruppo terze (Tromba + Fisarmonica)</v>
+        <v>AIRC · 3B</v>
       </c>
       <c r="C15" t="str">
         <v>temporanea</v>
@@ -832,10 +832,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E15" t="str">
-        <v>13:20</v>
+        <v>10:10</v>
       </c>
       <c r="F15" t="str">
-        <v>14:05</v>
+        <v>11:05</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -849,10 +849,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B16" t="str">
-        <v>Tromba · Musica d'insieme terze</v>
+        <v>AIRC · 3A</v>
       </c>
       <c r="C16" t="str">
         <v>temporanea</v>
@@ -861,10 +861,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E16" t="str">
-        <v>14:05</v>
+        <v>11:05</v>
       </c>
       <c r="F16" t="str">
-        <v>14:50</v>
+        <v>12:10</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -878,10 +878,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B17" t="str">
-        <v>Sax · Musica d'insieme terze</v>
+        <v>AIRC · 3C</v>
       </c>
       <c r="C17" t="str">
         <v>temporanea</v>
@@ -890,10 +890,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E17" t="str">
-        <v>14:05</v>
+        <v>12:10</v>
       </c>
       <c r="F17" t="str">
-        <v>14:50</v>
+        <v>13:05</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -910,7 +910,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="str">
-        <v>Pianoforte · Musica d'insieme terze</v>
+        <v>AIRC · 1A</v>
       </c>
       <c r="C18" t="str">
         <v>temporanea</v>
@@ -919,10 +919,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E18" t="str">
+        <v>13:05</v>
+      </c>
+      <c r="F18" t="str">
         <v>14:05</v>
-      </c>
-      <c r="F18" t="str">
-        <v>14:50</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -936,22 +936,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B19" t="str">
-        <v>Fisarmonica · Musica d'insieme terze</v>
+        <v>AIRC · 2A</v>
       </c>
       <c r="C19" t="str">
         <v>temporanea</v>
       </c>
       <c r="D19" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E19" t="str">
-        <v>14:05</v>
+        <v>08:05</v>
       </c>
       <c r="F19" t="str">
-        <v>14:50</v>
+        <v>09:05</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -965,22 +965,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B20" t="str">
-        <v>Tromba · Individuale 1</v>
+        <v>AIRC · 2D</v>
       </c>
       <c r="C20" t="str">
         <v>temporanea</v>
       </c>
       <c r="D20" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E20" t="str">
-        <v>14:50</v>
+        <v>10:10</v>
       </c>
       <c r="F20" t="str">
-        <v>15:50</v>
+        <v>11:05</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -994,22 +994,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B21" t="str">
-        <v>Sax · Individuale 1</v>
+        <v>AIRC · 2B</v>
       </c>
       <c r="C21" t="str">
         <v>temporanea</v>
       </c>
       <c r="D21" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E21" t="str">
-        <v>14:50</v>
+        <v>11:05</v>
       </c>
       <c r="F21" t="str">
-        <v>15:50</v>
+        <v>12:10</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1026,19 +1026,19 @@
         <v>7</v>
       </c>
       <c r="B22" t="str">
-        <v>Pianoforte · Individuale 1</v>
+        <v>AIRC · 3D</v>
       </c>
       <c r="C22" t="str">
         <v>temporanea</v>
       </c>
       <c r="D22" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E22" t="str">
-        <v>14:50</v>
+        <v>12:10</v>
       </c>
       <c r="F22" t="str">
-        <v>15:50</v>
+        <v>13:05</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1052,22 +1052,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B23" t="str">
-        <v>Fisarmonica · Individuale 1</v>
+        <v>AIRC · 1D</v>
       </c>
       <c r="C23" t="str">
         <v>temporanea</v>
       </c>
       <c r="D23" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E23" t="str">
-        <v>14:50</v>
+        <v>10:10</v>
       </c>
       <c r="F23" t="str">
-        <v>15:50</v>
+        <v>11:05</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1081,22 +1081,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B24" t="str">
-        <v>Tromba · Individuale 2</v>
+        <v>AIRC · 2C</v>
       </c>
       <c r="C24" t="str">
         <v>temporanea</v>
       </c>
       <c r="D24" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E24" t="str">
-        <v>15:35</v>
+        <v>11:05</v>
       </c>
       <c r="F24" t="str">
-        <v>16:35</v>
+        <v>12:10</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1110,22 +1110,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B25" t="str">
-        <v>Sax · Individuale 2</v>
+        <v>AIRC · 1B</v>
       </c>
       <c r="C25" t="str">
         <v>temporanea</v>
       </c>
       <c r="D25" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E25" t="str">
-        <v>15:35</v>
+        <v>12:10</v>
       </c>
       <c r="F25" t="str">
-        <v>16:35</v>
+        <v>13:05</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1142,19 +1142,19 @@
         <v>7</v>
       </c>
       <c r="B26" t="str">
-        <v>Pianoforte · Individuale 2</v>
+        <v>AIRC · 1C</v>
       </c>
       <c r="C26" t="str">
         <v>temporanea</v>
       </c>
       <c r="D26" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E26" t="str">
-        <v>15:35</v>
+        <v>13:05</v>
       </c>
       <c r="F26" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B27" t="str">
-        <v>Fisarmonica · Individuale 2</v>
+        <v>Teoria gruppo terze (Tromba + Fisarmonica)</v>
       </c>
       <c r="C27" t="str">
         <v>temporanea</v>
@@ -1180,10 +1180,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E27" t="str">
-        <v>15:35</v>
+        <v>13:20</v>
       </c>
       <c r="F27" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="str">
-        <v>Tromba · Individuale 3</v>
+        <v>Tromba · Musica d'insieme terze</v>
       </c>
       <c r="C28" t="str">
         <v>temporanea</v>
@@ -1209,10 +1209,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E28" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F28" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1229,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="str">
-        <v>Sax · Individuale 3</v>
+        <v>Sax · Musica d'insieme terze</v>
       </c>
       <c r="C29" t="str">
         <v>temporanea</v>
@@ -1238,10 +1238,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E29" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F29" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B30" t="str">
-        <v>Pianoforte · Individuale 3</v>
+        <v>Pianoforte · Musica d'insieme terze</v>
       </c>
       <c r="C30" t="str">
         <v>temporanea</v>
@@ -1267,10 +1267,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E30" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F30" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1287,7 +1287,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="str">
-        <v>Fisarmonica · Individuale 3</v>
+        <v>Fisarmonica · Musica d'insieme terze</v>
       </c>
       <c r="C31" t="str">
         <v>temporanea</v>
@@ -1296,10 +1296,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E31" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F31" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1313,22 +1313,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B32" t="str">
-        <v>Teoria gruppo seconde (Tromba + Fisarmonica)</v>
+        <v>Tromba · Individuale 1</v>
       </c>
       <c r="C32" t="str">
         <v>temporanea</v>
       </c>
       <c r="D32" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E32" t="str">
-        <v>13:20</v>
+        <v>14:50</v>
       </c>
       <c r="F32" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1342,22 +1342,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="str">
-        <v>Tromba · Musica d'insieme seconde</v>
+        <v>Sax · Individuale 1</v>
       </c>
       <c r="C33" t="str">
         <v>temporanea</v>
       </c>
       <c r="D33" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E33" t="str">
-        <v>14:05</v>
+        <v>14:50</v>
       </c>
       <c r="F33" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1371,22 +1371,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="str">
-        <v>Sax · Musica d'insieme seconde</v>
+        <v>Pianoforte · Individuale 1</v>
       </c>
       <c r="C34" t="str">
         <v>temporanea</v>
       </c>
       <c r="D34" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E34" t="str">
-        <v>14:05</v>
+        <v>14:50</v>
       </c>
       <c r="F34" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1400,22 +1400,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B35" t="str">
-        <v>Pianoforte · Musica d'insieme seconde</v>
+        <v>Fisarmonica · Individuale 1</v>
       </c>
       <c r="C35" t="str">
         <v>temporanea</v>
       </c>
       <c r="D35" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E35" t="str">
-        <v>14:05</v>
+        <v>14:50</v>
       </c>
       <c r="F35" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1429,22 +1429,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B36" t="str">
-        <v>Fisarmonica · Musica d'insieme terze</v>
+        <v>Tromba · Individuale 2</v>
       </c>
       <c r="C36" t="str">
         <v>temporanea</v>
       </c>
       <c r="D36" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E36" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="F36" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1458,22 +1458,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="str">
-        <v>Tromba · Individuale 4</v>
+        <v>Sax · Individuale 2</v>
       </c>
       <c r="C37" t="str">
         <v>temporanea</v>
       </c>
       <c r="D37" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E37" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="F37" t="str">
-        <v>15:50</v>
+        <v>16:20</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1487,22 +1487,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B38" t="str">
-        <v>Sax · Individuale 4</v>
+        <v>Pianoforte · Individuale 2</v>
       </c>
       <c r="C38" t="str">
         <v>temporanea</v>
       </c>
       <c r="D38" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E38" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="F38" t="str">
-        <v>15:50</v>
+        <v>16:20</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1516,22 +1516,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B39" t="str">
-        <v>Pianoforte · Individuale 4</v>
+        <v>Fisarmonica · Individuale 2</v>
       </c>
       <c r="C39" t="str">
         <v>temporanea</v>
       </c>
       <c r="D39" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E39" t="str">
-        <v>14:50</v>
+        <v>15:35</v>
       </c>
       <c r="F39" t="str">
-        <v>15:50</v>
+        <v>16:20</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1545,22 +1545,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B40" t="str">
-        <v>Fisarmonica · Individuale 4</v>
+        <v>Tromba · Individuale 3</v>
       </c>
       <c r="C40" t="str">
         <v>temporanea</v>
       </c>
       <c r="D40" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E40" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="F40" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1574,22 +1574,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="str">
-        <v>Tromba · Individuale 5</v>
+        <v>Sax · Individuale 3</v>
       </c>
       <c r="C41" t="str">
         <v>temporanea</v>
       </c>
       <c r="D41" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E41" t="str">
-        <v>15:35</v>
+        <v>16:20</v>
       </c>
       <c r="F41" t="str">
-        <v>16:35</v>
+        <v>17:20</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1603,22 +1603,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B42" t="str">
-        <v>Sax · Individuale 5</v>
+        <v>Pianoforte · Individuale 3</v>
       </c>
       <c r="C42" t="str">
         <v>temporanea</v>
       </c>
       <c r="D42" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E42" t="str">
-        <v>15:35</v>
+        <v>16:20</v>
       </c>
       <c r="F42" t="str">
-        <v>16:35</v>
+        <v>17:20</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1632,22 +1632,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B43" t="str">
-        <v>Pianoforte · Individuale 5</v>
+        <v>Fisarmonica · Individuale 3</v>
       </c>
       <c r="C43" t="str">
         <v>temporanea</v>
       </c>
       <c r="D43" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E43" t="str">
-        <v>15:35</v>
+        <v>16:20</v>
       </c>
       <c r="F43" t="str">
-        <v>16:35</v>
+        <v>17:20</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B44" t="str">
-        <v>Fisarmonica · Individuale 5</v>
+        <v>Teoria gruppo seconde (Tromba + Fisarmonica)</v>
       </c>
       <c r="C44" t="str">
         <v>temporanea</v>
@@ -1673,10 +1673,10 @@
         <v>Martedì</v>
       </c>
       <c r="E44" t="str">
-        <v>15:35</v>
+        <v>13:20</v>
       </c>
       <c r="F44" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="str">
-        <v>Tromba · Individuale 6</v>
+        <v>Tromba · Musica d'insieme seconde</v>
       </c>
       <c r="C45" t="str">
         <v>temporanea</v>
@@ -1702,10 +1702,10 @@
         <v>Martedì</v>
       </c>
       <c r="E45" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F45" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -1722,7 +1722,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="str">
-        <v>Sax · Individuale 6</v>
+        <v>Sax · Musica d'insieme seconde</v>
       </c>
       <c r="C46" t="str">
         <v>temporanea</v>
@@ -1731,10 +1731,10 @@
         <v>Martedì</v>
       </c>
       <c r="E46" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F46" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B47" t="str">
-        <v>Pianoforte · Individuale 6</v>
+        <v>Pianoforte · Musica d'insieme seconde</v>
       </c>
       <c r="C47" t="str">
         <v>temporanea</v>
@@ -1760,10 +1760,10 @@
         <v>Martedì</v>
       </c>
       <c r="E47" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F47" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>16</v>
       </c>
       <c r="B48" t="str">
-        <v>Fisarmonica · Individuale 6</v>
+        <v>Fisarmonica · Musica d'insieme terze</v>
       </c>
       <c r="C48" t="str">
         <v>temporanea</v>
@@ -1789,10 +1789,10 @@
         <v>Martedì</v>
       </c>
       <c r="E48" t="str">
-        <v>16:20</v>
+        <v>14:05</v>
       </c>
       <c r="F48" t="str">
-        <v>17:20</v>
+        <v>14:50</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -1809,19 +1809,19 @@
         <v>14</v>
       </c>
       <c r="B49" t="str">
-        <v>Tromba · Individuale 7</v>
+        <v>Tromba · Individuale 4</v>
       </c>
       <c r="C49" t="str">
         <v>temporanea</v>
       </c>
       <c r="D49" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E49" t="str">
-        <v>13:20</v>
+        <v>14:50</v>
       </c>
       <c r="F49" t="str">
-        <v>14:20</v>
+        <v>15:35</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -1838,19 +1838,19 @@
         <v>12</v>
       </c>
       <c r="B50" t="str">
-        <v>Sax · Individuale 7</v>
+        <v>Sax · Individuale 4</v>
       </c>
       <c r="C50" t="str">
         <v>temporanea</v>
       </c>
       <c r="D50" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E50" t="str">
-        <v>13:20</v>
+        <v>14:50</v>
       </c>
       <c r="F50" t="str">
-        <v>14:20</v>
+        <v>15:35</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -1864,22 +1864,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B51" t="str">
-        <v>Pianoforte · Individuale 7</v>
+        <v>Pianoforte · Individuale 4</v>
       </c>
       <c r="C51" t="str">
         <v>temporanea</v>
       </c>
       <c r="D51" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E51" t="str">
-        <v>13:20</v>
+        <v>14:50</v>
       </c>
       <c r="F51" t="str">
-        <v>14:20</v>
+        <v>15:35</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -1896,19 +1896,19 @@
         <v>16</v>
       </c>
       <c r="B52" t="str">
-        <v>Fisarmonica · Individuale 7</v>
+        <v>Fisarmonica · Individuale 4</v>
       </c>
       <c r="C52" t="str">
         <v>temporanea</v>
       </c>
       <c r="D52" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E52" t="str">
-        <v>13:20</v>
+        <v>14:50</v>
       </c>
       <c r="F52" t="str">
-        <v>14:20</v>
+        <v>15:35</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -1925,19 +1925,19 @@
         <v>14</v>
       </c>
       <c r="B53" t="str">
-        <v>Tromba · Individuale 8</v>
+        <v>Tromba · Individuale 5</v>
       </c>
       <c r="C53" t="str">
         <v>temporanea</v>
       </c>
       <c r="D53" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E53" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="F53" t="str">
-        <v>15:05</v>
+        <v>16:20</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -1954,19 +1954,19 @@
         <v>12</v>
       </c>
       <c r="B54" t="str">
-        <v>Sax · Individuale 8</v>
+        <v>Sax · Individuale 5</v>
       </c>
       <c r="C54" t="str">
         <v>temporanea</v>
       </c>
       <c r="D54" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E54" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="F54" t="str">
-        <v>15:05</v>
+        <v>16:20</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -1980,22 +1980,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B55" t="str">
-        <v>Pianoforte · Individuale 8</v>
+        <v>Pianoforte · Individuale 5</v>
       </c>
       <c r="C55" t="str">
         <v>temporanea</v>
       </c>
       <c r="D55" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E55" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="F55" t="str">
-        <v>15:05</v>
+        <v>16:20</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2012,19 +2012,19 @@
         <v>16</v>
       </c>
       <c r="B56" t="str">
-        <v>Fisarmonica · Individuale 8</v>
+        <v>Fisarmonica · Individuale 5</v>
       </c>
       <c r="C56" t="str">
         <v>temporanea</v>
       </c>
       <c r="D56" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E56" t="str">
-        <v>14:05</v>
+        <v>15:35</v>
       </c>
       <c r="F56" t="str">
-        <v>15:05</v>
+        <v>16:20</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2041,19 +2041,19 @@
         <v>14</v>
       </c>
       <c r="B57" t="str">
-        <v>Tromba · Individuale 9</v>
+        <v>Tromba · Individuale 6</v>
       </c>
       <c r="C57" t="str">
         <v>temporanea</v>
       </c>
       <c r="D57" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E57" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="F57" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2070,19 +2070,19 @@
         <v>12</v>
       </c>
       <c r="B58" t="str">
-        <v>Sax · Individuale 9</v>
+        <v>Sax · Individuale 6</v>
       </c>
       <c r="C58" t="str">
         <v>temporanea</v>
       </c>
       <c r="D58" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E58" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="F58" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B59" t="str">
-        <v>Pianoforte · Individuale 9</v>
+        <v>Pianoforte · Individuale 6</v>
       </c>
       <c r="C59" t="str">
         <v>temporanea</v>
       </c>
       <c r="D59" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E59" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="F59" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2128,19 +2128,19 @@
         <v>16</v>
       </c>
       <c r="B60" t="str">
-        <v>Fisarmonica · Individuale 9</v>
+        <v>Fisarmonica · Individuale 6</v>
       </c>
       <c r="C60" t="str">
         <v>temporanea</v>
       </c>
       <c r="D60" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E60" t="str">
-        <v>14:50</v>
+        <v>16:20</v>
       </c>
       <c r="F60" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B61" t="str">
-        <v>Sax · Individuale 10</v>
+        <v>Tromba · Individuale 7</v>
       </c>
       <c r="C61" t="str">
         <v>temporanea</v>
@@ -2166,10 +2166,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E61" t="str">
-        <v>15:35</v>
+        <v>13:20</v>
       </c>
       <c r="F61" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B62" t="str">
-        <v>Pianoforte · Individuale 10</v>
+        <v>Sax · Individuale 7</v>
       </c>
       <c r="C62" t="str">
         <v>temporanea</v>
@@ -2195,10 +2195,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E62" t="str">
-        <v>15:35</v>
+        <v>13:20</v>
       </c>
       <c r="F62" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B63" t="str">
-        <v>Sax · Individuale 13</v>
+        <v>Pianoforte · Individuale 7</v>
       </c>
       <c r="C63" t="str">
         <v>temporanea</v>
@@ -2224,10 +2224,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E63" t="str">
-        <v>16:20</v>
+        <v>13:20</v>
       </c>
       <c r="F63" t="str">
-        <v>17:20</v>
+        <v>14:05</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B64" t="str">
-        <v>Pianoforte · Individuale 13</v>
+        <v>Fisarmonica · Individuale 7</v>
       </c>
       <c r="C64" t="str">
         <v>temporanea</v>
@@ -2253,10 +2253,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E64" t="str">
-        <v>16:20</v>
+        <v>13:20</v>
       </c>
       <c r="F64" t="str">
-        <v>17:20</v>
+        <v>14:05</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2273,19 +2273,19 @@
         <v>14</v>
       </c>
       <c r="B65" t="str">
-        <v>Tromba · Individuale 10 Prime S.L.</v>
+        <v>Tromba · Individuale 8</v>
       </c>
       <c r="C65" t="str">
         <v>temporanea</v>
       </c>
       <c r="D65" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E65" t="str">
-        <v>13:20</v>
+        <v>14:05</v>
       </c>
       <c r="F65" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B66" t="str">
-        <v>Fisarmonica · Individuale 10 Prime S.L.</v>
+        <v>Sax · Individuale 8</v>
       </c>
       <c r="C66" t="str">
         <v>temporanea</v>
       </c>
       <c r="D66" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E66" t="str">
-        <v>13:20</v>
+        <v>14:05</v>
       </c>
       <c r="F66" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2328,22 +2328,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B67" t="str">
-        <v>Sax · Individuale 11 Prime S.L.</v>
+        <v>Pianoforte · Individuale 8</v>
       </c>
       <c r="C67" t="str">
         <v>temporanea</v>
       </c>
       <c r="D67" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E67" t="str">
-        <v>13:20</v>
+        <v>14:05</v>
       </c>
       <c r="F67" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B68" t="str">
-        <v>Pianoforte · Individuale 11 Prime S.L.</v>
+        <v>Fisarmonica · Individuale 8</v>
       </c>
       <c r="C68" t="str">
         <v>temporanea</v>
       </c>
       <c r="D68" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E68" t="str">
-        <v>13:20</v>
+        <v>14:05</v>
       </c>
       <c r="F68" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2389,19 +2389,19 @@
         <v>14</v>
       </c>
       <c r="B69" t="str">
-        <v>Tromba · Musica d'insieme prime</v>
+        <v>Tromba · Individuale 9</v>
       </c>
       <c r="C69" t="str">
         <v>temporanea</v>
       </c>
       <c r="D69" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E69" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="F69" t="str">
-        <v>15:05</v>
+        <v>15:50</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -2418,19 +2418,19 @@
         <v>12</v>
       </c>
       <c r="B70" t="str">
-        <v>Sax · Musica d'insieme prime</v>
+        <v>Sax · Individuale 9</v>
       </c>
       <c r="C70" t="str">
         <v>temporanea</v>
       </c>
       <c r="D70" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E70" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="F70" t="str">
-        <v>15:05</v>
+        <v>15:35</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -2444,22 +2444,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B71" t="str">
-        <v>Pianoforte · Musica d'insieme prime</v>
+        <v>Pianoforte · Individuale 9</v>
       </c>
       <c r="C71" t="str">
         <v>temporanea</v>
       </c>
       <c r="D71" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E71" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="F71" t="str">
-        <v>15:05</v>
+        <v>15:35</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -2476,19 +2476,19 @@
         <v>16</v>
       </c>
       <c r="B72" t="str">
-        <v>Fisarmonica · Musica d'insieme prime</v>
+        <v>Fisarmonica · Individuale 9</v>
       </c>
       <c r="C72" t="str">
         <v>temporanea</v>
       </c>
       <c r="D72" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E72" t="str">
-        <v>14:20</v>
+        <v>14:50</v>
       </c>
       <c r="F72" t="str">
-        <v>15:05</v>
+        <v>15:50</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -2502,22 +2502,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="str">
-        <v>Tromba · Individuale 11 (no prime)</v>
+        <v>Sax · Individuale 10</v>
       </c>
       <c r="C73" t="str">
         <v>temporanea</v>
       </c>
       <c r="D73" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E73" t="str">
-        <v>15:05</v>
+        <v>15:35</v>
       </c>
       <c r="F73" t="str">
-        <v>16:05</v>
+        <v>16:20</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B74" t="str">
-        <v>Pianoforte · Individuale 12 (no prime)</v>
+        <v>Pianoforte · Individuale 10</v>
       </c>
       <c r="C74" t="str">
         <v>temporanea</v>
       </c>
       <c r="D74" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E74" t="str">
-        <v>15:05</v>
+        <v>15:35</v>
       </c>
       <c r="F74" t="str">
-        <v>16:05</v>
+        <v>16:20</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -2560,22 +2560,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B75" t="str">
-        <v>Teoria gruppo prime (Sax + Fisarmonica)</v>
+        <v>Sax · Individuale 13</v>
       </c>
       <c r="C75" t="str">
         <v>temporanea</v>
       </c>
       <c r="D75" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E75" t="str">
-        <v>15:05</v>
+        <v>16:20</v>
       </c>
       <c r="F75" t="str">
-        <v>15:50</v>
+        <v>17:20</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -2589,22 +2589,22 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B76" t="str">
-        <v>Tromba · Individuale 12</v>
+        <v>Pianoforte · Individuale 13</v>
       </c>
       <c r="C76" t="str">
         <v>temporanea</v>
       </c>
       <c r="D76" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E76" t="str">
-        <v>15:50</v>
+        <v>16:20</v>
       </c>
       <c r="F76" t="str">
-        <v>16:50</v>
+        <v>17:20</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B77" t="str">
-        <v>Sax · Individuale 12</v>
+        <v>Tromba · Individuale 10 Prime S.L.</v>
       </c>
       <c r="C77" t="str">
         <v>temporanea</v>
@@ -2630,10 +2630,10 @@
         <v>Giovedì</v>
       </c>
       <c r="E77" t="str">
-        <v>15:50</v>
+        <v>13:20</v>
       </c>
       <c r="F77" t="str">
-        <v>16:50</v>
+        <v>14:20</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B78" t="str">
-        <v>Pianoforte · Individuale 13</v>
+        <v>Fisarmonica · Individuale 10 Prime S.L.</v>
       </c>
       <c r="C78" t="str">
         <v>temporanea</v>
@@ -2659,10 +2659,10 @@
         <v>Giovedì</v>
       </c>
       <c r="E78" t="str">
-        <v>15:50</v>
+        <v>13:20</v>
       </c>
       <c r="F78" t="str">
-        <v>16:50</v>
+        <v>14:20</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B79" t="str">
-        <v>Fisarmonica · Individuale 11</v>
+        <v>Sax · Individuale 11 Prime S.L.</v>
       </c>
       <c r="C79" t="str">
         <v>temporanea</v>
@@ -2688,10 +2688,10 @@
         <v>Giovedì</v>
       </c>
       <c r="E79" t="str">
-        <v>15:50</v>
+        <v>13:20</v>
       </c>
       <c r="F79" t="str">
-        <v>16:50</v>
+        <v>14:20</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B80" t="str">
-        <v>Fisarmonica · Individuale 12</v>
+        <v>Pianoforte · Individuale 11 Prime S.L.</v>
       </c>
       <c r="C80" t="str">
         <v>temporanea</v>
@@ -2717,10 +2717,10 @@
         <v>Giovedì</v>
       </c>
       <c r="E80" t="str">
-        <v>16:35</v>
+        <v>13:20</v>
       </c>
       <c r="F80" t="str">
-        <v>17:35</v>
+        <v>14:20</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -2737,19 +2737,19 @@
         <v>14</v>
       </c>
       <c r="B81" t="str">
-        <v>Tromba · Individuale 13</v>
+        <v>Tromba · Musica d'insieme prime</v>
       </c>
       <c r="C81" t="str">
         <v>temporanea</v>
       </c>
       <c r="D81" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E81" t="str">
-        <v>13:20</v>
+        <v>14:20</v>
       </c>
       <c r="F81" t="str">
-        <v>14:20</v>
+        <v>15:05</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -2763,19 +2763,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="str">
-        <v>Tromba · Individuale 14</v>
+        <v>Sax · Musica d'insieme prime</v>
       </c>
       <c r="C82" t="str">
         <v>temporanea</v>
       </c>
       <c r="D82" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E82" t="str">
-        <v>14:05</v>
+        <v>14:20</v>
       </c>
       <c r="F82" t="str">
         <v>15:05</v>
@@ -2792,22 +2792,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B83" t="str">
-        <v>Tromba · Individuale 15</v>
+        <v>Pianoforte · Musica d'insieme prime</v>
       </c>
       <c r="C83" t="str">
         <v>temporanea</v>
       </c>
       <c r="D83" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E83" t="str">
-        <v>14:50</v>
+        <v>14:20</v>
       </c>
       <c r="F83" t="str">
-        <v>15:50</v>
+        <v>15:05</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -2821,22 +2821,22 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B84" t="str">
-        <v>Tromba · Individuale 16</v>
+        <v>Fisarmonica · Musica d'insieme prime</v>
       </c>
       <c r="C84" t="str">
         <v>temporanea</v>
       </c>
       <c r="D84" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E84" t="str">
-        <v>15:35</v>
+        <v>14:20</v>
       </c>
       <c r="F84" t="str">
-        <v>16:35</v>
+        <v>15:05</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -2850,22 +2850,22 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B85" t="str">
-        <v>Sax · Individuale 14</v>
+        <v>Tromba · Individuale 11 (no prime)</v>
       </c>
       <c r="C85" t="str">
         <v>temporanea</v>
       </c>
       <c r="D85" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E85" t="str">
-        <v>13:20</v>
+        <v>15:05</v>
       </c>
       <c r="F85" t="str">
-        <v>14:20</v>
+        <v>15:50</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B86" t="str">
-        <v>Sax · Individuale 15</v>
+        <v>Pianoforte · Individuale 12 (no prime)</v>
       </c>
       <c r="C86" t="str">
         <v>temporanea</v>
       </c>
       <c r="D86" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E86" t="str">
-        <v>14:05</v>
+        <v>15:05</v>
       </c>
       <c r="F86" t="str">
-        <v>15:05</v>
+        <v>15:50</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -2911,16 +2911,16 @@
         <v>12</v>
       </c>
       <c r="B87" t="str">
-        <v>Sax · Individuale 16</v>
+        <v>Teoria gruppo prime (Sax + Fisarmonica)</v>
       </c>
       <c r="C87" t="str">
         <v>temporanea</v>
       </c>
       <c r="D87" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E87" t="str">
-        <v>14:50</v>
+        <v>15:05</v>
       </c>
       <c r="F87" t="str">
         <v>15:50</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B88" t="str">
-        <v>Sax · Individuale 17</v>
+        <v>Tromba · Individuale 12</v>
       </c>
       <c r="C88" t="str">
         <v>temporanea</v>
       </c>
       <c r="D88" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E88" t="str">
-        <v>15:35</v>
+        <v>15:50</v>
       </c>
       <c r="F88" t="str">
-        <v>16:35</v>
+        <v>16:50</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -2969,19 +2969,19 @@
         <v>12</v>
       </c>
       <c r="B89" t="str">
-        <v>Sax · Individuale 18</v>
+        <v>Sax · Individuale 12</v>
       </c>
       <c r="C89" t="str">
         <v>temporanea</v>
       </c>
       <c r="D89" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E89" t="str">
-        <v>16:20</v>
+        <v>15:50</v>
       </c>
       <c r="F89" t="str">
-        <v>17:20</v>
+        <v>16:50</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B90" t="str">
-        <v>Pianoforte · Individuale 15</v>
+        <v>Pianoforte · Individuale 13</v>
       </c>
       <c r="C90" t="str">
         <v>temporanea</v>
       </c>
       <c r="D90" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E90" t="str">
-        <v>13:20</v>
+        <v>15:50</v>
       </c>
       <c r="F90" t="str">
-        <v>14:20</v>
+        <v>16:50</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3024,22 +3024,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B91" t="str">
-        <v>Pianoforte · Individuale 16</v>
+        <v>Fisarmonica · Individuale 11</v>
       </c>
       <c r="C91" t="str">
         <v>temporanea</v>
       </c>
       <c r="D91" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E91" t="str">
-        <v>14:05</v>
+        <v>15:50</v>
       </c>
       <c r="F91" t="str">
-        <v>15:05</v>
+        <v>16:35</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B92" t="str">
-        <v>Pianoforte · Individuale 17</v>
+        <v>Fisarmonica · Individuale 12</v>
       </c>
       <c r="C92" t="str">
         <v>temporanea</v>
       </c>
       <c r="D92" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E92" t="str">
-        <v>14:50</v>
+        <v>16:35</v>
       </c>
       <c r="F92" t="str">
-        <v>15:50</v>
+        <v>17:35</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B93" t="str">
-        <v>Pianoforte · Individuale 18</v>
+        <v>Tromba · Individuale 13</v>
       </c>
       <c r="C93" t="str">
         <v>temporanea</v>
@@ -3094,10 +3094,10 @@
         <v>Venerdì</v>
       </c>
       <c r="E93" t="str">
-        <v>15:35</v>
+        <v>13:20</v>
       </c>
       <c r="F93" t="str">
-        <v>16:35</v>
+        <v>14:05</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B94" t="str">
-        <v>Pianoforte · Individuale 19</v>
+        <v>Tromba · Individuale 14</v>
       </c>
       <c r="C94" t="str">
         <v>temporanea</v>
@@ -3123,24 +3123,372 @@
         <v>Venerdì</v>
       </c>
       <c r="E94" t="str">
+        <v>14:05</v>
+      </c>
+      <c r="F94" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>14</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Tromba · Individuale 15</v>
+      </c>
+      <c r="C95" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E95" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="F95" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>14</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Tromba · Individuale 16</v>
+      </c>
+      <c r="C96" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E96" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="F96" t="str">
+        <v>16:35</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>12</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Sax · Individuale 14</v>
+      </c>
+      <c r="C97" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E97" t="str">
+        <v>13:20</v>
+      </c>
+      <c r="F97" t="str">
+        <v>14:05</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>12</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Sax · Individuale 15</v>
+      </c>
+      <c r="C98" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E98" t="str">
+        <v>14:05</v>
+      </c>
+      <c r="F98" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>12</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Sax · Individuale 16</v>
+      </c>
+      <c r="C99" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E99" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="F99" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>12</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Sax · Individuale 17</v>
+      </c>
+      <c r="C100" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E100" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="F100" t="str">
         <v>16:20</v>
       </c>
-      <c r="F94" t="str">
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>12</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Sax · Individuale 18</v>
+      </c>
+      <c r="C101" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E101" t="str">
+        <v>16:20</v>
+      </c>
+      <c r="F101" t="str">
         <v>17:20</v>
       </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-      <c r="I94" t="str">
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>17</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Pianoforte · Individuale 15</v>
+      </c>
+      <c r="C102" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E102" t="str">
+        <v>13:20</v>
+      </c>
+      <c r="F102" t="str">
+        <v>14:05</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>17</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Pianoforte · Individuale 16</v>
+      </c>
+      <c r="C103" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E103" t="str">
+        <v>14:05</v>
+      </c>
+      <c r="F103" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>17</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Pianoforte · Individuale 17</v>
+      </c>
+      <c r="C104" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E104" t="str">
+        <v>14:50</v>
+      </c>
+      <c r="F104" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>17</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Pianoforte · Individuale 18</v>
+      </c>
+      <c r="C105" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E105" t="str">
+        <v>15:35</v>
+      </c>
+      <c r="F105" t="str">
+        <v>16:20</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>17</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Pianoforte · Individuale 19</v>
+      </c>
+      <c r="C106" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E106" t="str">
+        <v>16:20</v>
+      </c>
+      <c r="F106" t="str">
+        <v>17:20</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I106"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I126"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -3486,9 +3486,589 @@
         <v/>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>12</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Francese · 3A-3C</v>
+      </c>
+      <c r="C107" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E107" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F107" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>19</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Spagnolo · 3A-3C</v>
+      </c>
+      <c r="C108" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E108" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F108" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>12</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Francese · 1B-1D</v>
+      </c>
+      <c r="C109" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E109" t="str">
+        <v>10:10</v>
+      </c>
+      <c r="F109" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>19</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Spagnolo · 1B-1D</v>
+      </c>
+      <c r="C110" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E110" t="str">
+        <v>10:10</v>
+      </c>
+      <c r="F110" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>12</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Francese · 1A-1C</v>
+      </c>
+      <c r="C111" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E111" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F111" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>19</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Spagnolo · 1A-1C</v>
+      </c>
+      <c r="C112" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E112" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F112" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>12</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Francese · 1B-1D</v>
+      </c>
+      <c r="C113" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E113" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F113" t="str">
+        <v>09:05</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>19</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Spagnolo · 1B-1D</v>
+      </c>
+      <c r="C114" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E114" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F114" t="str">
+        <v>09:05</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>12</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Francese · 1A-1C</v>
+      </c>
+      <c r="C115" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E115" t="str">
+        <v>10:10</v>
+      </c>
+      <c r="F115" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>19</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Spagnolo · 1A-1C</v>
+      </c>
+      <c r="C116" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E116" t="str">
+        <v>10:10</v>
+      </c>
+      <c r="F116" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>12</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Francese · 2B-2D</v>
+      </c>
+      <c r="C117" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E117" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F117" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>19</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Spagnolo · 2B-2D</v>
+      </c>
+      <c r="C118" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E118" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F118" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>12</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Francese · 2A-2C</v>
+      </c>
+      <c r="C119" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E119" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="F119" t="str">
+        <v>13:05</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>19</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Spagnolo · 2A-2C</v>
+      </c>
+      <c r="C120" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E120" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="F120" t="str">
+        <v>13:05</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>12</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Francese · 3B-3D</v>
+      </c>
+      <c r="C121" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E121" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F121" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>19</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Spagnolo · 3B-3D</v>
+      </c>
+      <c r="C122" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E122" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F122" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>12</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Francese · 2A-2C</v>
+      </c>
+      <c r="C123" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E123" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F123" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>19</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Spagnolo · 2A-2C</v>
+      </c>
+      <c r="C124" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E124" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F124" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>12</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Francese · 2B-2D</v>
+      </c>
+      <c r="C125" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E125" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="F125" t="str">
+        <v>13:05</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v>Basso R.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>19</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Spagnolo · 2B-2D</v>
+      </c>
+      <c r="C126" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E126" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="F126" t="str">
+        <v>13:05</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>Martinelli</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I126"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -7730,8 +7730,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="str">
-        <v/>
+      <c r="A210">
+        <v>1</v>
       </c>
       <c r="B210" t="str">
         <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
@@ -7743,10 +7743,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E210" t="str">
-        <v>08:05</v>
+        <v>08:30</v>
       </c>
       <c r="F210" t="str">
-        <v>13:05</v>
+        <v>13:00</v>
       </c>
       <c r="G210" t="str">
         <v>2026-11-23</v>
@@ -7758,10 +7758,10 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K210" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -7870,8 +7870,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="str">
-        <v/>
+      <c r="A214">
+        <v>1</v>
       </c>
       <c r="B214" t="str">
         <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
@@ -7883,10 +7883,10 @@
         <v>Venerdì</v>
       </c>
       <c r="E214" t="str">
-        <v>08:05</v>
+        <v>08:30</v>
       </c>
       <c r="F214" t="str">
-        <v>13:05</v>
+        <v>13:00</v>
       </c>
       <c r="G214" t="str">
         <v>2026-11-27</v>
@@ -7898,10 +7898,10 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K214" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -8010,8 +8010,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="str">
-        <v/>
+      <c r="A218">
+        <v>1</v>
       </c>
       <c r="B218" t="str">
         <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
@@ -8023,10 +8023,10 @@
         <v>Martedì</v>
       </c>
       <c r="E218" t="str">
-        <v>08:05</v>
+        <v>08:30</v>
       </c>
       <c r="F218" t="str">
-        <v>13:05</v>
+        <v>13:00</v>
       </c>
       <c r="G218" t="str">
         <v>2026-11-24</v>
@@ -8038,15 +8038,15 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K218" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="str">
-        <v/>
+      <c r="A219">
+        <v>1</v>
       </c>
       <c r="B219" t="str">
         <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
@@ -8058,10 +8058,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E219" t="str">
-        <v>08:05</v>
+        <v>08:30</v>
       </c>
       <c r="F219" t="str">
-        <v>13:05</v>
+        <v>13:00</v>
       </c>
       <c r="G219" t="str">
         <v>2026-11-25</v>
@@ -8073,10 +8073,10 @@
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K219" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="220">

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K622"/>
+  <dimension ref="A1:K626"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -7240,11 +7240,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="str">
-        <v/>
+      <c r="A196">
+        <v>21</v>
       </c>
       <c r="B196" t="str">
-        <v>Continuità con classi V · 2A + 2C</v>
+        <v>Continuità con classi V · laboratorio di arte · 2A + 2C</v>
       </c>
       <c r="C196" t="str">
         <v>temporanea</v>
@@ -7253,10 +7253,10 @@
         <v>Giovedì</v>
       </c>
       <c r="E196" t="str">
-        <v>09:00</v>
+        <v>09:20</v>
       </c>
       <c r="F196" t="str">
-        <v>12:00</v>
+        <v>11:30</v>
       </c>
       <c r="G196" t="str">
         <v>2026-11-12</v>
@@ -7268,10 +7268,10 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K196" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -7279,69 +7279,69 @@
         <v/>
       </c>
       <c r="B197" t="str">
-        <v>Incontro ICARO/Pars · 3C + 3A</v>
+        <v>Continuità con classi V · laboratorio di ed. fisica · 2A + 2C</v>
       </c>
       <c r="C197" t="str">
         <v>temporanea</v>
       </c>
       <c r="D197" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E197" t="str">
-        <v>08:05</v>
+        <v>09:20</v>
       </c>
       <c r="F197" t="str">
-        <v>12:10</v>
+        <v>11:30</v>
       </c>
       <c r="G197" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="I197" t="str">
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>Auditorium</v>
+        <v>Palestra</v>
       </c>
       <c r="K197" t="str">
         <v>terra</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198">
-        <v>4</v>
+      <c r="A198" t="str">
+        <v/>
       </c>
       <c r="B198" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>Continuità con classi V · saluti del Dirigente · 2A + 2C</v>
       </c>
       <c r="C198" t="str">
         <v>temporanea</v>
       </c>
       <c r="D198" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E198" t="str">
-        <v>14:30</v>
+        <v>11:30</v>
       </c>
       <c r="F198" t="str">
-        <v>17:00</v>
+        <v>11:45</v>
       </c>
       <c r="G198" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-12</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-12</v>
       </c>
       <c r="I198" t="str">
         <v/>
       </c>
       <c r="J198" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K198" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="199">
@@ -7349,13 +7349,13 @@
         <v/>
       </c>
       <c r="B199" t="str">
-        <v>Incontro ICARO/Pars · 3B + 3D</v>
+        <v>Incontro ICARO/Pars · 3C + 3A</v>
       </c>
       <c r="C199" t="str">
         <v>temporanea</v>
       </c>
       <c r="D199" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E199" t="str">
         <v>08:05</v>
@@ -7364,10 +7364,10 @@
         <v>12:10</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-13</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-13</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7381,10 +7381,10 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B200" t="str">
-        <v>Orientamento con psicologa (classi 3)</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C200" t="str">
         <v>temporanea</v>
@@ -7393,10 +7393,10 @@
         <v>Martedì</v>
       </c>
       <c r="E200" t="str">
-        <v>09:05</v>
+        <v>14:30</v>
       </c>
       <c r="F200" t="str">
-        <v>13:05</v>
+        <v>17:00</v>
       </c>
       <c r="G200" t="str">
         <v>2026-11-10</v>
@@ -7419,25 +7419,25 @@
         <v/>
       </c>
       <c r="B201" t="str">
-        <v>Continuità con classi V · 2B + 2D</v>
+        <v>Incontro ICARO/Pars · 3B + 3D</v>
       </c>
       <c r="C201" t="str">
         <v>temporanea</v>
       </c>
       <c r="D201" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E201" t="str">
-        <v>09:00</v>
+        <v>08:05</v>
       </c>
       <c r="F201" t="str">
-        <v>12:00</v>
+        <v>12:10</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-12</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-12</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7451,10 +7451,10 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B202" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>Orientamento con psicologa (classi 3)</v>
       </c>
       <c r="C202" t="str">
         <v>temporanea</v>
@@ -7463,16 +7463,16 @@
         <v>Martedì</v>
       </c>
       <c r="E202" t="str">
-        <v>14:30</v>
+        <v>09:05</v>
       </c>
       <c r="F202" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G202" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-10</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-10</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7485,38 +7485,38 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="str">
-        <v/>
+      <c r="A203">
+        <v>21</v>
       </c>
       <c r="B203" t="str">
-        <v>Progetto lotta al tabagismo · 2C</v>
+        <v>Continuità con classi V · laboratorio di arte · 2B + 2D</v>
       </c>
       <c r="C203" t="str">
         <v>temporanea</v>
       </c>
       <c r="D203" t="str">
-        <v>Mercoledì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E203" t="str">
-        <v>09:05</v>
+        <v>09:20</v>
       </c>
       <c r="F203" t="str">
-        <v>11:05</v>
+        <v>11:00</v>
       </c>
       <c r="G203" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-16</v>
       </c>
       <c r="I203" t="str">
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K203" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -7524,31 +7524,31 @@
         <v/>
       </c>
       <c r="B204" t="str">
-        <v>Progetto lotta al tabagismo · 2D</v>
+        <v>Continuità con classi V · laboratorio di ed. fisica · 2B + 2D</v>
       </c>
       <c r="C204" t="str">
         <v>temporanea</v>
       </c>
       <c r="D204" t="str">
-        <v>Mercoledì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E204" t="str">
-        <v>11:05</v>
+        <v>09:20</v>
       </c>
       <c r="F204" t="str">
-        <v>13:05</v>
+        <v>11:00</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-16</v>
       </c>
       <c r="I204" t="str">
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>Auditorium</v>
+        <v>Palestra</v>
       </c>
       <c r="K204" t="str">
         <v>terra</v>
@@ -7559,25 +7559,25 @@
         <v/>
       </c>
       <c r="B205" t="str">
-        <v>Progetto lotta al tabagismo · 2A</v>
+        <v>Continuità con classi V · saluti del Dirigente · 2B + 2D</v>
       </c>
       <c r="C205" t="str">
         <v>temporanea</v>
       </c>
       <c r="D205" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E205" t="str">
-        <v>09:05</v>
+        <v>11:30</v>
       </c>
       <c r="F205" t="str">
-        <v>11:05</v>
+        <v>11:45</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-16</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7590,81 +7590,81 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="str">
-        <v/>
+      <c r="A206">
+        <v>3</v>
       </c>
       <c r="B206" t="str">
-        <v>Progetto lotta al tabagismo · 2B</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C206" t="str">
         <v>temporanea</v>
       </c>
       <c r="D206" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E206" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="F206" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2026-11-17</v>
+      </c>
+      <c r="H206" t="str">
+        <v>2026-11-17</v>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v/>
+      </c>
+      <c r="B207" t="str">
+        <v>Progetto lotta al tabagismo · 2C</v>
+      </c>
+      <c r="C207" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E207" t="str">
+        <v>09:05</v>
+      </c>
+      <c r="F207" t="str">
         <v>11:05</v>
       </c>
-      <c r="F206" t="str">
-        <v>13:05</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2026-11-19</v>
-      </c>
-      <c r="H206" t="str">
-        <v>2026-11-19</v>
-      </c>
-      <c r="I206" t="str">
-        <v/>
-      </c>
-      <c r="J206" t="str">
+      <c r="G207" t="str">
+        <v>2026-11-18</v>
+      </c>
+      <c r="H207" t="str">
+        <v>2026-11-18</v>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
         <v>Auditorium</v>
       </c>
-      <c r="K206" t="str">
+      <c r="K207" t="str">
         <v>terra</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207">
-        <v>4</v>
-      </c>
-      <c r="B207" t="str">
-        <v>PN Key for Schools · classi 3</v>
-      </c>
-      <c r="C207" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D207" t="str">
-        <v>Martedì</v>
-      </c>
-      <c r="E207" t="str">
-        <v>14:30</v>
-      </c>
-      <c r="F207" t="str">
-        <v>17:00</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2026-11-17</v>
-      </c>
-      <c r="H207" t="str">
-        <v>2026-11-17</v>
-      </c>
-      <c r="I207" t="str">
-        <v/>
-      </c>
-      <c r="J207" t="str">
-        <v/>
-      </c>
-      <c r="K207" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="208">
-      <c r="A208">
-        <v>21</v>
+      <c r="A208" t="str">
+        <v/>
       </c>
       <c r="B208" t="str">
-        <v>PN Arte</v>
+        <v>Progetto lotta al tabagismo · 2D</v>
       </c>
       <c r="C208" t="str">
         <v>temporanea</v>
@@ -7673,10 +7673,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E208" t="str">
-        <v>14:00</v>
+        <v>11:05</v>
       </c>
       <c r="F208" t="str">
-        <v>18:00</v>
+        <v>13:05</v>
       </c>
       <c r="G208" t="str">
         <v>2026-11-18</v>
@@ -7688,88 +7688,88 @@
         <v/>
       </c>
       <c r="J208" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K208" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209">
-        <v>10</v>
+      <c r="A209" t="str">
+        <v/>
       </c>
       <c r="B209" t="str">
-        <v>Orientamento con psicologa (classi 3)</v>
+        <v>Progetto lotta al tabagismo · 2A</v>
       </c>
       <c r="C209" t="str">
         <v>temporanea</v>
       </c>
       <c r="D209" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E209" t="str">
         <v>09:05</v>
       </c>
       <c r="F209" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="G209" t="str">
+        <v>2026-11-19</v>
+      </c>
+      <c r="H209" t="str">
+        <v>2026-11-19</v>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" t="str">
+        <v>Auditorium</v>
+      </c>
+      <c r="K209" t="str">
+        <v>terra</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v/>
+      </c>
+      <c r="B210" t="str">
+        <v>Progetto lotta al tabagismo · 2B</v>
+      </c>
+      <c r="C210" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Giovedì</v>
+      </c>
+      <c r="E210" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="F210" t="str">
         <v>13:05</v>
       </c>
-      <c r="G209" t="str">
-        <v>2026-11-17</v>
-      </c>
-      <c r="H209" t="str">
-        <v>2026-11-17</v>
-      </c>
-      <c r="I209" t="str">
-        <v/>
-      </c>
-      <c r="J209" t="str">
-        <v/>
-      </c>
-      <c r="K209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210">
-        <v>1</v>
-      </c>
-      <c r="B210" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
-      </c>
-      <c r="C210" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D210" t="str">
-        <v>Lunedì</v>
-      </c>
-      <c r="E210" t="str">
-        <v>08:30</v>
-      </c>
-      <c r="F210" t="str">
-        <v>13:00</v>
-      </c>
       <c r="G210" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-19</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-19</v>
       </c>
       <c r="I210" t="str">
         <v/>
       </c>
       <c r="J210" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K210" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B211" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C211" t="str">
         <v>temporanea</v>
@@ -7784,10 +7784,10 @@
         <v>17:00</v>
       </c>
       <c r="G211" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-17</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-17</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -7801,10 +7801,10 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B212" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>PN Arte</v>
       </c>
       <c r="C212" t="str">
         <v>temporanea</v>
@@ -7813,16 +7813,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E212" t="str">
-        <v>13:05</v>
+        <v>14:00</v>
       </c>
       <c r="F212" t="str">
-        <v>15:35</v>
+        <v>18:00</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-18</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-18</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -7835,38 +7835,38 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="str">
-        <v/>
+      <c r="A213">
+        <v>10</v>
       </c>
       <c r="B213" t="str">
-        <v>Progetto lettura: Pinocchio (classi 1 e 2)</v>
+        <v>Orientamento con psicologa (classi 3)</v>
       </c>
       <c r="C213" t="str">
         <v>temporanea</v>
       </c>
       <c r="D213" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E213" t="str">
-        <v>08:05</v>
+        <v>09:05</v>
       </c>
       <c r="F213" t="str">
         <v>13:05</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-17</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-17</v>
       </c>
       <c r="I213" t="str">
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K213" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -7880,7 +7880,7 @@
         <v>temporanea</v>
       </c>
       <c r="D214" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E214" t="str">
         <v>08:30</v>
@@ -7889,10 +7889,10 @@
         <v>13:00</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-23</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-23</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7905,64 +7905,64 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="str">
-        <v/>
+      <c r="A215">
+        <v>3</v>
       </c>
       <c r="B215" t="str">
-        <v>Open day</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C215" t="str">
         <v>temporanea</v>
       </c>
       <c r="D215" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E215" t="str">
-        <v>17:30</v>
+        <v>14:30</v>
       </c>
       <c r="F215" t="str">
-        <v>19:30</v>
+        <v>17:00</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K215" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B216" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C216" t="str">
         <v>temporanea</v>
       </c>
       <c r="D216" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E216" t="str">
-        <v>14:30</v>
+        <v>13:05</v>
       </c>
       <c r="F216" t="str">
-        <v>17:00</v>
+        <v>15:35</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7975,38 +7975,38 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217">
-        <v>21</v>
+      <c r="A217" t="str">
+        <v/>
       </c>
       <c r="B217" t="str">
-        <v>PN Arte</v>
+        <v>Progetto lettura: Pinocchio (classi 1 e 2)</v>
       </c>
       <c r="C217" t="str">
         <v>temporanea</v>
       </c>
       <c r="D217" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E217" t="str">
-        <v>14:00</v>
+        <v>08:05</v>
       </c>
       <c r="F217" t="str">
-        <v>18:00</v>
+        <v>13:05</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-26</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-26</v>
       </c>
       <c r="I217" t="str">
         <v/>
       </c>
       <c r="J217" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K217" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="218">
@@ -8020,7 +8020,7 @@
         <v>temporanea</v>
       </c>
       <c r="D218" t="str">
-        <v>Martedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E218" t="str">
         <v>08:30</v>
@@ -8029,10 +8029,10 @@
         <v>13:00</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-27</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-27</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -8045,46 +8045,46 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219">
-        <v>1</v>
+      <c r="A219" t="str">
+        <v/>
       </c>
       <c r="B219" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
+        <v>Open day</v>
       </c>
       <c r="C219" t="str">
         <v>temporanea</v>
       </c>
       <c r="D219" t="str">
-        <v>Mercoledì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E219" t="str">
-        <v>08:30</v>
+        <v>17:30</v>
       </c>
       <c r="F219" t="str">
-        <v>13:00</v>
+        <v>19:30</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-23</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-23</v>
       </c>
       <c r="I219" t="str">
         <v/>
       </c>
       <c r="J219" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K219" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B220" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C220" t="str">
         <v>temporanea</v>
@@ -8099,10 +8099,10 @@
         <v>17:00</v>
       </c>
       <c r="G220" t="str">
-        <v>2026-12-01</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-12-01</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B221" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>PN Arte</v>
       </c>
       <c r="C221" t="str">
         <v>temporanea</v>
@@ -8128,16 +8128,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E221" t="str">
-        <v>13:05</v>
+        <v>14:00</v>
       </c>
       <c r="F221" t="str">
-        <v>15:35</v>
+        <v>18:00</v>
       </c>
       <c r="G221" t="str">
-        <v>2026-12-02</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-12-02</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -8151,28 +8151,28 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B222" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C222" t="str">
         <v>temporanea</v>
       </c>
       <c r="D222" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E222" t="str">
-        <v>14:00</v>
+        <v>08:30</v>
       </c>
       <c r="F222" t="str">
-        <v>20:00</v>
+        <v>13:00</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-12-03</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-12-03</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -8186,28 +8186,28 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B223" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C223" t="str">
         <v>temporanea</v>
       </c>
       <c r="D223" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E223" t="str">
-        <v>14:00</v>
+        <v>08:30</v>
       </c>
       <c r="F223" t="str">
-        <v>20:00</v>
+        <v>13:00</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-12-04</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-12-04</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -8221,10 +8221,10 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B224" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C224" t="str">
         <v>temporanea</v>
@@ -8256,10 +8256,10 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B225" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C225" t="str">
         <v>temporanea</v>
@@ -8268,10 +8268,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E225" t="str">
-        <v>14:00</v>
+        <v>13:05</v>
       </c>
       <c r="F225" t="str">
-        <v>20:00</v>
+        <v>15:35</v>
       </c>
       <c r="G225" t="str">
         <v>2026-12-02</v>
@@ -8291,28 +8291,28 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B226" t="str">
-        <v>PN Arte</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C226" t="str">
         <v>temporanea</v>
       </c>
       <c r="D226" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E226" t="str">
         <v>14:00</v>
       </c>
       <c r="F226" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-03</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-03</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -8326,28 +8326,28 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B227" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C227" t="str">
         <v>temporanea</v>
       </c>
       <c r="D227" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E227" t="str">
-        <v>13:05</v>
+        <v>14:00</v>
       </c>
       <c r="F227" t="str">
-        <v>15:35</v>
+        <v>20:00</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-04</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-04</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8361,28 +8361,28 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B228" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C228" t="str">
         <v>temporanea</v>
       </c>
       <c r="D228" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E228" t="str">
-        <v>15:00</v>
+        <v>14:30</v>
       </c>
       <c r="F228" t="str">
-        <v>19:00</v>
+        <v>17:00</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-01</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-01</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8396,28 +8396,28 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B229" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C229" t="str">
         <v>temporanea</v>
       </c>
       <c r="D229" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E229" t="str">
-        <v>14:30</v>
+        <v>14:00</v>
       </c>
       <c r="F229" t="str">
-        <v>17:00</v>
+        <v>20:00</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-02</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8431,10 +8431,10 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B230" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>PN Arte</v>
       </c>
       <c r="C230" t="str">
         <v>temporanea</v>
@@ -8443,16 +8443,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E230" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F230" t="str">
-        <v>19:00</v>
+        <v>18:00</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-02</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8466,28 +8466,28 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B231" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C231" t="str">
         <v>temporanea</v>
       </c>
       <c r="D231" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E231" t="str">
-        <v>14:30</v>
+        <v>13:05</v>
       </c>
       <c r="F231" t="str">
-        <v>17:00</v>
+        <v>15:35</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
         <v>temporanea</v>
       </c>
       <c r="D232" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E232" t="str">
         <v>15:00</v>
@@ -8519,10 +8519,10 @@
         <v>19:00</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8545,7 +8545,7 @@
         <v>temporanea</v>
       </c>
       <c r="D233" t="str">
-        <v>Martedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E233" t="str">
         <v>14:30</v>
@@ -8554,10 +8554,10 @@
         <v>17:00</v>
       </c>
       <c r="G233" t="str">
-        <v>2026-12-15</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-12-15</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -8574,7 +8574,7 @@
         <v>2</v>
       </c>
       <c r="B234" t="str">
-        <v>Consigli di classe · classi 3</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C234" t="str">
         <v>temporanea</v>
@@ -8583,16 +8583,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E234" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F234" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-12-16</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-12-16</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8605,46 +8605,46 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="str">
-        <v/>
+      <c r="A235">
+        <v>4</v>
       </c>
       <c r="B235" t="str">
-        <v>Incontro ICARO/Pars · 3D + 3B</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C235" t="str">
         <v>temporanea</v>
       </c>
       <c r="D235" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E235" t="str">
-        <v>08:05</v>
+        <v>14:30</v>
       </c>
       <c r="F235" t="str">
-        <v>12:10</v>
+        <v>17:00</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-12-17</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I235" t="str">
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K235" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="str">
-        <v/>
+      <c r="A236">
+        <v>2</v>
       </c>
       <c r="B236" t="str">
-        <v>Incontro ICARO/Pars · 3A + 3C</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C236" t="str">
         <v>temporanea</v>
@@ -8653,33 +8653,33 @@
         <v>Venerdì</v>
       </c>
       <c r="E236" t="str">
-        <v>08:05</v>
+        <v>15:00</v>
       </c>
       <c r="F236" t="str">
-        <v>12:10</v>
+        <v>19:00</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I236" t="str">
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K236" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B237" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C237" t="str">
         <v>temporanea</v>
@@ -8710,38 +8710,38 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="str">
-        <v/>
+      <c r="A238">
+        <v>2</v>
       </c>
       <c r="B238" t="str">
-        <v>Incontro ICARO/Pars · docenti</v>
+        <v>Consigli di classe · classi 3</v>
       </c>
       <c r="C238" t="str">
         <v>temporanea</v>
       </c>
       <c r="D238" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E238" t="str">
-        <v>14:30</v>
+        <v>14:00</v>
       </c>
       <c r="F238" t="str">
-        <v>16:30</v>
+        <v>20:00</v>
       </c>
       <c r="G238" t="str">
-        <v>2027-01-12</v>
+        <v>2026-12-16</v>
       </c>
       <c r="H238" t="str">
-        <v>2027-01-12</v>
+        <v>2026-12-16</v>
       </c>
       <c r="I238" t="str">
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K238" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -8749,7 +8749,7 @@
         <v/>
       </c>
       <c r="B239" t="str">
-        <v>Incontro ICARO/Pars · genitori</v>
+        <v>Incontro ICARO/Pars · 3D + 3B</v>
       </c>
       <c r="C239" t="str">
         <v>temporanea</v>
@@ -8758,16 +8758,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E239" t="str">
-        <v>18:00</v>
+        <v>08:05</v>
       </c>
       <c r="F239" t="str">
-        <v>20:00</v>
+        <v>12:10</v>
       </c>
       <c r="G239" t="str">
-        <v>2027-01-14</v>
+        <v>2026-12-17</v>
       </c>
       <c r="H239" t="str">
-        <v>2027-01-14</v>
+        <v>2026-12-17</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -8784,25 +8784,25 @@
         <v/>
       </c>
       <c r="B240" t="str">
-        <v>Open day</v>
+        <v>Incontro ICARO/Pars · 3A + 3C</v>
       </c>
       <c r="C240" t="str">
         <v>temporanea</v>
       </c>
       <c r="D240" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E240" t="str">
-        <v>17:30</v>
+        <v>08:05</v>
       </c>
       <c r="F240" t="str">
-        <v>19:30</v>
+        <v>12:10</v>
       </c>
       <c r="G240" t="str">
-        <v>2027-01-18</v>
+        <v>2026-12-18</v>
       </c>
       <c r="H240" t="str">
-        <v>2027-01-18</v>
+        <v>2026-12-18</v>
       </c>
       <c r="I240" t="str">
         <v/>
@@ -8815,11 +8815,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="str">
-        <v/>
+      <c r="A241">
+        <v>4</v>
       </c>
       <c r="B241" t="str">
-        <v>Incontro ICARO/Pars · docenti</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C241" t="str">
         <v>temporanea</v>
@@ -8831,65 +8831,65 @@
         <v>14:30</v>
       </c>
       <c r="F241" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="G241" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="H241" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v/>
+      </c>
+      <c r="B242" t="str">
+        <v>Incontro ICARO/Pars · docenti</v>
+      </c>
+      <c r="C242" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Martedì</v>
+      </c>
+      <c r="E242" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="F242" t="str">
         <v>16:30</v>
       </c>
-      <c r="G241" t="str">
-        <v>2027-01-19</v>
-      </c>
-      <c r="H241" t="str">
-        <v>2027-01-19</v>
-      </c>
-      <c r="I241" t="str">
-        <v/>
-      </c>
-      <c r="J241" t="str">
+      <c r="G242" t="str">
+        <v>2027-01-12</v>
+      </c>
+      <c r="H242" t="str">
+        <v>2027-01-12</v>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
         <v>Auditorium</v>
       </c>
-      <c r="K241" t="str">
+      <c r="K242" t="str">
         <v>terra</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242">
-        <v>2</v>
-      </c>
-      <c r="B242" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C242" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D242" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E242" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="F242" t="str">
-        <v>20:00</v>
-      </c>
-      <c r="G242" t="str">
-        <v>2027-02-03</v>
-      </c>
-      <c r="H242" t="str">
-        <v>2027-02-03</v>
-      </c>
-      <c r="I242" t="str">
-        <v/>
-      </c>
-      <c r="J242" t="str">
-        <v/>
-      </c>
-      <c r="K242" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="243">
-      <c r="A243">
-        <v>2</v>
+      <c r="A243" t="str">
+        <v/>
       </c>
       <c r="B243" t="str">
-        <v>Scrutini</v>
+        <v>Incontro ICARO/Pars · genitori</v>
       </c>
       <c r="C243" t="str">
         <v>temporanea</v>
@@ -8898,121 +8898,121 @@
         <v>Giovedì</v>
       </c>
       <c r="E243" t="str">
-        <v>14:00</v>
+        <v>18:00</v>
       </c>
       <c r="F243" t="str">
         <v>20:00</v>
       </c>
       <c r="G243" t="str">
-        <v>2027-02-04</v>
+        <v>2027-01-14</v>
       </c>
       <c r="H243" t="str">
-        <v>2027-02-04</v>
+        <v>2027-01-14</v>
       </c>
       <c r="I243" t="str">
         <v/>
       </c>
       <c r="J243" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K243" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244">
-        <v>2</v>
+      <c r="A244" t="str">
+        <v/>
       </c>
       <c r="B244" t="str">
-        <v>Scrutini</v>
+        <v>Open day</v>
       </c>
       <c r="C244" t="str">
         <v>temporanea</v>
       </c>
       <c r="D244" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E244" t="str">
-        <v>14:00</v>
+        <v>17:30</v>
       </c>
       <c r="F244" t="str">
-        <v>20:00</v>
+        <v>19:30</v>
       </c>
       <c r="G244" t="str">
-        <v>2027-02-05</v>
+        <v>2027-01-18</v>
       </c>
       <c r="H244" t="str">
-        <v>2027-02-05</v>
+        <v>2027-01-18</v>
       </c>
       <c r="I244" t="str">
         <v/>
       </c>
       <c r="J244" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K244" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245">
-        <v>4</v>
+      <c r="A245" t="str">
+        <v/>
       </c>
       <c r="B245" t="str">
-        <v>Dip. verticale umanistico</v>
+        <v>Incontro ICARO/Pars · docenti</v>
       </c>
       <c r="C245" t="str">
         <v>temporanea</v>
       </c>
       <c r="D245" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E245" t="str">
-        <v>16:45</v>
+        <v>14:30</v>
       </c>
       <c r="F245" t="str">
-        <v>18:45</v>
+        <v>16:30</v>
       </c>
       <c r="G245" t="str">
-        <v>2027-02-15</v>
+        <v>2027-01-19</v>
       </c>
       <c r="H245" t="str">
-        <v>2027-02-15</v>
+        <v>2027-01-19</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K245" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B246" t="str">
-        <v>Dip. verticale matematico-scientifico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C246" t="str">
         <v>temporanea</v>
       </c>
       <c r="D246" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E246" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F246" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G246" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H246" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I246" t="str">
         <v/>
@@ -9026,28 +9026,28 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B247" t="str">
-        <v>Dip. verticale linguistico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C247" t="str">
         <v>temporanea</v>
       </c>
       <c r="D247" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E247" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F247" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G247" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H247" t="str">
-        <v>2027-02-15</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -9061,115 +9061,115 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B248" t="str">
-        <v>Dip. verticale artistico-motorio + musicale</v>
+        <v>Scrutini</v>
       </c>
       <c r="C248" t="str">
         <v>temporanea</v>
       </c>
       <c r="D248" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E248" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="F248" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="G248" t="str">
+        <v>2027-02-05</v>
+      </c>
+      <c r="H248" t="str">
+        <v>2027-02-05</v>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" t="str">
+        <v/>
+      </c>
+      <c r="K248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>4</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Dip. verticale umanistico</v>
+      </c>
+      <c r="C249" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D249" t="str">
         <v>Lunedì</v>
       </c>
-      <c r="E248" t="str">
+      <c r="E249" t="str">
         <v>16:45</v>
       </c>
-      <c r="F248" t="str">
+      <c r="F249" t="str">
         <v>18:45</v>
       </c>
-      <c r="G248" t="str">
+      <c r="G249" t="str">
         <v>2027-02-15</v>
       </c>
-      <c r="H248" t="str">
+      <c r="H249" t="str">
         <v>2027-02-15</v>
       </c>
-      <c r="I248" t="str">
-        <v/>
-      </c>
-      <c r="J248" t="str">
-        <v/>
-      </c>
-      <c r="K248" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v/>
-      </c>
-      <c r="B249" t="str">
-        <v>Incontro ICARO/Pars · 3B + 3D</v>
-      </c>
-      <c r="C249" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D249" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E249" t="str">
-        <v>08:05</v>
-      </c>
-      <c r="F249" t="str">
-        <v>12:10</v>
-      </c>
-      <c r="G249" t="str">
-        <v>2027-02-17</v>
-      </c>
-      <c r="H249" t="str">
-        <v>2027-02-17</v>
-      </c>
       <c r="I249" t="str">
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K249" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="str">
-        <v/>
+      <c r="A250">
+        <v>20</v>
       </c>
       <c r="B250" t="str">
-        <v>Incontro ICARO/Pars · 3C + 3A</v>
+        <v>Dip. verticale matematico-scientifico</v>
       </c>
       <c r="C250" t="str">
         <v>temporanea</v>
       </c>
       <c r="D250" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E250" t="str">
-        <v>08:05</v>
+        <v>16:45</v>
       </c>
       <c r="F250" t="str">
-        <v>12:10</v>
+        <v>18:45</v>
       </c>
       <c r="G250" t="str">
-        <v>2027-02-18</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H250" t="str">
-        <v>2027-02-18</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I250" t="str">
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K250" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="str">
-        <v/>
+      <c r="A251">
+        <v>3</v>
       </c>
       <c r="B251" t="str">
-        <v>Collegio docenti</v>
+        <v>Dip. verticale linguistico</v>
       </c>
       <c r="C251" t="str">
         <v>temporanea</v>
@@ -9178,51 +9178,51 @@
         <v>Lunedì</v>
       </c>
       <c r="E251" t="str">
-        <v>17:00</v>
+        <v>16:45</v>
       </c>
       <c r="F251" t="str">
-        <v>19:00</v>
+        <v>18:45</v>
       </c>
       <c r="G251" t="str">
-        <v>2027-03-15</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H251" t="str">
-        <v>2027-03-15</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I251" t="str">
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K251" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B252" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. verticale artistico-motorio + musicale</v>
       </c>
       <c r="C252" t="str">
         <v>temporanea</v>
       </c>
       <c r="D252" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E252" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F252" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G252" t="str">
-        <v>2027-03-16</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H252" t="str">
-        <v>2027-03-16</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -9235,73 +9235,73 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253">
-        <v>2</v>
+      <c r="A253" t="str">
+        <v/>
       </c>
       <c r="B253" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Incontro ICARO/Pars · 3B + 3D</v>
       </c>
       <c r="C253" t="str">
         <v>temporanea</v>
       </c>
       <c r="D253" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E253" t="str">
+        <v>08:05</v>
+      </c>
+      <c r="F253" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="G253" t="str">
+        <v>2027-02-17</v>
+      </c>
+      <c r="H253" t="str">
+        <v>2027-02-17</v>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253" t="str">
+        <v>Auditorium</v>
+      </c>
+      <c r="K253" t="str">
+        <v>terra</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v/>
+      </c>
+      <c r="B254" t="str">
+        <v>Incontro ICARO/Pars · 3C + 3A</v>
+      </c>
+      <c r="C254" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D254" t="str">
         <v>Giovedì</v>
       </c>
-      <c r="E253" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="F253" t="str">
-        <v>20:00</v>
-      </c>
-      <c r="G253" t="str">
-        <v>2027-03-18</v>
-      </c>
-      <c r="H253" t="str">
-        <v>2027-03-18</v>
-      </c>
-      <c r="I253" t="str">
-        <v/>
-      </c>
-      <c r="J253" t="str">
-        <v/>
-      </c>
-      <c r="K253" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254">
-        <v>2</v>
-      </c>
-      <c r="B254" t="str">
-        <v>Consigli di classe con genitori</v>
-      </c>
-      <c r="C254" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D254" t="str">
-        <v>Venerdì</v>
-      </c>
       <c r="E254" t="str">
-        <v>14:00</v>
+        <v>08:05</v>
       </c>
       <c r="F254" t="str">
-        <v>20:00</v>
+        <v>12:10</v>
       </c>
       <c r="G254" t="str">
-        <v>2027-03-19</v>
+        <v>2027-02-18</v>
       </c>
       <c r="H254" t="str">
-        <v>2027-03-19</v>
+        <v>2027-02-18</v>
       </c>
       <c r="I254" t="str">
         <v/>
       </c>
       <c r="J254" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K254" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="255">
@@ -9309,25 +9309,25 @@
         <v/>
       </c>
       <c r="B255" t="str">
-        <v>Spettacolo teatrale in lingua inglese</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C255" t="str">
         <v>temporanea</v>
       </c>
       <c r="D255" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E255" t="str">
-        <v>08:05</v>
+        <v>17:00</v>
       </c>
       <c r="F255" t="str">
-        <v>13:05</v>
+        <v>19:00</v>
       </c>
       <c r="G255" t="str">
-        <v>2027-03-18</v>
+        <v>2027-03-15</v>
       </c>
       <c r="H255" t="str">
-        <v>2027-03-18</v>
+        <v>2027-03-15</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -9344,25 +9344,25 @@
         <v>2</v>
       </c>
       <c r="B256" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C256" t="str">
         <v>temporanea</v>
       </c>
       <c r="D256" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E256" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F256" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G256" t="str">
-        <v>2027-04-14</v>
+        <v>2027-03-16</v>
       </c>
       <c r="H256" t="str">
-        <v>2027-04-14</v>
+        <v>2027-03-16</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9379,7 +9379,7 @@
         <v>2</v>
       </c>
       <c r="B257" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C257" t="str">
         <v>temporanea</v>
@@ -9388,16 +9388,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E257" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F257" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G257" t="str">
-        <v>2027-04-15</v>
+        <v>2027-03-18</v>
       </c>
       <c r="H257" t="str">
-        <v>2027-04-15</v>
+        <v>2027-03-18</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9414,7 +9414,7 @@
         <v>2</v>
       </c>
       <c r="B258" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C258" t="str">
         <v>temporanea</v>
@@ -9423,16 +9423,16 @@
         <v>Venerdì</v>
       </c>
       <c r="E258" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F258" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G258" t="str">
-        <v>2027-04-16</v>
+        <v>2027-03-19</v>
       </c>
       <c r="H258" t="str">
-        <v>2027-04-16</v>
+        <v>2027-03-19</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9445,46 +9445,46 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259">
-        <v>4</v>
+      <c r="A259" t="str">
+        <v/>
       </c>
       <c r="B259" t="str">
-        <v>Dip. umanistico</v>
+        <v>Spettacolo teatrale in lingua inglese</v>
       </c>
       <c r="C259" t="str">
         <v>temporanea</v>
       </c>
       <c r="D259" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E259" t="str">
-        <v>16:00</v>
+        <v>08:05</v>
       </c>
       <c r="F259" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G259" t="str">
-        <v>2027-04-21</v>
+        <v>2027-03-18</v>
       </c>
       <c r="H259" t="str">
-        <v>2027-04-21</v>
+        <v>2027-03-18</v>
       </c>
       <c r="I259" t="str">
         <v/>
       </c>
       <c r="J259" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K259" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B260" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C260" t="str">
         <v>temporanea</v>
@@ -9493,16 +9493,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E260" t="str">
-        <v>16:00</v>
+        <v>15:00</v>
       </c>
       <c r="F260" t="str">
-        <v>17:00</v>
+        <v>19:00</v>
       </c>
       <c r="G260" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H260" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9516,28 +9516,28 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B261" t="str">
-        <v>Dip. linguistico</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C261" t="str">
         <v>temporanea</v>
       </c>
       <c r="D261" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E261" t="str">
-        <v>16:00</v>
+        <v>15:00</v>
       </c>
       <c r="F261" t="str">
-        <v>17:00</v>
+        <v>19:00</v>
       </c>
       <c r="G261" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H261" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I261" t="str">
         <v/>
@@ -9551,28 +9551,28 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B262" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C262" t="str">
         <v>temporanea</v>
       </c>
       <c r="D262" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E262" t="str">
-        <v>16:00</v>
+        <v>15:00</v>
       </c>
       <c r="F262" t="str">
-        <v>17:00</v>
+        <v>19:00</v>
       </c>
       <c r="G262" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H262" t="str">
-        <v>2027-04-21</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9586,10 +9586,10 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B263" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C263" t="str">
         <v>temporanea</v>
@@ -9598,16 +9598,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E263" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F263" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G263" t="str">
-        <v>2027-05-05</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H263" t="str">
-        <v>2027-05-05</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9621,28 +9621,28 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B264" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C264" t="str">
         <v>temporanea</v>
       </c>
       <c r="D264" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E264" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F264" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G264" t="str">
-        <v>2027-05-06</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H264" t="str">
-        <v>2027-05-06</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9656,28 +9656,28 @@
     </row>
     <row r="265">
       <c r="A265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B265" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C265" t="str">
         <v>temporanea</v>
       </c>
       <c r="D265" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E265" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F265" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G265" t="str">
-        <v>2027-05-07</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H265" t="str">
-        <v>2027-05-07</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B266" t="str">
-        <v>Dip. umanistico</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C266" t="str">
         <v>temporanea</v>
@@ -9706,13 +9706,13 @@
         <v>16:00</v>
       </c>
       <c r="F266" t="str">
-        <v>18:00</v>
+        <v>17:00</v>
       </c>
       <c r="G266" t="str">
-        <v>2027-05-12</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H266" t="str">
-        <v>2027-05-12</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I266" t="str">
         <v/>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B267" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C267" t="str">
         <v>temporanea</v>
@@ -9738,16 +9738,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E267" t="str">
-        <v>16:00</v>
+        <v>14:00</v>
       </c>
       <c r="F267" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G267" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-05</v>
       </c>
       <c r="H267" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-05</v>
       </c>
       <c r="I267" t="str">
         <v/>
@@ -9761,28 +9761,28 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B268" t="str">
-        <v>Dip. linguistico</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C268" t="str">
         <v>temporanea</v>
       </c>
       <c r="D268" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E268" t="str">
-        <v>16:00</v>
+        <v>14:00</v>
       </c>
       <c r="F268" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G268" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-06</v>
       </c>
       <c r="H268" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-06</v>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -9796,80 +9796,80 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B269" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C269" t="str">
         <v>temporanea</v>
       </c>
       <c r="D269" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E269" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="F269" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="G269" t="str">
+        <v>2027-05-07</v>
+      </c>
+      <c r="H269" t="str">
+        <v>2027-05-07</v>
+      </c>
+      <c r="I269" t="str">
+        <v/>
+      </c>
+      <c r="J269" t="str">
+        <v/>
+      </c>
+      <c r="K269" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>4</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Dip. umanistico</v>
+      </c>
+      <c r="C270" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D270" t="str">
         <v>Mercoledì</v>
       </c>
-      <c r="E269" t="str">
+      <c r="E270" t="str">
         <v>16:00</v>
       </c>
-      <c r="F269" t="str">
+      <c r="F270" t="str">
         <v>18:00</v>
       </c>
-      <c r="G269" t="str">
+      <c r="G270" t="str">
         <v>2027-05-12</v>
       </c>
-      <c r="H269" t="str">
+      <c r="H270" t="str">
         <v>2027-05-12</v>
       </c>
-      <c r="I269" t="str">
-        <v/>
-      </c>
-      <c r="J269" t="str">
-        <v/>
-      </c>
-      <c r="K269" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v/>
-      </c>
-      <c r="B270" t="str">
-        <v>Collegio docenti</v>
-      </c>
-      <c r="C270" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D270" t="str">
-        <v>Giovedì</v>
-      </c>
-      <c r="E270" t="str">
-        <v>17:00</v>
-      </c>
-      <c r="F270" t="str">
-        <v>19:00</v>
-      </c>
-      <c r="G270" t="str">
-        <v>2027-05-13</v>
-      </c>
-      <c r="H270" t="str">
-        <v>2027-05-13</v>
-      </c>
       <c r="I270" t="str">
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K270" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B271" t="str">
-        <v>Dip. verticale umanistico</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C271" t="str">
         <v>temporanea</v>
@@ -9878,16 +9878,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E271" t="str">
-        <v>16:45</v>
+        <v>16:00</v>
       </c>
       <c r="F271" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G271" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H271" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B272" t="str">
-        <v>Dip. verticale matematico-scientifico</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C272" t="str">
         <v>temporanea</v>
@@ -9913,16 +9913,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E272" t="str">
-        <v>16:45</v>
+        <v>16:00</v>
       </c>
       <c r="F272" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G272" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H272" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B273" t="str">
-        <v>Dip. verticale linguistico</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C273" t="str">
         <v>temporanea</v>
@@ -9948,16 +9948,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E273" t="str">
-        <v>16:45</v>
+        <v>16:00</v>
       </c>
       <c r="F273" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G273" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H273" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9970,64 +9970,64 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274">
-        <v>5</v>
+      <c r="A274" t="str">
+        <v/>
       </c>
       <c r="B274" t="str">
-        <v>Dip. verticale artistico-motorio + musicale</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C274" t="str">
         <v>temporanea</v>
       </c>
       <c r="D274" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E274" t="str">
-        <v>16:45</v>
+        <v>17:00</v>
       </c>
       <c r="F274" t="str">
-        <v>18:45</v>
+        <v>19:00</v>
       </c>
       <c r="G274" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-13</v>
       </c>
       <c r="H274" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-13</v>
       </c>
       <c r="I274" t="str">
         <v/>
       </c>
       <c r="J274" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K274" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B275" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. verticale umanistico</v>
       </c>
       <c r="C275" t="str">
         <v>temporanea</v>
       </c>
       <c r="D275" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E275" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F275" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G275" t="str">
-        <v>2027-05-25</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H275" t="str">
-        <v>2027-05-25</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I275" t="str">
         <v/>
@@ -10041,10 +10041,10 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B276" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. verticale matematico-scientifico</v>
       </c>
       <c r="C276" t="str">
         <v>temporanea</v>
@@ -10053,16 +10053,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E276" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F276" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G276" t="str">
-        <v>2027-05-26</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H276" t="str">
-        <v>2027-05-26</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I276" t="str">
         <v/>
@@ -10076,28 +10076,28 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B277" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. verticale linguistico</v>
       </c>
       <c r="C277" t="str">
         <v>temporanea</v>
       </c>
       <c r="D277" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E277" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F277" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G277" t="str">
-        <v>2027-05-27</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H277" t="str">
-        <v>2027-05-27</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -10111,28 +10111,28 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B278" t="str">
-        <v>Dip. umanistico</v>
+        <v>Dip. verticale artistico-motorio + musicale</v>
       </c>
       <c r="C278" t="str">
         <v>temporanea</v>
       </c>
       <c r="D278" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E278" t="str">
-        <v>16:30</v>
+        <v>16:45</v>
       </c>
       <c r="F278" t="str">
-        <v>18:00</v>
+        <v>18:45</v>
       </c>
       <c r="G278" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H278" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -10146,28 +10146,28 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B279" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Consigli di classe</v>
       </c>
       <c r="C279" t="str">
         <v>temporanea</v>
       </c>
       <c r="D279" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E279" t="str">
-        <v>16:30</v>
+        <v>14:00</v>
       </c>
       <c r="F279" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G279" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-25</v>
       </c>
       <c r="H279" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-25</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -10181,28 +10181,28 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B280" t="str">
-        <v>Dip. linguistico</v>
+        <v>Consigli di classe</v>
       </c>
       <c r="C280" t="str">
         <v>temporanea</v>
       </c>
       <c r="D280" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E280" t="str">
-        <v>16:30</v>
+        <v>14:00</v>
       </c>
       <c r="F280" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G280" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-26</v>
       </c>
       <c r="H280" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-26</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B281" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Consigli di classe</v>
       </c>
       <c r="C281" t="str">
         <v>temporanea</v>
@@ -10228,16 +10228,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E281" t="str">
-        <v>16:30</v>
+        <v>14:00</v>
       </c>
       <c r="F281" t="str">
-        <v>18:00</v>
+        <v>20:00</v>
       </c>
       <c r="G281" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-27</v>
       </c>
       <c r="H281" t="str">
-        <v>2027-06-03</v>
+        <v>2027-05-27</v>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -10260,19 +10260,19 @@
         <v>temporanea</v>
       </c>
       <c r="D282" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E282" t="str">
-        <v>15:00</v>
+        <v>16:30</v>
       </c>
       <c r="F282" t="str">
-        <v>16:30</v>
+        <v>18:00</v>
       </c>
       <c r="G282" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H282" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I282" t="str">
         <v/>
@@ -10295,19 +10295,19 @@
         <v>temporanea</v>
       </c>
       <c r="D283" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E283" t="str">
-        <v>15:00</v>
+        <v>16:30</v>
       </c>
       <c r="F283" t="str">
-        <v>16:30</v>
+        <v>18:00</v>
       </c>
       <c r="G283" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H283" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I283" t="str">
         <v/>
@@ -10330,19 +10330,19 @@
         <v>temporanea</v>
       </c>
       <c r="D284" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E284" t="str">
-        <v>15:00</v>
+        <v>16:30</v>
       </c>
       <c r="F284" t="str">
-        <v>16:30</v>
+        <v>18:00</v>
       </c>
       <c r="G284" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H284" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -10365,19 +10365,19 @@
         <v>temporanea</v>
       </c>
       <c r="D285" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E285" t="str">
-        <v>15:00</v>
+        <v>16:30</v>
       </c>
       <c r="F285" t="str">
-        <v>16:30</v>
+        <v>18:00</v>
       </c>
       <c r="G285" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H285" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -10391,28 +10391,28 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B286" t="str">
-        <v>Scrutini</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C286" t="str">
         <v>temporanea</v>
       </c>
       <c r="D286" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E286" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F286" t="str">
-        <v>17:30</v>
+        <v>16:30</v>
       </c>
       <c r="G286" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H286" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -10426,28 +10426,28 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B287" t="str">
-        <v>Scrutini</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C287" t="str">
         <v>temporanea</v>
       </c>
       <c r="D287" t="str">
-        <v>Martedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E287" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F287" t="str">
-        <v>17:30</v>
+        <v>16:30</v>
       </c>
       <c r="G287" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H287" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -10461,28 +10461,28 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B288" t="str">
-        <v>Scrutini</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C288" t="str">
         <v>temporanea</v>
       </c>
       <c r="D288" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E288" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F288" t="str">
-        <v>17:30</v>
+        <v>16:30</v>
       </c>
       <c r="G288" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H288" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10495,11 +10495,11 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="str">
-        <v/>
+      <c r="A289">
+        <v>5</v>
       </c>
       <c r="B289" t="str">
-        <v>Esame: prova scritta italiano</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C289" t="str">
         <v>temporanea</v>
@@ -10508,33 +10508,33 @@
         <v>Venerdì</v>
       </c>
       <c r="E289" t="str">
-        <v>08:30</v>
+        <v>15:00</v>
       </c>
       <c r="F289" t="str">
-        <v>12:30</v>
+        <v>16:30</v>
       </c>
       <c r="G289" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H289" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I289" t="str">
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K289" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="str">
-        <v/>
+      <c r="A290">
+        <v>2</v>
       </c>
       <c r="B290" t="str">
-        <v>Esame: prova scritta matematica</v>
+        <v>Scrutini</v>
       </c>
       <c r="C290" t="str">
         <v>temporanea</v>
@@ -10543,33 +10543,33 @@
         <v>Lunedì</v>
       </c>
       <c r="E290" t="str">
-        <v>08:30</v>
+        <v>09:30</v>
       </c>
       <c r="F290" t="str">
-        <v>12:30</v>
+        <v>17:30</v>
       </c>
       <c r="G290" t="str">
-        <v>2027-06-14</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H290" t="str">
-        <v>2027-06-14</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I290" t="str">
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K290" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B291" t="str">
-        <v>Dip. umanistico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C291" t="str">
         <v>temporanea</v>
@@ -10578,16 +10578,16 @@
         <v>Martedì</v>
       </c>
       <c r="E291" t="str">
-        <v>16:30</v>
+        <v>09:30</v>
       </c>
       <c r="F291" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G291" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H291" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10601,28 +10601,28 @@
     </row>
     <row r="292">
       <c r="A292">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B292" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C292" t="str">
         <v>temporanea</v>
       </c>
       <c r="D292" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E292" t="str">
-        <v>16:30</v>
+        <v>09:30</v>
       </c>
       <c r="F292" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G292" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H292" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I292" t="str">
         <v/>
@@ -10635,99 +10635,99 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293">
-        <v>3</v>
+      <c r="A293" t="str">
+        <v/>
       </c>
       <c r="B293" t="str">
-        <v>Dip. linguistico</v>
+        <v>Esame: prova scritta italiano</v>
       </c>
       <c r="C293" t="str">
         <v>temporanea</v>
       </c>
       <c r="D293" t="str">
-        <v>Martedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E293" t="str">
-        <v>16:30</v>
+        <v>08:30</v>
       </c>
       <c r="F293" t="str">
-        <v>18:00</v>
+        <v>12:30</v>
       </c>
       <c r="G293" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-11</v>
       </c>
       <c r="H293" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-11</v>
       </c>
       <c r="I293" t="str">
         <v/>
       </c>
       <c r="J293" t="str">
-        <v/>
+        <v>Corridoi piano terra</v>
       </c>
       <c r="K293" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294">
-        <v>5</v>
+      <c r="A294" t="str">
+        <v/>
       </c>
       <c r="B294" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Esame: prova scritta matematica</v>
       </c>
       <c r="C294" t="str">
         <v>temporanea</v>
       </c>
       <c r="D294" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E294" t="str">
-        <v>16:30</v>
+        <v>08:30</v>
       </c>
       <c r="F294" t="str">
-        <v>18:00</v>
+        <v>12:30</v>
       </c>
       <c r="G294" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-14</v>
       </c>
       <c r="H294" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-14</v>
       </c>
       <c r="I294" t="str">
         <v/>
       </c>
       <c r="J294" t="str">
-        <v/>
+        <v>Corridoi piano terra</v>
       </c>
       <c r="K294" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B295" t="str">
-        <v>Esami: orali</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C295" t="str">
         <v>temporanea</v>
       </c>
       <c r="D295" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E295" t="str">
-        <v>08:30</v>
+        <v>16:30</v>
       </c>
       <c r="F295" t="str">
-        <v>17:30</v>
+        <v>18:00</v>
       </c>
       <c r="G295" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H295" t="str">
-        <v>2027-06-17</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10741,28 +10741,28 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B296" t="str">
-        <v>Esami: orali</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C296" t="str">
         <v>temporanea</v>
       </c>
       <c r="D296" t="str">
-        <v>Venerdì</v>
+        <v>Martedì</v>
       </c>
       <c r="E296" t="str">
-        <v>08:30</v>
+        <v>16:30</v>
       </c>
       <c r="F296" t="str">
-        <v>17:30</v>
+        <v>18:00</v>
       </c>
       <c r="G296" t="str">
-        <v>2027-06-18</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H296" t="str">
-        <v>2027-06-18</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10775,11 +10775,11 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="str">
-        <v/>
+      <c r="A297">
+        <v>3</v>
       </c>
       <c r="B297" t="str">
-        <v>Esame: prova scritta lingue</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C297" t="str">
         <v>temporanea</v>
@@ -10788,10 +10788,10 @@
         <v>Martedì</v>
       </c>
       <c r="E297" t="str">
-        <v>08:30</v>
+        <v>16:30</v>
       </c>
       <c r="F297" t="str">
-        <v>12:30</v>
+        <v>18:00</v>
       </c>
       <c r="G297" t="str">
         <v>2027-06-15</v>
@@ -10803,36 +10803,36 @@
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K297" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B298" t="str">
-        <v>Esami: orali</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C298" t="str">
         <v>temporanea</v>
       </c>
       <c r="D298" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E298" t="str">
-        <v>08:30</v>
+        <v>16:30</v>
       </c>
       <c r="F298" t="str">
-        <v>17:30</v>
+        <v>18:00</v>
       </c>
       <c r="G298" t="str">
-        <v>2027-06-21</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H298" t="str">
-        <v>2027-06-21</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -10855,7 +10855,7 @@
         <v>temporanea</v>
       </c>
       <c r="D299" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E299" t="str">
         <v>08:30</v>
@@ -10864,10 +10864,10 @@
         <v>17:30</v>
       </c>
       <c r="G299" t="str">
-        <v>2027-06-22</v>
+        <v>2027-06-17</v>
       </c>
       <c r="H299" t="str">
-        <v>2027-06-22</v>
+        <v>2027-06-17</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10880,99 +10880,99 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="str">
-        <v/>
+      <c r="A300">
+        <v>2</v>
       </c>
       <c r="B300" t="str">
-        <v>Collegio docenti</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C300" t="str">
         <v>temporanea</v>
       </c>
       <c r="D300" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E300" t="str">
-        <v>17:00</v>
+        <v>08:30</v>
       </c>
       <c r="F300" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G300" t="str">
-        <v>2027-06-30</v>
+        <v>2027-06-18</v>
       </c>
       <c r="H300" t="str">
-        <v>2027-06-30</v>
+        <v>2027-06-18</v>
       </c>
       <c r="I300" t="str">
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K300" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v/>
+      </c>
+      <c r="B301" t="str">
+        <v>Esame: prova scritta lingue</v>
+      </c>
+      <c r="C301" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Martedì</v>
+      </c>
+      <c r="E301" t="str">
+        <v>08:30</v>
+      </c>
+      <c r="F301" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="G301" t="str">
+        <v>2027-06-15</v>
+      </c>
+      <c r="H301" t="str">
+        <v>2027-06-15</v>
+      </c>
+      <c r="I301" t="str">
+        <v/>
+      </c>
+      <c r="J301" t="str">
+        <v>Corridoi piano terra</v>
+      </c>
+      <c r="K301" t="str">
         <v>terra</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301">
-        <v>1</v>
-      </c>
-      <c r="B301" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
-      </c>
-      <c r="C301" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D301" t="str">
-        <v>Giovedì</v>
-      </c>
-      <c r="E301" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="F301" t="str">
-        <v>19:00</v>
-      </c>
-      <c r="G301" t="str">
-        <v>2026-10-22</v>
-      </c>
-      <c r="H301" t="str">
-        <v>2026-10-22</v>
-      </c>
-      <c r="I301" t="str">
-        <v/>
-      </c>
-      <c r="J301" t="str">
-        <v/>
-      </c>
-      <c r="K301" t="str">
-        <v/>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B302" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C302" t="str">
         <v>temporanea</v>
       </c>
       <c r="D302" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E302" t="str">
-        <v>18:00</v>
+        <v>08:30</v>
       </c>
       <c r="F302" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G302" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-21</v>
       </c>
       <c r="H302" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-21</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10986,28 +10986,28 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B303" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C303" t="str">
         <v>temporanea</v>
       </c>
       <c r="D303" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E303" t="str">
-        <v>18:00</v>
+        <v>08:30</v>
       </c>
       <c r="F303" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G303" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-22</v>
       </c>
       <c r="H303" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-22</v>
       </c>
       <c r="I303" t="str">
         <v/>
@@ -11020,43 +11020,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304">
-        <v>5</v>
+      <c r="A304" t="str">
+        <v/>
       </c>
       <c r="B304" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C304" t="str">
         <v>temporanea</v>
       </c>
       <c r="D304" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E304" t="str">
-        <v>18:00</v>
+        <v>17:00</v>
       </c>
       <c r="F304" t="str">
         <v>19:00</v>
       </c>
       <c r="G304" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-30</v>
       </c>
       <c r="H304" t="str">
-        <v>2026-10-22</v>
+        <v>2027-06-30</v>
       </c>
       <c r="I304" t="str">
         <v/>
       </c>
       <c r="J304" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K304" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B305" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11091,7 +11091,7 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B306" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B307" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11161,7 +11161,7 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B308" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B309" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11231,7 +11231,7 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B310" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B311" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B312" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B313" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11371,7 +11371,7 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B314" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B315" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11441,7 +11441,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B316" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B317" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B318" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B319" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11581,7 +11581,7 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B320" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B321" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11651,7 +11651,7 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B322" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B323" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11721,7 +11721,7 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B324" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B325" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11791,10 +11791,10 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B326" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C326" t="str">
         <v>temporanea</v>
@@ -11803,16 +11803,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E326" t="str">
-        <v>15:00</v>
+        <v>18:00</v>
       </c>
       <c r="F326" t="str">
         <v>19:00</v>
       </c>
       <c r="G326" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H326" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I326" t="str">
         <v/>
@@ -11826,10 +11826,10 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B327" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C327" t="str">
         <v>temporanea</v>
@@ -11838,16 +11838,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E327" t="str">
-        <v>15:00</v>
+        <v>18:00</v>
       </c>
       <c r="F327" t="str">
         <v>19:00</v>
       </c>
       <c r="G327" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H327" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I327" t="str">
         <v/>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B328" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C328" t="str">
         <v>temporanea</v>
@@ -11873,16 +11873,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E328" t="str">
-        <v>15:00</v>
+        <v>18:00</v>
       </c>
       <c r="F328" t="str">
         <v>19:00</v>
       </c>
       <c r="G328" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H328" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I328" t="str">
         <v/>
@@ -11896,10 +11896,10 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B329" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C329" t="str">
         <v>temporanea</v>
@@ -11908,16 +11908,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E329" t="str">
-        <v>15:00</v>
+        <v>18:00</v>
       </c>
       <c r="F329" t="str">
         <v>19:00</v>
       </c>
       <c r="G329" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H329" t="str">
-        <v>2026-12-10</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I329" t="str">
         <v/>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B330" t="str">
         <v>Colloqui con le famiglie</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B331" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12001,7 +12001,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B332" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B333" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12071,7 +12071,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B334" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B335" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12141,7 +12141,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B336" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B337" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12211,7 +12211,7 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B338" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B339" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B340" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B341" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12351,7 +12351,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B342" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B343" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12421,7 +12421,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B344" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B345" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12491,7 +12491,7 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B346" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B347" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12561,7 +12561,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B348" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B349" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12631,7 +12631,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B350" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B351" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12675,7 +12675,7 @@
         <v>temporanea</v>
       </c>
       <c r="D351" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E351" t="str">
         <v>15:00</v>
@@ -12684,10 +12684,10 @@
         <v>19:00</v>
       </c>
       <c r="G351" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H351" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I351" t="str">
         <v/>
@@ -12701,7 +12701,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B352" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12710,7 +12710,7 @@
         <v>temporanea</v>
       </c>
       <c r="D352" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E352" t="str">
         <v>15:00</v>
@@ -12719,10 +12719,10 @@
         <v>19:00</v>
       </c>
       <c r="G352" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H352" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B353" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12745,7 +12745,7 @@
         <v>temporanea</v>
       </c>
       <c r="D353" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E353" t="str">
         <v>15:00</v>
@@ -12754,10 +12754,10 @@
         <v>19:00</v>
       </c>
       <c r="G353" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H353" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12771,7 +12771,7 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B354" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12780,7 +12780,7 @@
         <v>temporanea</v>
       </c>
       <c r="D354" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E354" t="str">
         <v>15:00</v>
@@ -12789,10 +12789,10 @@
         <v>19:00</v>
       </c>
       <c r="G354" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H354" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I354" t="str">
         <v/>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B355" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12841,7 +12841,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B356" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B357" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12911,7 +12911,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B358" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B359" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12981,7 +12981,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B360" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B361" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B362" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B363" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B364" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B365" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13191,7 +13191,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B366" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B367" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13261,7 +13261,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B368" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B369" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13331,7 +13331,7 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B370" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B371" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13401,7 +13401,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B372" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B373" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13471,7 +13471,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B374" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B375" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13515,7 +13515,7 @@
         <v>temporanea</v>
       </c>
       <c r="D375" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E375" t="str">
         <v>15:00</v>
@@ -13524,10 +13524,10 @@
         <v>19:00</v>
       </c>
       <c r="G375" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H375" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I375" t="str">
         <v/>
@@ -13541,7 +13541,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B376" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13550,7 +13550,7 @@
         <v>temporanea</v>
       </c>
       <c r="D376" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E376" t="str">
         <v>15:00</v>
@@ -13559,10 +13559,10 @@
         <v>19:00</v>
       </c>
       <c r="G376" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H376" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I376" t="str">
         <v/>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B377" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13585,7 +13585,7 @@
         <v>temporanea</v>
       </c>
       <c r="D377" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E377" t="str">
         <v>15:00</v>
@@ -13594,10 +13594,10 @@
         <v>19:00</v>
       </c>
       <c r="G377" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H377" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I377" t="str">
         <v/>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B378" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13620,7 +13620,7 @@
         <v>temporanea</v>
       </c>
       <c r="D378" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E378" t="str">
         <v>15:00</v>
@@ -13629,10 +13629,10 @@
         <v>19:00</v>
       </c>
       <c r="G378" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H378" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I378" t="str">
         <v/>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B379" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13681,7 +13681,7 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B380" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B381" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13751,7 +13751,7 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B382" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B383" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13821,7 +13821,7 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B384" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B385" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13891,7 +13891,7 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B386" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B387" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13961,7 +13961,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B388" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B389" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14031,7 +14031,7 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B390" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B391" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14101,7 +14101,7 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B392" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B393" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14171,7 +14171,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B394" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B395" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14241,7 +14241,7 @@
     </row>
     <row r="396">
       <c r="A396">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B396" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B397" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14311,28 +14311,28 @@
     </row>
     <row r="398">
       <c r="A398">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B398" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C398" t="str">
         <v>temporanea</v>
       </c>
       <c r="D398" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E398" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F398" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G398" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H398" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I398" t="str">
         <v/>
@@ -14346,28 +14346,28 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B399" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C399" t="str">
         <v>temporanea</v>
       </c>
       <c r="D399" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E399" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F399" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G399" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H399" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I399" t="str">
         <v/>
@@ -14381,28 +14381,28 @@
     </row>
     <row r="400">
       <c r="A400">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B400" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C400" t="str">
         <v>temporanea</v>
       </c>
       <c r="D400" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E400" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F400" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G400" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H400" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I400" t="str">
         <v/>
@@ -14416,28 +14416,28 @@
     </row>
     <row r="401">
       <c r="A401">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B401" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C401" t="str">
         <v>temporanea</v>
       </c>
       <c r="D401" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E401" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F401" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G401" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H401" t="str">
-        <v>2027-02-03</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I401" t="str">
         <v/>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="402">
       <c r="A402">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B402" t="str">
         <v>Scrutini</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="403">
       <c r="A403">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B403" t="str">
         <v>Scrutini</v>
@@ -14521,7 +14521,7 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B404" t="str">
         <v>Scrutini</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B405" t="str">
         <v>Scrutini</v>
@@ -14591,7 +14591,7 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B406" t="str">
         <v>Scrutini</v>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="407">
       <c r="A407">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B407" t="str">
         <v>Scrutini</v>
@@ -14661,7 +14661,7 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B408" t="str">
         <v>Scrutini</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="409">
       <c r="A409">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B409" t="str">
         <v>Scrutini</v>
@@ -14731,7 +14731,7 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B410" t="str">
         <v>Scrutini</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B411" t="str">
         <v>Scrutini</v>
@@ -14801,7 +14801,7 @@
     </row>
     <row r="412">
       <c r="A412">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B412" t="str">
         <v>Scrutini</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B413" t="str">
         <v>Scrutini</v>
@@ -14871,7 +14871,7 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B414" t="str">
         <v>Scrutini</v>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="415">
       <c r="A415">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B415" t="str">
         <v>Scrutini</v>
@@ -14941,7 +14941,7 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B416" t="str">
         <v>Scrutini</v>
@@ -14976,7 +14976,7 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B417" t="str">
         <v>Scrutini</v>
@@ -15011,7 +15011,7 @@
     </row>
     <row r="418">
       <c r="A418">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B418" t="str">
         <v>Scrutini</v>
@@ -15046,7 +15046,7 @@
     </row>
     <row r="419">
       <c r="A419">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B419" t="str">
         <v>Scrutini</v>
@@ -15081,7 +15081,7 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B420" t="str">
         <v>Scrutini</v>
@@ -15116,7 +15116,7 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B421" t="str">
         <v>Scrutini</v>
@@ -15151,7 +15151,7 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B422" t="str">
         <v>Scrutini</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B423" t="str">
         <v>Scrutini</v>
@@ -15195,7 +15195,7 @@
         <v>temporanea</v>
       </c>
       <c r="D423" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E423" t="str">
         <v>14:00</v>
@@ -15204,10 +15204,10 @@
         <v>20:00</v>
       </c>
       <c r="G423" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H423" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I423" t="str">
         <v/>
@@ -15221,7 +15221,7 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B424" t="str">
         <v>Scrutini</v>
@@ -15230,7 +15230,7 @@
         <v>temporanea</v>
       </c>
       <c r="D424" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E424" t="str">
         <v>14:00</v>
@@ -15239,10 +15239,10 @@
         <v>20:00</v>
       </c>
       <c r="G424" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H424" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I424" t="str">
         <v/>
@@ -15256,7 +15256,7 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B425" t="str">
         <v>Scrutini</v>
@@ -15265,7 +15265,7 @@
         <v>temporanea</v>
       </c>
       <c r="D425" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E425" t="str">
         <v>14:00</v>
@@ -15274,10 +15274,10 @@
         <v>20:00</v>
       </c>
       <c r="G425" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H425" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I425" t="str">
         <v/>
@@ -15291,7 +15291,7 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B426" t="str">
         <v>Scrutini</v>
@@ -15300,7 +15300,7 @@
         <v>temporanea</v>
       </c>
       <c r="D426" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E426" t="str">
         <v>14:00</v>
@@ -15309,10 +15309,10 @@
         <v>20:00</v>
       </c>
       <c r="G426" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H426" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I426" t="str">
         <v/>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="427">
       <c r="A427">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B427" t="str">
         <v>Scrutini</v>
@@ -15361,7 +15361,7 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B428" t="str">
         <v>Scrutini</v>
@@ -15396,7 +15396,7 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B429" t="str">
         <v>Scrutini</v>
@@ -15431,7 +15431,7 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B430" t="str">
         <v>Scrutini</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="431">
       <c r="A431">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B431" t="str">
         <v>Scrutini</v>
@@ -15501,7 +15501,7 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B432" t="str">
         <v>Scrutini</v>
@@ -15536,7 +15536,7 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B433" t="str">
         <v>Scrutini</v>
@@ -15571,7 +15571,7 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B434" t="str">
         <v>Scrutini</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B435" t="str">
         <v>Scrutini</v>
@@ -15641,7 +15641,7 @@
     </row>
     <row r="436">
       <c r="A436">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B436" t="str">
         <v>Scrutini</v>
@@ -15676,7 +15676,7 @@
     </row>
     <row r="437">
       <c r="A437">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B437" t="str">
         <v>Scrutini</v>
@@ -15711,7 +15711,7 @@
     </row>
     <row r="438">
       <c r="A438">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B438" t="str">
         <v>Scrutini</v>
@@ -15746,7 +15746,7 @@
     </row>
     <row r="439">
       <c r="A439">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B439" t="str">
         <v>Scrutini</v>
@@ -15781,7 +15781,7 @@
     </row>
     <row r="440">
       <c r="A440">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B440" t="str">
         <v>Scrutini</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="441">
       <c r="A441">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B441" t="str">
         <v>Scrutini</v>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="442">
       <c r="A442">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B442" t="str">
         <v>Scrutini</v>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="443">
       <c r="A443">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B443" t="str">
         <v>Scrutini</v>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="444">
       <c r="A444">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B444" t="str">
         <v>Scrutini</v>
@@ -15956,7 +15956,7 @@
     </row>
     <row r="445">
       <c r="A445">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B445" t="str">
         <v>Scrutini</v>
@@ -15991,7 +15991,7 @@
     </row>
     <row r="446">
       <c r="A446">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B446" t="str">
         <v>Scrutini</v>
@@ -16026,7 +16026,7 @@
     </row>
     <row r="447">
       <c r="A447">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B447" t="str">
         <v>Scrutini</v>
@@ -16061,7 +16061,7 @@
     </row>
     <row r="448">
       <c r="A448">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B448" t="str">
         <v>Scrutini</v>
@@ -16070,7 +16070,7 @@
         <v>temporanea</v>
       </c>
       <c r="D448" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E448" t="str">
         <v>14:00</v>
@@ -16079,10 +16079,10 @@
         <v>20:00</v>
       </c>
       <c r="G448" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H448" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I448" t="str">
         <v/>
@@ -16096,7 +16096,7 @@
     </row>
     <row r="449">
       <c r="A449">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B449" t="str">
         <v>Scrutini</v>
@@ -16105,7 +16105,7 @@
         <v>temporanea</v>
       </c>
       <c r="D449" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E449" t="str">
         <v>14:00</v>
@@ -16114,10 +16114,10 @@
         <v>20:00</v>
       </c>
       <c r="G449" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H449" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I449" t="str">
         <v/>
@@ -16131,7 +16131,7 @@
     </row>
     <row r="450">
       <c r="A450">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B450" t="str">
         <v>Scrutini</v>
@@ -16140,7 +16140,7 @@
         <v>temporanea</v>
       </c>
       <c r="D450" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E450" t="str">
         <v>14:00</v>
@@ -16149,10 +16149,10 @@
         <v>20:00</v>
       </c>
       <c r="G450" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H450" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I450" t="str">
         <v/>
@@ -16166,7 +16166,7 @@
     </row>
     <row r="451">
       <c r="A451">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B451" t="str">
         <v>Scrutini</v>
@@ -16175,7 +16175,7 @@
         <v>temporanea</v>
       </c>
       <c r="D451" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E451" t="str">
         <v>14:00</v>
@@ -16184,10 +16184,10 @@
         <v>20:00</v>
       </c>
       <c r="G451" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H451" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I451" t="str">
         <v/>
@@ -16201,7 +16201,7 @@
     </row>
     <row r="452">
       <c r="A452">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B452" t="str">
         <v>Scrutini</v>
@@ -16236,7 +16236,7 @@
     </row>
     <row r="453">
       <c r="A453">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B453" t="str">
         <v>Scrutini</v>
@@ -16271,7 +16271,7 @@
     </row>
     <row r="454">
       <c r="A454">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B454" t="str">
         <v>Scrutini</v>
@@ -16306,7 +16306,7 @@
     </row>
     <row r="455">
       <c r="A455">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B455" t="str">
         <v>Scrutini</v>
@@ -16341,7 +16341,7 @@
     </row>
     <row r="456">
       <c r="A456">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B456" t="str">
         <v>Scrutini</v>
@@ -16376,7 +16376,7 @@
     </row>
     <row r="457">
       <c r="A457">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B457" t="str">
         <v>Scrutini</v>
@@ -16411,7 +16411,7 @@
     </row>
     <row r="458">
       <c r="A458">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B458" t="str">
         <v>Scrutini</v>
@@ -16446,7 +16446,7 @@
     </row>
     <row r="459">
       <c r="A459">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B459" t="str">
         <v>Scrutini</v>
@@ -16481,7 +16481,7 @@
     </row>
     <row r="460">
       <c r="A460">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B460" t="str">
         <v>Scrutini</v>
@@ -16516,7 +16516,7 @@
     </row>
     <row r="461">
       <c r="A461">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B461" t="str">
         <v>Scrutini</v>
@@ -16551,7 +16551,7 @@
     </row>
     <row r="462">
       <c r="A462">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B462" t="str">
         <v>Scrutini</v>
@@ -16586,7 +16586,7 @@
     </row>
     <row r="463">
       <c r="A463">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B463" t="str">
         <v>Scrutini</v>
@@ -16621,7 +16621,7 @@
     </row>
     <row r="464">
       <c r="A464">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B464" t="str">
         <v>Scrutini</v>
@@ -16656,7 +16656,7 @@
     </row>
     <row r="465">
       <c r="A465">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B465" t="str">
         <v>Scrutini</v>
@@ -16691,7 +16691,7 @@
     </row>
     <row r="466">
       <c r="A466">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B466" t="str">
         <v>Scrutini</v>
@@ -16726,7 +16726,7 @@
     </row>
     <row r="467">
       <c r="A467">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B467" t="str">
         <v>Scrutini</v>
@@ -16761,7 +16761,7 @@
     </row>
     <row r="468">
       <c r="A468">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B468" t="str">
         <v>Scrutini</v>
@@ -16796,7 +16796,7 @@
     </row>
     <row r="469">
       <c r="A469">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B469" t="str">
         <v>Scrutini</v>
@@ -16831,7 +16831,7 @@
     </row>
     <row r="470">
       <c r="A470">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B470" t="str">
         <v>Scrutini</v>
@@ -16866,7 +16866,7 @@
     </row>
     <row r="471">
       <c r="A471">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B471" t="str">
         <v>Scrutini</v>
@@ -16901,7 +16901,7 @@
     </row>
     <row r="472">
       <c r="A472">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B472" t="str">
         <v>Scrutini</v>
@@ -16936,28 +16936,28 @@
     </row>
     <row r="473">
       <c r="A473">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B473" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C473" t="str">
         <v>temporanea</v>
       </c>
       <c r="D473" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E473" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F473" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G473" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H473" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I473" t="str">
         <v/>
@@ -16971,28 +16971,28 @@
     </row>
     <row r="474">
       <c r="A474">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B474" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C474" t="str">
         <v>temporanea</v>
       </c>
       <c r="D474" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E474" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F474" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G474" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H474" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I474" t="str">
         <v/>
@@ -17006,28 +17006,28 @@
     </row>
     <row r="475">
       <c r="A475">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B475" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C475" t="str">
         <v>temporanea</v>
       </c>
       <c r="D475" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E475" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F475" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G475" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H475" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I475" t="str">
         <v/>
@@ -17041,28 +17041,28 @@
     </row>
     <row r="476">
       <c r="A476">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B476" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C476" t="str">
         <v>temporanea</v>
       </c>
       <c r="D476" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E476" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F476" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G476" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H476" t="str">
-        <v>2027-04-14</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I476" t="str">
         <v/>
@@ -17076,7 +17076,7 @@
     </row>
     <row r="477">
       <c r="A477">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B477" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17111,7 +17111,7 @@
     </row>
     <row r="478">
       <c r="A478">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B478" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17146,7 +17146,7 @@
     </row>
     <row r="479">
       <c r="A479">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B479" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17181,7 +17181,7 @@
     </row>
     <row r="480">
       <c r="A480">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B480" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17216,7 +17216,7 @@
     </row>
     <row r="481">
       <c r="A481">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B481" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17251,7 +17251,7 @@
     </row>
     <row r="482">
       <c r="A482">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B482" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17286,7 +17286,7 @@
     </row>
     <row r="483">
       <c r="A483">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B483" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17321,7 +17321,7 @@
     </row>
     <row r="484">
       <c r="A484">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B484" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17356,7 +17356,7 @@
     </row>
     <row r="485">
       <c r="A485">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B485" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17391,7 +17391,7 @@
     </row>
     <row r="486">
       <c r="A486">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B486" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17426,7 +17426,7 @@
     </row>
     <row r="487">
       <c r="A487">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B487" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17461,7 +17461,7 @@
     </row>
     <row r="488">
       <c r="A488">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B488" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="489">
       <c r="A489">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B489" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17531,7 +17531,7 @@
     </row>
     <row r="490">
       <c r="A490">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B490" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17566,7 +17566,7 @@
     </row>
     <row r="491">
       <c r="A491">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B491" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17601,7 +17601,7 @@
     </row>
     <row r="492">
       <c r="A492">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B492" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="493">
       <c r="A493">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B493" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17671,7 +17671,7 @@
     </row>
     <row r="494">
       <c r="A494">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B494" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17706,7 +17706,7 @@
     </row>
     <row r="495">
       <c r="A495">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B495" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17741,7 +17741,7 @@
     </row>
     <row r="496">
       <c r="A496">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B496" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17776,7 +17776,7 @@
     </row>
     <row r="497">
       <c r="A497">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B497" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17811,7 +17811,7 @@
     </row>
     <row r="498">
       <c r="A498">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B498" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17820,7 +17820,7 @@
         <v>temporanea</v>
       </c>
       <c r="D498" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E498" t="str">
         <v>15:00</v>
@@ -17829,10 +17829,10 @@
         <v>19:00</v>
       </c>
       <c r="G498" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H498" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I498" t="str">
         <v/>
@@ -17846,7 +17846,7 @@
     </row>
     <row r="499">
       <c r="A499">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B499" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17855,7 +17855,7 @@
         <v>temporanea</v>
       </c>
       <c r="D499" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E499" t="str">
         <v>15:00</v>
@@ -17864,10 +17864,10 @@
         <v>19:00</v>
       </c>
       <c r="G499" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H499" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I499" t="str">
         <v/>
@@ -17881,7 +17881,7 @@
     </row>
     <row r="500">
       <c r="A500">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B500" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17890,7 +17890,7 @@
         <v>temporanea</v>
       </c>
       <c r="D500" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E500" t="str">
         <v>15:00</v>
@@ -17899,10 +17899,10 @@
         <v>19:00</v>
       </c>
       <c r="G500" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H500" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I500" t="str">
         <v/>
@@ -17916,7 +17916,7 @@
     </row>
     <row r="501">
       <c r="A501">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B501" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17925,7 +17925,7 @@
         <v>temporanea</v>
       </c>
       <c r="D501" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E501" t="str">
         <v>15:00</v>
@@ -17934,10 +17934,10 @@
         <v>19:00</v>
       </c>
       <c r="G501" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H501" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I501" t="str">
         <v/>
@@ -17951,7 +17951,7 @@
     </row>
     <row r="502">
       <c r="A502">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B502" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17986,7 +17986,7 @@
     </row>
     <row r="503">
       <c r="A503">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B503" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18021,7 +18021,7 @@
     </row>
     <row r="504">
       <c r="A504">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B504" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18056,7 +18056,7 @@
     </row>
     <row r="505">
       <c r="A505">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B505" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18091,7 +18091,7 @@
     </row>
     <row r="506">
       <c r="A506">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B506" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18126,7 +18126,7 @@
     </row>
     <row r="507">
       <c r="A507">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B507" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18161,7 +18161,7 @@
     </row>
     <row r="508">
       <c r="A508">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B508" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18196,7 +18196,7 @@
     </row>
     <row r="509">
       <c r="A509">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B509" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="510">
       <c r="A510">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B510" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18266,7 +18266,7 @@
     </row>
     <row r="511">
       <c r="A511">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B511" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="512">
       <c r="A512">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B512" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18336,7 +18336,7 @@
     </row>
     <row r="513">
       <c r="A513">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B513" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18371,7 +18371,7 @@
     </row>
     <row r="514">
       <c r="A514">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B514" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18406,7 +18406,7 @@
     </row>
     <row r="515">
       <c r="A515">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B515" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18441,7 +18441,7 @@
     </row>
     <row r="516">
       <c r="A516">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B516" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18476,7 +18476,7 @@
     </row>
     <row r="517">
       <c r="A517">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B517" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18511,7 +18511,7 @@
     </row>
     <row r="518">
       <c r="A518">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B518" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18546,7 +18546,7 @@
     </row>
     <row r="519">
       <c r="A519">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B519" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18581,7 +18581,7 @@
     </row>
     <row r="520">
       <c r="A520">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B520" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18616,7 +18616,7 @@
     </row>
     <row r="521">
       <c r="A521">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B521" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18651,7 +18651,7 @@
     </row>
     <row r="522">
       <c r="A522">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B522" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18686,7 +18686,7 @@
     </row>
     <row r="523">
       <c r="A523">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B523" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18695,7 +18695,7 @@
         <v>temporanea</v>
       </c>
       <c r="D523" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E523" t="str">
         <v>15:00</v>
@@ -18704,10 +18704,10 @@
         <v>19:00</v>
       </c>
       <c r="G523" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H523" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I523" t="str">
         <v/>
@@ -18721,7 +18721,7 @@
     </row>
     <row r="524">
       <c r="A524">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B524" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18730,7 +18730,7 @@
         <v>temporanea</v>
       </c>
       <c r="D524" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E524" t="str">
         <v>15:00</v>
@@ -18739,10 +18739,10 @@
         <v>19:00</v>
       </c>
       <c r="G524" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H524" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I524" t="str">
         <v/>
@@ -18756,7 +18756,7 @@
     </row>
     <row r="525">
       <c r="A525">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B525" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18765,7 +18765,7 @@
         <v>temporanea</v>
       </c>
       <c r="D525" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E525" t="str">
         <v>15:00</v>
@@ -18774,10 +18774,10 @@
         <v>19:00</v>
       </c>
       <c r="G525" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H525" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I525" t="str">
         <v/>
@@ -18791,7 +18791,7 @@
     </row>
     <row r="526">
       <c r="A526">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B526" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18800,7 +18800,7 @@
         <v>temporanea</v>
       </c>
       <c r="D526" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E526" t="str">
         <v>15:00</v>
@@ -18809,10 +18809,10 @@
         <v>19:00</v>
       </c>
       <c r="G526" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H526" t="str">
-        <v>2027-04-16</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I526" t="str">
         <v/>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="527">
       <c r="A527">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B527" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="528">
       <c r="A528">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B528" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18896,7 +18896,7 @@
     </row>
     <row r="529">
       <c r="A529">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B529" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18931,7 +18931,7 @@
     </row>
     <row r="530">
       <c r="A530">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B530" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18966,7 +18966,7 @@
     </row>
     <row r="531">
       <c r="A531">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B531" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19001,7 +19001,7 @@
     </row>
     <row r="532">
       <c r="A532">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B532" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19036,7 +19036,7 @@
     </row>
     <row r="533">
       <c r="A533">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B533" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19071,7 +19071,7 @@
     </row>
     <row r="534">
       <c r="A534">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B534" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19106,7 +19106,7 @@
     </row>
     <row r="535">
       <c r="A535">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B535" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19141,7 +19141,7 @@
     </row>
     <row r="536">
       <c r="A536">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B536" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19176,7 +19176,7 @@
     </row>
     <row r="537">
       <c r="A537">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B537" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19211,7 +19211,7 @@
     </row>
     <row r="538">
       <c r="A538">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B538" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19246,7 +19246,7 @@
     </row>
     <row r="539">
       <c r="A539">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B539" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19281,7 +19281,7 @@
     </row>
     <row r="540">
       <c r="A540">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B540" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19316,7 +19316,7 @@
     </row>
     <row r="541">
       <c r="A541">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B541" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19351,7 +19351,7 @@
     </row>
     <row r="542">
       <c r="A542">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B542" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19386,7 +19386,7 @@
     </row>
     <row r="543">
       <c r="A543">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B543" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19421,7 +19421,7 @@
     </row>
     <row r="544">
       <c r="A544">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B544" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19456,7 +19456,7 @@
     </row>
     <row r="545">
       <c r="A545">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B545" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19491,7 +19491,7 @@
     </row>
     <row r="546">
       <c r="A546">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B546" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19526,7 +19526,7 @@
     </row>
     <row r="547">
       <c r="A547">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B547" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19561,28 +19561,28 @@
     </row>
     <row r="548">
       <c r="A548">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B548" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C548" t="str">
         <v>temporanea</v>
       </c>
       <c r="D548" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E548" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F548" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G548" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H548" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I548" t="str">
         <v/>
@@ -19596,28 +19596,28 @@
     </row>
     <row r="549">
       <c r="A549">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B549" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C549" t="str">
         <v>temporanea</v>
       </c>
       <c r="D549" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E549" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F549" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G549" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H549" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I549" t="str">
         <v/>
@@ -19631,28 +19631,28 @@
     </row>
     <row r="550">
       <c r="A550">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B550" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C550" t="str">
         <v>temporanea</v>
       </c>
       <c r="D550" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E550" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F550" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G550" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H550" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I550" t="str">
         <v/>
@@ -19666,28 +19666,28 @@
     </row>
     <row r="551">
       <c r="A551">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B551" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C551" t="str">
         <v>temporanea</v>
       </c>
       <c r="D551" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E551" t="str">
-        <v>09:30</v>
+        <v>15:00</v>
       </c>
       <c r="F551" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G551" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H551" t="str">
-        <v>2027-06-07</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I551" t="str">
         <v/>
@@ -19701,7 +19701,7 @@
     </row>
     <row r="552">
       <c r="A552">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B552" t="str">
         <v>Scrutini</v>
@@ -19736,7 +19736,7 @@
     </row>
     <row r="553">
       <c r="A553">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B553" t="str">
         <v>Scrutini</v>
@@ -19771,7 +19771,7 @@
     </row>
     <row r="554">
       <c r="A554">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B554" t="str">
         <v>Scrutini</v>
@@ -19806,7 +19806,7 @@
     </row>
     <row r="555">
       <c r="A555">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B555" t="str">
         <v>Scrutini</v>
@@ -19841,7 +19841,7 @@
     </row>
     <row r="556">
       <c r="A556">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B556" t="str">
         <v>Scrutini</v>
@@ -19876,7 +19876,7 @@
     </row>
     <row r="557">
       <c r="A557">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B557" t="str">
         <v>Scrutini</v>
@@ -19911,7 +19911,7 @@
     </row>
     <row r="558">
       <c r="A558">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B558" t="str">
         <v>Scrutini</v>
@@ -19946,7 +19946,7 @@
     </row>
     <row r="559">
       <c r="A559">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B559" t="str">
         <v>Scrutini</v>
@@ -19981,7 +19981,7 @@
     </row>
     <row r="560">
       <c r="A560">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B560" t="str">
         <v>Scrutini</v>
@@ -20016,7 +20016,7 @@
     </row>
     <row r="561">
       <c r="A561">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B561" t="str">
         <v>Scrutini</v>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="562">
       <c r="A562">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B562" t="str">
         <v>Scrutini</v>
@@ -20086,7 +20086,7 @@
     </row>
     <row r="563">
       <c r="A563">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B563" t="str">
         <v>Scrutini</v>
@@ -20121,7 +20121,7 @@
     </row>
     <row r="564">
       <c r="A564">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B564" t="str">
         <v>Scrutini</v>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="565">
       <c r="A565">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B565" t="str">
         <v>Scrutini</v>
@@ -20191,7 +20191,7 @@
     </row>
     <row r="566">
       <c r="A566">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B566" t="str">
         <v>Scrutini</v>
@@ -20226,7 +20226,7 @@
     </row>
     <row r="567">
       <c r="A567">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B567" t="str">
         <v>Scrutini</v>
@@ -20261,7 +20261,7 @@
     </row>
     <row r="568">
       <c r="A568">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B568" t="str">
         <v>Scrutini</v>
@@ -20296,7 +20296,7 @@
     </row>
     <row r="569">
       <c r="A569">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B569" t="str">
         <v>Scrutini</v>
@@ -20331,7 +20331,7 @@
     </row>
     <row r="570">
       <c r="A570">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B570" t="str">
         <v>Scrutini</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="571">
       <c r="A571">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B571" t="str">
         <v>Scrutini</v>
@@ -20401,7 +20401,7 @@
     </row>
     <row r="572">
       <c r="A572">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B572" t="str">
         <v>Scrutini</v>
@@ -20436,7 +20436,7 @@
     </row>
     <row r="573">
       <c r="A573">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B573" t="str">
         <v>Scrutini</v>
@@ -20445,7 +20445,7 @@
         <v>temporanea</v>
       </c>
       <c r="D573" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E573" t="str">
         <v>09:30</v>
@@ -20454,10 +20454,10 @@
         <v>17:30</v>
       </c>
       <c r="G573" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H573" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I573" t="str">
         <v/>
@@ -20471,7 +20471,7 @@
     </row>
     <row r="574">
       <c r="A574">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B574" t="str">
         <v>Scrutini</v>
@@ -20480,7 +20480,7 @@
         <v>temporanea</v>
       </c>
       <c r="D574" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E574" t="str">
         <v>09:30</v>
@@ -20489,10 +20489,10 @@
         <v>17:30</v>
       </c>
       <c r="G574" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H574" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I574" t="str">
         <v/>
@@ -20506,7 +20506,7 @@
     </row>
     <row r="575">
       <c r="A575">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B575" t="str">
         <v>Scrutini</v>
@@ -20515,7 +20515,7 @@
         <v>temporanea</v>
       </c>
       <c r="D575" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E575" t="str">
         <v>09:30</v>
@@ -20524,10 +20524,10 @@
         <v>17:30</v>
       </c>
       <c r="G575" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H575" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I575" t="str">
         <v/>
@@ -20541,7 +20541,7 @@
     </row>
     <row r="576">
       <c r="A576">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B576" t="str">
         <v>Scrutini</v>
@@ -20550,7 +20550,7 @@
         <v>temporanea</v>
       </c>
       <c r="D576" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E576" t="str">
         <v>09:30</v>
@@ -20559,10 +20559,10 @@
         <v>17:30</v>
       </c>
       <c r="G576" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H576" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I576" t="str">
         <v/>
@@ -20576,7 +20576,7 @@
     </row>
     <row r="577">
       <c r="A577">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B577" t="str">
         <v>Scrutini</v>
@@ -20611,7 +20611,7 @@
     </row>
     <row r="578">
       <c r="A578">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B578" t="str">
         <v>Scrutini</v>
@@ -20646,7 +20646,7 @@
     </row>
     <row r="579">
       <c r="A579">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B579" t="str">
         <v>Scrutini</v>
@@ -20681,7 +20681,7 @@
     </row>
     <row r="580">
       <c r="A580">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B580" t="str">
         <v>Scrutini</v>
@@ -20716,7 +20716,7 @@
     </row>
     <row r="581">
       <c r="A581">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B581" t="str">
         <v>Scrutini</v>
@@ -20751,7 +20751,7 @@
     </row>
     <row r="582">
       <c r="A582">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B582" t="str">
         <v>Scrutini</v>
@@ -20786,7 +20786,7 @@
     </row>
     <row r="583">
       <c r="A583">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B583" t="str">
         <v>Scrutini</v>
@@ -20821,7 +20821,7 @@
     </row>
     <row r="584">
       <c r="A584">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B584" t="str">
         <v>Scrutini</v>
@@ -20856,7 +20856,7 @@
     </row>
     <row r="585">
       <c r="A585">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B585" t="str">
         <v>Scrutini</v>
@@ -20891,7 +20891,7 @@
     </row>
     <row r="586">
       <c r="A586">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B586" t="str">
         <v>Scrutini</v>
@@ -20926,7 +20926,7 @@
     </row>
     <row r="587">
       <c r="A587">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B587" t="str">
         <v>Scrutini</v>
@@ -20961,7 +20961,7 @@
     </row>
     <row r="588">
       <c r="A588">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B588" t="str">
         <v>Scrutini</v>
@@ -20996,7 +20996,7 @@
     </row>
     <row r="589">
       <c r="A589">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B589" t="str">
         <v>Scrutini</v>
@@ -21031,7 +21031,7 @@
     </row>
     <row r="590">
       <c r="A590">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B590" t="str">
         <v>Scrutini</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="591">
       <c r="A591">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B591" t="str">
         <v>Scrutini</v>
@@ -21101,7 +21101,7 @@
     </row>
     <row r="592">
       <c r="A592">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B592" t="str">
         <v>Scrutini</v>
@@ -21136,7 +21136,7 @@
     </row>
     <row r="593">
       <c r="A593">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B593" t="str">
         <v>Scrutini</v>
@@ -21171,7 +21171,7 @@
     </row>
     <row r="594">
       <c r="A594">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B594" t="str">
         <v>Scrutini</v>
@@ -21206,7 +21206,7 @@
     </row>
     <row r="595">
       <c r="A595">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B595" t="str">
         <v>Scrutini</v>
@@ -21241,7 +21241,7 @@
     </row>
     <row r="596">
       <c r="A596">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B596" t="str">
         <v>Scrutini</v>
@@ -21276,7 +21276,7 @@
     </row>
     <row r="597">
       <c r="A597">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B597" t="str">
         <v>Scrutini</v>
@@ -21311,7 +21311,7 @@
     </row>
     <row r="598">
       <c r="A598">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B598" t="str">
         <v>Scrutini</v>
@@ -21320,7 +21320,7 @@
         <v>temporanea</v>
       </c>
       <c r="D598" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E598" t="str">
         <v>09:30</v>
@@ -21329,10 +21329,10 @@
         <v>17:30</v>
       </c>
       <c r="G598" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H598" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I598" t="str">
         <v/>
@@ -21346,7 +21346,7 @@
     </row>
     <row r="599">
       <c r="A599">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B599" t="str">
         <v>Scrutini</v>
@@ -21355,7 +21355,7 @@
         <v>temporanea</v>
       </c>
       <c r="D599" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E599" t="str">
         <v>09:30</v>
@@ -21364,10 +21364,10 @@
         <v>17:30</v>
       </c>
       <c r="G599" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H599" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I599" t="str">
         <v/>
@@ -21381,7 +21381,7 @@
     </row>
     <row r="600">
       <c r="A600">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B600" t="str">
         <v>Scrutini</v>
@@ -21390,7 +21390,7 @@
         <v>temporanea</v>
       </c>
       <c r="D600" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E600" t="str">
         <v>09:30</v>
@@ -21399,10 +21399,10 @@
         <v>17:30</v>
       </c>
       <c r="G600" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H600" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I600" t="str">
         <v/>
@@ -21416,7 +21416,7 @@
     </row>
     <row r="601">
       <c r="A601">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B601" t="str">
         <v>Scrutini</v>
@@ -21425,7 +21425,7 @@
         <v>temporanea</v>
       </c>
       <c r="D601" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E601" t="str">
         <v>09:30</v>
@@ -21434,10 +21434,10 @@
         <v>17:30</v>
       </c>
       <c r="G601" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H601" t="str">
-        <v>2027-06-09</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I601" t="str">
         <v/>
@@ -21451,7 +21451,7 @@
     </row>
     <row r="602">
       <c r="A602">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B602" t="str">
         <v>Scrutini</v>
@@ -21486,7 +21486,7 @@
     </row>
     <row r="603">
       <c r="A603">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B603" t="str">
         <v>Scrutini</v>
@@ -21521,7 +21521,7 @@
     </row>
     <row r="604">
       <c r="A604">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B604" t="str">
         <v>Scrutini</v>
@@ -21556,7 +21556,7 @@
     </row>
     <row r="605">
       <c r="A605">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B605" t="str">
         <v>Scrutini</v>
@@ -21591,7 +21591,7 @@
     </row>
     <row r="606">
       <c r="A606">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B606" t="str">
         <v>Scrutini</v>
@@ -21626,7 +21626,7 @@
     </row>
     <row r="607">
       <c r="A607">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B607" t="str">
         <v>Scrutini</v>
@@ -21661,7 +21661,7 @@
     </row>
     <row r="608">
       <c r="A608">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B608" t="str">
         <v>Scrutini</v>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="609">
       <c r="A609">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B609" t="str">
         <v>Scrutini</v>
@@ -21731,7 +21731,7 @@
     </row>
     <row r="610">
       <c r="A610">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B610" t="str">
         <v>Scrutini</v>
@@ -21766,7 +21766,7 @@
     </row>
     <row r="611">
       <c r="A611">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B611" t="str">
         <v>Scrutini</v>
@@ -21801,7 +21801,7 @@
     </row>
     <row r="612">
       <c r="A612">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B612" t="str">
         <v>Scrutini</v>
@@ -21836,7 +21836,7 @@
     </row>
     <row r="613">
       <c r="A613">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B613" t="str">
         <v>Scrutini</v>
@@ -21871,7 +21871,7 @@
     </row>
     <row r="614">
       <c r="A614">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B614" t="str">
         <v>Scrutini</v>
@@ -21906,7 +21906,7 @@
     </row>
     <row r="615">
       <c r="A615">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B615" t="str">
         <v>Scrutini</v>
@@ -21941,7 +21941,7 @@
     </row>
     <row r="616">
       <c r="A616">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B616" t="str">
         <v>Scrutini</v>
@@ -21976,7 +21976,7 @@
     </row>
     <row r="617">
       <c r="A617">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B617" t="str">
         <v>Scrutini</v>
@@ -22011,7 +22011,7 @@
     </row>
     <row r="618">
       <c r="A618">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B618" t="str">
         <v>Scrutini</v>
@@ -22046,7 +22046,7 @@
     </row>
     <row r="619">
       <c r="A619">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B619" t="str">
         <v>Scrutini</v>
@@ -22081,7 +22081,7 @@
     </row>
     <row r="620">
       <c r="A620">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B620" t="str">
         <v>Scrutini</v>
@@ -22116,7 +22116,7 @@
     </row>
     <row r="621">
       <c r="A621">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B621" t="str">
         <v>Scrutini</v>
@@ -22151,7 +22151,7 @@
     </row>
     <row r="622">
       <c r="A622">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B622" t="str">
         <v>Scrutini</v>
@@ -22184,9 +22184,149 @@
         <v/>
       </c>
     </row>
+    <row r="623">
+      <c r="A623">
+        <v>24</v>
+      </c>
+      <c r="B623" t="str">
+        <v>Scrutini</v>
+      </c>
+      <c r="C623" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D623" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E623" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="F623" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="G623" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="H623" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="I623" t="str">
+        <v/>
+      </c>
+      <c r="J623" t="str">
+        <v/>
+      </c>
+      <c r="K623" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624">
+        <v>25</v>
+      </c>
+      <c r="B624" t="str">
+        <v>Scrutini</v>
+      </c>
+      <c r="C624" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D624" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E624" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="F624" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="G624" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="H624" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="I624" t="str">
+        <v/>
+      </c>
+      <c r="J624" t="str">
+        <v/>
+      </c>
+      <c r="K624" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625">
+        <v>26</v>
+      </c>
+      <c r="B625" t="str">
+        <v>Scrutini</v>
+      </c>
+      <c r="C625" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D625" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E625" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="F625" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="G625" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="H625" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="I625" t="str">
+        <v/>
+      </c>
+      <c r="J625" t="str">
+        <v/>
+      </c>
+      <c r="K625" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626">
+        <v>27</v>
+      </c>
+      <c r="B626" t="str">
+        <v>Scrutini</v>
+      </c>
+      <c r="C626" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D626" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E626" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="F626" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="G626" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="H626" t="str">
+        <v>2027-06-09</v>
+      </c>
+      <c r="I626" t="str">
+        <v/>
+      </c>
+      <c r="J626" t="str">
+        <v/>
+      </c>
+      <c r="K626" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K622"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K626"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K626"/>
+  <dimension ref="A1:K620"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -7345,46 +7345,46 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="str">
-        <v/>
+      <c r="A199">
+        <v>4</v>
       </c>
       <c r="B199" t="str">
-        <v>Incontro ICARO/Pars · 3C + 3A</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C199" t="str">
         <v>temporanea</v>
       </c>
       <c r="D199" t="str">
-        <v>Venerdì</v>
+        <v>Martedì</v>
       </c>
       <c r="E199" t="str">
-        <v>08:05</v>
+        <v>14:30</v>
       </c>
       <c r="F199" t="str">
-        <v>12:10</v>
+        <v>17:00</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-10</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-11-13</v>
+        <v>2026-11-10</v>
       </c>
       <c r="I199" t="str">
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K199" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B200" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>Orientamento con psicologa (classi 3)</v>
       </c>
       <c r="C200" t="str">
         <v>temporanea</v>
@@ -7393,10 +7393,10 @@
         <v>Martedì</v>
       </c>
       <c r="E200" t="str">
-        <v>14:30</v>
+        <v>09:05</v>
       </c>
       <c r="F200" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G200" t="str">
         <v>2026-11-10</v>
@@ -7415,81 +7415,81 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="str">
-        <v/>
+      <c r="A201">
+        <v>21</v>
       </c>
       <c r="B201" t="str">
-        <v>Incontro ICARO/Pars · 3B + 3D</v>
+        <v>Continuità con classi V · laboratorio di arte · 2B + 2D</v>
       </c>
       <c r="C201" t="str">
         <v>temporanea</v>
       </c>
       <c r="D201" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E201" t="str">
-        <v>08:05</v>
+        <v>09:20</v>
       </c>
       <c r="F201" t="str">
-        <v>12:10</v>
+        <v>11:00</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-16</v>
       </c>
       <c r="I201" t="str">
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v/>
+      </c>
+      <c r="B202" t="str">
+        <v>Continuità con classi V · laboratorio di ed. fisica · 2B + 2D</v>
+      </c>
+      <c r="C202" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Lunedì</v>
+      </c>
+      <c r="E202" t="str">
+        <v>09:20</v>
+      </c>
+      <c r="F202" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2026-11-16</v>
+      </c>
+      <c r="H202" t="str">
+        <v>2026-11-16</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v>Palestra</v>
+      </c>
+      <c r="K202" t="str">
         <v>terra</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202">
-        <v>10</v>
-      </c>
-      <c r="B202" t="str">
-        <v>Orientamento con psicologa (classi 3)</v>
-      </c>
-      <c r="C202" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D202" t="str">
-        <v>Martedì</v>
-      </c>
-      <c r="E202" t="str">
-        <v>09:05</v>
-      </c>
-      <c r="F202" t="str">
-        <v>13:05</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2026-11-10</v>
-      </c>
-      <c r="H202" t="str">
-        <v>2026-11-10</v>
-      </c>
-      <c r="I202" t="str">
-        <v/>
-      </c>
-      <c r="J202" t="str">
-        <v/>
-      </c>
-      <c r="K202" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="203">
-      <c r="A203">
-        <v>21</v>
+      <c r="A203" t="str">
+        <v/>
       </c>
       <c r="B203" t="str">
-        <v>Continuità con classi V · laboratorio di arte · 2B + 2D</v>
+        <v>Continuità con classi V · saluti del Dirigente · 2B + 2D</v>
       </c>
       <c r="C203" t="str">
         <v>temporanea</v>
@@ -7498,10 +7498,10 @@
         <v>Lunedì</v>
       </c>
       <c r="E203" t="str">
-        <v>09:20</v>
+        <v>11:30</v>
       </c>
       <c r="F203" t="str">
-        <v>11:00</v>
+        <v>11:45</v>
       </c>
       <c r="G203" t="str">
         <v>2026-11-16</v>
@@ -7513,45 +7513,45 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K203" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="str">
-        <v/>
+      <c r="A204">
+        <v>3</v>
       </c>
       <c r="B204" t="str">
-        <v>Continuità con classi V · laboratorio di ed. fisica · 2B + 2D</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C204" t="str">
         <v>temporanea</v>
       </c>
       <c r="D204" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E204" t="str">
-        <v>09:20</v>
+        <v>14:30</v>
       </c>
       <c r="F204" t="str">
-        <v>11:00</v>
+        <v>17:00</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-17</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-17</v>
       </c>
       <c r="I204" t="str">
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>Palestra</v>
+        <v/>
       </c>
       <c r="K204" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -7559,25 +7559,25 @@
         <v/>
       </c>
       <c r="B205" t="str">
-        <v>Continuità con classi V · saluti del Dirigente · 2B + 2D</v>
+        <v>Progetto lotta al tabagismo · 2C</v>
       </c>
       <c r="C205" t="str">
         <v>temporanea</v>
       </c>
       <c r="D205" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E205" t="str">
-        <v>11:30</v>
+        <v>09:05</v>
       </c>
       <c r="F205" t="str">
-        <v>11:45</v>
+        <v>11:05</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-18</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-11-16</v>
+        <v>2026-11-18</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7590,38 +7590,38 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206">
-        <v>3</v>
+      <c r="A206" t="str">
+        <v/>
       </c>
       <c r="B206" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>Progetto lotta al tabagismo · 2D</v>
       </c>
       <c r="C206" t="str">
         <v>temporanea</v>
       </c>
       <c r="D206" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E206" t="str">
-        <v>14:30</v>
+        <v>11:05</v>
       </c>
       <c r="F206" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G206" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-18</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-18</v>
       </c>
       <c r="I206" t="str">
         <v/>
       </c>
       <c r="J206" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K206" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="207">
@@ -7629,13 +7629,13 @@
         <v/>
       </c>
       <c r="B207" t="str">
-        <v>Progetto lotta al tabagismo · 2C</v>
+        <v>Progetto lotta al tabagismo · 2A</v>
       </c>
       <c r="C207" t="str">
         <v>temporanea</v>
       </c>
       <c r="D207" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E207" t="str">
         <v>09:05</v>
@@ -7644,10 +7644,10 @@
         <v>11:05</v>
       </c>
       <c r="G207" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-19</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-19</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -7664,13 +7664,13 @@
         <v/>
       </c>
       <c r="B208" t="str">
-        <v>Progetto lotta al tabagismo · 2D</v>
+        <v>Progetto lotta al tabagismo · 2B</v>
       </c>
       <c r="C208" t="str">
         <v>temporanea</v>
       </c>
       <c r="D208" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E208" t="str">
         <v>11:05</v>
@@ -7679,10 +7679,10 @@
         <v>13:05</v>
       </c>
       <c r="G208" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-19</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-19</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7695,81 +7695,81 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="str">
-        <v/>
+      <c r="A209">
+        <v>4</v>
       </c>
       <c r="B209" t="str">
-        <v>Progetto lotta al tabagismo · 2A</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C209" t="str">
         <v>temporanea</v>
       </c>
       <c r="D209" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E209" t="str">
-        <v>09:05</v>
+        <v>14:30</v>
       </c>
       <c r="F209" t="str">
-        <v>11:05</v>
+        <v>17:00</v>
       </c>
       <c r="G209" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-17</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-17</v>
       </c>
       <c r="I209" t="str">
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K209" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="str">
-        <v/>
+      <c r="A210">
+        <v>21</v>
       </c>
       <c r="B210" t="str">
-        <v>Progetto lotta al tabagismo · 2B</v>
+        <v>PN Arte</v>
       </c>
       <c r="C210" t="str">
         <v>temporanea</v>
       </c>
       <c r="D210" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E210" t="str">
-        <v>11:05</v>
+        <v>14:00</v>
       </c>
       <c r="F210" t="str">
-        <v>13:05</v>
+        <v>18:00</v>
       </c>
       <c r="G210" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-18</v>
       </c>
       <c r="I210" t="str">
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K210" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B211" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>Orientamento con psicologa (classi 3)</v>
       </c>
       <c r="C211" t="str">
         <v>temporanea</v>
@@ -7778,10 +7778,10 @@
         <v>Martedì</v>
       </c>
       <c r="E211" t="str">
-        <v>14:30</v>
+        <v>09:05</v>
       </c>
       <c r="F211" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G211" t="str">
         <v>2026-11-17</v>
@@ -7801,28 +7801,28 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B212" t="str">
-        <v>PN Arte</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C212" t="str">
         <v>temporanea</v>
       </c>
       <c r="D212" t="str">
-        <v>Mercoledì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E212" t="str">
-        <v>14:00</v>
+        <v>08:30</v>
       </c>
       <c r="F212" t="str">
-        <v>18:00</v>
+        <v>13:00</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-23</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-11-18</v>
+        <v>2026-11-23</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -7836,10 +7836,10 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B213" t="str">
-        <v>Orientamento con psicologa (classi 3)</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C213" t="str">
         <v>temporanea</v>
@@ -7848,16 +7848,16 @@
         <v>Martedì</v>
       </c>
       <c r="E213" t="str">
-        <v>09:05</v>
+        <v>14:30</v>
       </c>
       <c r="F213" t="str">
-        <v>13:05</v>
+        <v>17:00</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-11-17</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -7874,25 +7874,25 @@
         <v>1</v>
       </c>
       <c r="B214" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C214" t="str">
         <v>temporanea</v>
       </c>
       <c r="D214" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E214" t="str">
-        <v>08:30</v>
+        <v>13:05</v>
       </c>
       <c r="F214" t="str">
-        <v>13:00</v>
+        <v>15:35</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7905,38 +7905,38 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215">
-        <v>3</v>
+      <c r="A215" t="str">
+        <v/>
       </c>
       <c r="B215" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>Progetto lettura: Pinocchio (classi 1 e 2)</v>
       </c>
       <c r="C215" t="str">
         <v>temporanea</v>
       </c>
       <c r="D215" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E215" t="str">
-        <v>14:30</v>
+        <v>08:05</v>
       </c>
       <c r="F215" t="str">
-        <v>17:00</v>
+        <v>13:05</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-26</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-11-24</v>
+        <v>2026-11-26</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K215" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="216">
@@ -7944,25 +7944,25 @@
         <v>1</v>
       </c>
       <c r="B216" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C216" t="str">
         <v>temporanea</v>
       </c>
       <c r="D216" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E216" t="str">
-        <v>13:05</v>
+        <v>08:30</v>
       </c>
       <c r="F216" t="str">
-        <v>15:35</v>
+        <v>13:00</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-27</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-11-25</v>
+        <v>2026-11-27</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7979,25 +7979,25 @@
         <v/>
       </c>
       <c r="B217" t="str">
-        <v>Progetto lettura: Pinocchio (classi 1 e 2)</v>
+        <v>Open day</v>
       </c>
       <c r="C217" t="str">
         <v>temporanea</v>
       </c>
       <c r="D217" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E217" t="str">
-        <v>08:05</v>
+        <v>17:30</v>
       </c>
       <c r="F217" t="str">
-        <v>13:05</v>
+        <v>19:30</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-23</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-23</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -8011,28 +8011,28 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B218" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C218" t="str">
         <v>temporanea</v>
       </c>
       <c r="D218" t="str">
-        <v>Venerdì</v>
+        <v>Martedì</v>
       </c>
       <c r="E218" t="str">
-        <v>08:30</v>
+        <v>14:30</v>
       </c>
       <c r="F218" t="str">
-        <v>13:00</v>
+        <v>17:00</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-11-27</v>
+        <v>2026-11-24</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -8045,46 +8045,46 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="str">
-        <v/>
+      <c r="A219">
+        <v>21</v>
       </c>
       <c r="B219" t="str">
-        <v>Open day</v>
+        <v>PN Arte</v>
       </c>
       <c r="C219" t="str">
         <v>temporanea</v>
       </c>
       <c r="D219" t="str">
-        <v>Lunedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E219" t="str">
-        <v>17:30</v>
+        <v>14:00</v>
       </c>
       <c r="F219" t="str">
-        <v>19:30</v>
+        <v>18:00</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-25</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-25</v>
       </c>
       <c r="I219" t="str">
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K219" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B220" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C220" t="str">
         <v>temporanea</v>
@@ -8093,10 +8093,10 @@
         <v>Martedì</v>
       </c>
       <c r="E220" t="str">
-        <v>14:30</v>
+        <v>08:30</v>
       </c>
       <c r="F220" t="str">
-        <v>17:00</v>
+        <v>13:00</v>
       </c>
       <c r="G220" t="str">
         <v>2026-11-24</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B221" t="str">
-        <v>PN Arte</v>
+        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
       </c>
       <c r="C221" t="str">
         <v>temporanea</v>
@@ -8128,10 +8128,10 @@
         <v>Mercoledì</v>
       </c>
       <c r="E221" t="str">
-        <v>14:00</v>
+        <v>08:30</v>
       </c>
       <c r="F221" t="str">
-        <v>18:00</v>
+        <v>13:00</v>
       </c>
       <c r="G221" t="str">
         <v>2026-11-25</v>
@@ -8151,10 +8151,10 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B222" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C222" t="str">
         <v>temporanea</v>
@@ -8163,16 +8163,16 @@
         <v>Martedì</v>
       </c>
       <c r="E222" t="str">
-        <v>08:30</v>
+        <v>14:30</v>
       </c>
       <c r="F222" t="str">
-        <v>13:00</v>
+        <v>17:00</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-11-24</v>
+        <v>2026-12-01</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-11-24</v>
+        <v>2026-12-01</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -8189,7 +8189,7 @@
         <v>1</v>
       </c>
       <c r="B223" t="str">
-        <v>Orientamento: laboratori scuole secondarie (classi 3)</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C223" t="str">
         <v>temporanea</v>
@@ -8198,16 +8198,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E223" t="str">
-        <v>08:30</v>
+        <v>13:05</v>
       </c>
       <c r="F223" t="str">
-        <v>13:00</v>
+        <v>15:35</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-11-25</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-11-25</v>
+        <v>2026-12-02</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -8221,28 +8221,28 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B224" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C224" t="str">
         <v>temporanea</v>
       </c>
       <c r="D224" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E224" t="str">
-        <v>14:30</v>
+        <v>14:00</v>
       </c>
       <c r="F224" t="str">
-        <v>17:00</v>
+        <v>20:00</v>
       </c>
       <c r="G224" t="str">
-        <v>2026-12-01</v>
+        <v>2026-12-03</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-12-01</v>
+        <v>2026-12-03</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -8256,28 +8256,28 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B225" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C225" t="str">
         <v>temporanea</v>
       </c>
       <c r="D225" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E225" t="str">
-        <v>13:05</v>
+        <v>14:00</v>
       </c>
       <c r="F225" t="str">
-        <v>15:35</v>
+        <v>20:00</v>
       </c>
       <c r="G225" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-04</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-04</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8291,28 +8291,28 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B226" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C226" t="str">
         <v>temporanea</v>
       </c>
       <c r="D226" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E226" t="str">
-        <v>14:00</v>
+        <v>14:30</v>
       </c>
       <c r="F226" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-12-03</v>
+        <v>2026-12-01</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-12-03</v>
+        <v>2026-12-01</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -8335,7 +8335,7 @@
         <v>temporanea</v>
       </c>
       <c r="D227" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E227" t="str">
         <v>14:00</v>
@@ -8344,10 +8344,10 @@
         <v>20:00</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-12-04</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-12-04</v>
+        <v>2026-12-02</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8361,28 +8361,28 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B228" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Arte</v>
       </c>
       <c r="C228" t="str">
         <v>temporanea</v>
       </c>
       <c r="D228" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E228" t="str">
-        <v>14:30</v>
+        <v>14:00</v>
       </c>
       <c r="F228" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-12-01</v>
+        <v>2026-12-02</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-12-01</v>
+        <v>2026-12-02</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B229" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>PN Orchestra / Coro</v>
       </c>
       <c r="C229" t="str">
         <v>temporanea</v>
@@ -8408,16 +8408,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E229" t="str">
-        <v>14:00</v>
+        <v>13:05</v>
       </c>
       <c r="F229" t="str">
-        <v>20:00</v>
+        <v>15:35</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8431,28 +8431,28 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B230" t="str">
-        <v>PN Arte</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C230" t="str">
         <v>temporanea</v>
       </c>
       <c r="D230" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E230" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F230" t="str">
-        <v>18:00</v>
+        <v>19:00</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-12-02</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8466,28 +8466,28 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B231" t="str">
-        <v>PN Orchestra / Coro</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C231" t="str">
         <v>temporanea</v>
       </c>
       <c r="D231" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E231" t="str">
-        <v>13:05</v>
+        <v>14:30</v>
       </c>
       <c r="F231" t="str">
-        <v>15:35</v>
+        <v>17:00</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
         <v>temporanea</v>
       </c>
       <c r="D232" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E232" t="str">
         <v>15:00</v>
@@ -8519,10 +8519,10 @@
         <v>19:00</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="233">
       <c r="A233">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B233" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C233" t="str">
         <v>temporanea</v>
@@ -8580,7 +8580,7 @@
         <v>temporanea</v>
       </c>
       <c r="D234" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E234" t="str">
         <v>15:00</v>
@@ -8589,10 +8589,10 @@
         <v>19:00</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8606,16 +8606,16 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B235" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>PN Key for Schools · classi 2</v>
       </c>
       <c r="C235" t="str">
         <v>temporanea</v>
       </c>
       <c r="D235" t="str">
-        <v>Venerdì</v>
+        <v>Martedì</v>
       </c>
       <c r="E235" t="str">
         <v>14:30</v>
@@ -8624,10 +8624,10 @@
         <v>17:00</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-15</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-15</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8644,25 +8644,25 @@
         <v>2</v>
       </c>
       <c r="B236" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe · classi 3</v>
       </c>
       <c r="C236" t="str">
         <v>temporanea</v>
       </c>
       <c r="D236" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E236" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F236" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-16</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-16</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B237" t="str">
-        <v>PN Key for Schools · classi 2</v>
+        <v>PN Key for Schools · classi 3</v>
       </c>
       <c r="C237" t="str">
         <v>temporanea</v>
@@ -8710,38 +8710,38 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238">
-        <v>2</v>
+      <c r="A238" t="str">
+        <v/>
       </c>
       <c r="B238" t="str">
-        <v>Consigli di classe · classi 3</v>
+        <v>Incontro ICARO/Pars · docenti</v>
       </c>
       <c r="C238" t="str">
         <v>temporanea</v>
       </c>
       <c r="D238" t="str">
-        <v>Mercoledì</v>
+        <v>Martedì</v>
       </c>
       <c r="E238" t="str">
-        <v>14:00</v>
+        <v>14:30</v>
       </c>
       <c r="F238" t="str">
-        <v>20:00</v>
+        <v>16:30</v>
       </c>
       <c r="G238" t="str">
-        <v>2026-12-16</v>
+        <v>2027-01-12</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-12-16</v>
+        <v>2027-01-12</v>
       </c>
       <c r="I238" t="str">
         <v/>
       </c>
       <c r="J238" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K238" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="239">
@@ -8749,7 +8749,7 @@
         <v/>
       </c>
       <c r="B239" t="str">
-        <v>Incontro ICARO/Pars · 3D + 3B</v>
+        <v>Incontro ICARO/Pars · genitori</v>
       </c>
       <c r="C239" t="str">
         <v>temporanea</v>
@@ -8758,16 +8758,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E239" t="str">
-        <v>08:05</v>
+        <v>18:00</v>
       </c>
       <c r="F239" t="str">
-        <v>12:10</v>
+        <v>20:00</v>
       </c>
       <c r="G239" t="str">
-        <v>2026-12-17</v>
+        <v>2027-01-14</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-12-17</v>
+        <v>2027-01-14</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -8784,25 +8784,25 @@
         <v/>
       </c>
       <c r="B240" t="str">
-        <v>Incontro ICARO/Pars · 3A + 3C</v>
+        <v>Open day</v>
       </c>
       <c r="C240" t="str">
         <v>temporanea</v>
       </c>
       <c r="D240" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E240" t="str">
-        <v>08:05</v>
+        <v>17:30</v>
       </c>
       <c r="F240" t="str">
-        <v>12:10</v>
+        <v>19:30</v>
       </c>
       <c r="G240" t="str">
-        <v>2026-12-18</v>
+        <v>2027-01-18</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-12-18</v>
+        <v>2027-01-18</v>
       </c>
       <c r="I240" t="str">
         <v/>
@@ -8815,11 +8815,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241">
-        <v>4</v>
+      <c r="A241" t="str">
+        <v/>
       </c>
       <c r="B241" t="str">
-        <v>PN Key for Schools · classi 3</v>
+        <v>Incontro ICARO/Pars · docenti</v>
       </c>
       <c r="C241" t="str">
         <v>temporanea</v>
@@ -8831,65 +8831,65 @@
         <v>14:30</v>
       </c>
       <c r="F241" t="str">
-        <v>17:00</v>
+        <v>16:30</v>
       </c>
       <c r="G241" t="str">
-        <v>2026-12-15</v>
+        <v>2027-01-19</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-12-15</v>
+        <v>2027-01-19</v>
       </c>
       <c r="I241" t="str">
         <v/>
       </c>
       <c r="J241" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K241" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="str">
-        <v/>
+      <c r="A242">
+        <v>2</v>
       </c>
       <c r="B242" t="str">
-        <v>Incontro ICARO/Pars · docenti</v>
+        <v>Scrutini</v>
       </c>
       <c r="C242" t="str">
         <v>temporanea</v>
       </c>
       <c r="D242" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E242" t="str">
-        <v>14:30</v>
+        <v>14:00</v>
       </c>
       <c r="F242" t="str">
-        <v>16:30</v>
+        <v>20:00</v>
       </c>
       <c r="G242" t="str">
-        <v>2027-01-12</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H242" t="str">
-        <v>2027-01-12</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I242" t="str">
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K242" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="str">
-        <v/>
+      <c r="A243">
+        <v>2</v>
       </c>
       <c r="B243" t="str">
-        <v>Incontro ICARO/Pars · genitori</v>
+        <v>Scrutini</v>
       </c>
       <c r="C243" t="str">
         <v>temporanea</v>
@@ -8898,121 +8898,121 @@
         <v>Giovedì</v>
       </c>
       <c r="E243" t="str">
-        <v>18:00</v>
+        <v>14:00</v>
       </c>
       <c r="F243" t="str">
         <v>20:00</v>
       </c>
       <c r="G243" t="str">
-        <v>2027-01-14</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H243" t="str">
-        <v>2027-01-14</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I243" t="str">
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K243" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="str">
-        <v/>
+      <c r="A244">
+        <v>2</v>
       </c>
       <c r="B244" t="str">
-        <v>Open day</v>
+        <v>Scrutini</v>
       </c>
       <c r="C244" t="str">
         <v>temporanea</v>
       </c>
       <c r="D244" t="str">
+        <v>Venerdì</v>
+      </c>
+      <c r="E244" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="F244" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="G244" t="str">
+        <v>2027-02-05</v>
+      </c>
+      <c r="H244" t="str">
+        <v>2027-02-05</v>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" t="str">
+        <v/>
+      </c>
+      <c r="K244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>4</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Dip. verticale umanistico</v>
+      </c>
+      <c r="C245" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D245" t="str">
         <v>Lunedì</v>
       </c>
-      <c r="E244" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="F244" t="str">
-        <v>19:30</v>
-      </c>
-      <c r="G244" t="str">
-        <v>2027-01-18</v>
-      </c>
-      <c r="H244" t="str">
-        <v>2027-01-18</v>
-      </c>
-      <c r="I244" t="str">
-        <v/>
-      </c>
-      <c r="J244" t="str">
-        <v>Auditorium</v>
-      </c>
-      <c r="K244" t="str">
-        <v>terra</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v/>
-      </c>
-      <c r="B245" t="str">
-        <v>Incontro ICARO/Pars · docenti</v>
-      </c>
-      <c r="C245" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D245" t="str">
-        <v>Martedì</v>
-      </c>
       <c r="E245" t="str">
-        <v>14:30</v>
+        <v>16:45</v>
       </c>
       <c r="F245" t="str">
-        <v>16:30</v>
+        <v>18:45</v>
       </c>
       <c r="G245" t="str">
-        <v>2027-01-19</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H245" t="str">
-        <v>2027-01-19</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K245" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B246" t="str">
-        <v>Scrutini</v>
+        <v>Dip. verticale matematico-scientifico</v>
       </c>
       <c r="C246" t="str">
         <v>temporanea</v>
       </c>
       <c r="D246" t="str">
-        <v>Mercoledì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E246" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F246" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G246" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H246" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I246" t="str">
         <v/>
@@ -9026,28 +9026,28 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B247" t="str">
-        <v>Scrutini</v>
+        <v>Dip. verticale linguistico</v>
       </c>
       <c r="C247" t="str">
         <v>temporanea</v>
       </c>
       <c r="D247" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E247" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F247" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G247" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H247" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -9061,28 +9061,28 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B248" t="str">
-        <v>Scrutini</v>
+        <v>Dip. verticale artistico-motorio + musicale</v>
       </c>
       <c r="C248" t="str">
         <v>temporanea</v>
       </c>
       <c r="D248" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E248" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F248" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G248" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-15</v>
       </c>
       <c r="H248" t="str">
-        <v>2027-02-05</v>
+        <v>2027-02-15</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -9095,11 +9095,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249">
-        <v>4</v>
+      <c r="A249" t="str">
+        <v/>
       </c>
       <c r="B249" t="str">
-        <v>Dip. verticale umanistico</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C249" t="str">
         <v>temporanea</v>
@@ -9108,51 +9108,51 @@
         <v>Lunedì</v>
       </c>
       <c r="E249" t="str">
-        <v>16:45</v>
+        <v>17:00</v>
       </c>
       <c r="F249" t="str">
-        <v>18:45</v>
+        <v>19:00</v>
       </c>
       <c r="G249" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-15</v>
       </c>
       <c r="H249" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-15</v>
       </c>
       <c r="I249" t="str">
         <v/>
       </c>
       <c r="J249" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K249" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B250" t="str">
-        <v>Dip. verticale matematico-scientifico</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C250" t="str">
         <v>temporanea</v>
       </c>
       <c r="D250" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E250" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F250" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G250" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-16</v>
       </c>
       <c r="H250" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-16</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -9166,28 +9166,28 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B251" t="str">
-        <v>Dip. verticale linguistico</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C251" t="str">
         <v>temporanea</v>
       </c>
       <c r="D251" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E251" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F251" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G251" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-18</v>
       </c>
       <c r="H251" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-18</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -9201,28 +9201,28 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B252" t="str">
-        <v>Dip. verticale artistico-motorio + musicale</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C252" t="str">
         <v>temporanea</v>
       </c>
       <c r="D252" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E252" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F252" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G252" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-19</v>
       </c>
       <c r="H252" t="str">
-        <v>2027-02-15</v>
+        <v>2027-03-19</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -9239,25 +9239,25 @@
         <v/>
       </c>
       <c r="B253" t="str">
-        <v>Incontro ICARO/Pars · 3B + 3D</v>
+        <v>Spettacolo teatrale in lingua inglese</v>
       </c>
       <c r="C253" t="str">
         <v>temporanea</v>
       </c>
       <c r="D253" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E253" t="str">
         <v>08:05</v>
       </c>
       <c r="F253" t="str">
-        <v>12:10</v>
+        <v>13:05</v>
       </c>
       <c r="G253" t="str">
-        <v>2027-02-17</v>
+        <v>2027-03-18</v>
       </c>
       <c r="H253" t="str">
-        <v>2027-02-17</v>
+        <v>2027-03-18</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -9270,73 +9270,73 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="str">
-        <v/>
+      <c r="A254">
+        <v>2</v>
       </c>
       <c r="B254" t="str">
-        <v>Incontro ICARO/Pars · 3C + 3A</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C254" t="str">
         <v>temporanea</v>
       </c>
       <c r="D254" t="str">
+        <v>Mercoledì</v>
+      </c>
+      <c r="E254" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="F254" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="G254" t="str">
+        <v>2027-04-14</v>
+      </c>
+      <c r="H254" t="str">
+        <v>2027-04-14</v>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
+      <c r="K254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>2</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Colloqui con le famiglie</v>
+      </c>
+      <c r="C255" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D255" t="str">
         <v>Giovedì</v>
       </c>
-      <c r="E254" t="str">
-        <v>08:05</v>
-      </c>
-      <c r="F254" t="str">
-        <v>12:10</v>
-      </c>
-      <c r="G254" t="str">
-        <v>2027-02-18</v>
-      </c>
-      <c r="H254" t="str">
-        <v>2027-02-18</v>
-      </c>
-      <c r="I254" t="str">
-        <v/>
-      </c>
-      <c r="J254" t="str">
-        <v>Auditorium</v>
-      </c>
-      <c r="K254" t="str">
-        <v>terra</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v/>
-      </c>
-      <c r="B255" t="str">
-        <v>Collegio docenti</v>
-      </c>
-      <c r="C255" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D255" t="str">
-        <v>Lunedì</v>
-      </c>
       <c r="E255" t="str">
-        <v>17:00</v>
+        <v>15:00</v>
       </c>
       <c r="F255" t="str">
         <v>19:00</v>
       </c>
       <c r="G255" t="str">
-        <v>2027-03-15</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H255" t="str">
-        <v>2027-03-15</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I255" t="str">
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K255" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="256">
@@ -9344,25 +9344,25 @@
         <v>2</v>
       </c>
       <c r="B256" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C256" t="str">
         <v>temporanea</v>
       </c>
       <c r="D256" t="str">
-        <v>Martedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E256" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F256" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G256" t="str">
-        <v>2027-03-16</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H256" t="str">
-        <v>2027-03-16</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9376,28 +9376,28 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B257" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C257" t="str">
         <v>temporanea</v>
       </c>
       <c r="D257" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E257" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F257" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G257" t="str">
-        <v>2027-03-18</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H257" t="str">
-        <v>2027-03-18</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9411,28 +9411,28 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B258" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C258" t="str">
         <v>temporanea</v>
       </c>
       <c r="D258" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E258" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F258" t="str">
-        <v>20:00</v>
+        <v>17:00</v>
       </c>
       <c r="G258" t="str">
-        <v>2027-03-19</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H258" t="str">
-        <v>2027-03-19</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9445,46 +9445,46 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="str">
-        <v/>
+      <c r="A259">
+        <v>3</v>
       </c>
       <c r="B259" t="str">
-        <v>Spettacolo teatrale in lingua inglese</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C259" t="str">
         <v>temporanea</v>
       </c>
       <c r="D259" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E259" t="str">
-        <v>08:05</v>
+        <v>16:00</v>
       </c>
       <c r="F259" t="str">
-        <v>13:05</v>
+        <v>17:00</v>
       </c>
       <c r="G259" t="str">
-        <v>2027-03-18</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H259" t="str">
-        <v>2027-03-18</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I259" t="str">
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K259" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B260" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C260" t="str">
         <v>temporanea</v>
@@ -9493,16 +9493,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E260" t="str">
-        <v>15:00</v>
+        <v>16:00</v>
       </c>
       <c r="F260" t="str">
-        <v>19:00</v>
+        <v>17:00</v>
       </c>
       <c r="G260" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-21</v>
       </c>
       <c r="H260" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-21</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9519,25 +9519,25 @@
         <v>2</v>
       </c>
       <c r="B261" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C261" t="str">
         <v>temporanea</v>
       </c>
       <c r="D261" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E261" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F261" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G261" t="str">
-        <v>2027-04-15</v>
+        <v>2027-05-05</v>
       </c>
       <c r="H261" t="str">
-        <v>2027-04-15</v>
+        <v>2027-05-05</v>
       </c>
       <c r="I261" t="str">
         <v/>
@@ -9554,25 +9554,25 @@
         <v>2</v>
       </c>
       <c r="B262" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C262" t="str">
         <v>temporanea</v>
       </c>
       <c r="D262" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E262" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F262" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G262" t="str">
-        <v>2027-04-16</v>
+        <v>2027-05-06</v>
       </c>
       <c r="H262" t="str">
-        <v>2027-04-16</v>
+        <v>2027-05-06</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9586,28 +9586,28 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B263" t="str">
-        <v>Dip. umanistico</v>
+        <v>Consigli di classe con genitori</v>
       </c>
       <c r="C263" t="str">
         <v>temporanea</v>
       </c>
       <c r="D263" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E263" t="str">
-        <v>16:00</v>
+        <v>14:00</v>
       </c>
       <c r="F263" t="str">
-        <v>17:00</v>
+        <v>20:00</v>
       </c>
       <c r="G263" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-07</v>
       </c>
       <c r="H263" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-07</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B264" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C264" t="str">
         <v>temporanea</v>
@@ -9636,13 +9636,13 @@
         <v>16:00</v>
       </c>
       <c r="F264" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="G264" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H264" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9656,10 +9656,10 @@
     </row>
     <row r="265">
       <c r="A265">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B265" t="str">
-        <v>Dip. linguistico</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C265" t="str">
         <v>temporanea</v>
@@ -9671,13 +9671,13 @@
         <v>16:00</v>
       </c>
       <c r="F265" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="G265" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H265" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B266" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C266" t="str">
         <v>temporanea</v>
@@ -9706,13 +9706,13 @@
         <v>16:00</v>
       </c>
       <c r="F266" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="G266" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H266" t="str">
-        <v>2027-04-21</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I266" t="str">
         <v/>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B267" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C267" t="str">
         <v>temporanea</v>
@@ -9738,16 +9738,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E267" t="str">
-        <v>14:00</v>
+        <v>16:00</v>
       </c>
       <c r="F267" t="str">
-        <v>20:00</v>
+        <v>18:00</v>
       </c>
       <c r="G267" t="str">
-        <v>2027-05-05</v>
+        <v>2027-05-12</v>
       </c>
       <c r="H267" t="str">
-        <v>2027-05-05</v>
+        <v>2027-05-12</v>
       </c>
       <c r="I267" t="str">
         <v/>
@@ -9760,11 +9760,11 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268">
-        <v>2</v>
+      <c r="A268" t="str">
+        <v/>
       </c>
       <c r="B268" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C268" t="str">
         <v>temporanea</v>
@@ -9773,51 +9773,51 @@
         <v>Giovedì</v>
       </c>
       <c r="E268" t="str">
-        <v>14:00</v>
+        <v>17:00</v>
       </c>
       <c r="F268" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G268" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-13</v>
       </c>
       <c r="H268" t="str">
-        <v>2027-05-06</v>
+        <v>2027-05-13</v>
       </c>
       <c r="I268" t="str">
         <v/>
       </c>
       <c r="J268" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K268" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B269" t="str">
-        <v>Consigli di classe con genitori</v>
+        <v>Dip. verticale umanistico</v>
       </c>
       <c r="C269" t="str">
         <v>temporanea</v>
       </c>
       <c r="D269" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E269" t="str">
-        <v>14:00</v>
+        <v>16:45</v>
       </c>
       <c r="F269" t="str">
-        <v>20:00</v>
+        <v>18:45</v>
       </c>
       <c r="G269" t="str">
-        <v>2027-05-07</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H269" t="str">
-        <v>2027-05-07</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I269" t="str">
         <v/>
@@ -9831,10 +9831,10 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B270" t="str">
-        <v>Dip. umanistico</v>
+        <v>Dip. verticale matematico-scientifico</v>
       </c>
       <c r="C270" t="str">
         <v>temporanea</v>
@@ -9843,16 +9843,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E270" t="str">
-        <v>16:00</v>
+        <v>16:45</v>
       </c>
       <c r="F270" t="str">
-        <v>18:00</v>
+        <v>18:45</v>
       </c>
       <c r="G270" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H270" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I270" t="str">
         <v/>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B271" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Dip. verticale linguistico</v>
       </c>
       <c r="C271" t="str">
         <v>temporanea</v>
@@ -9878,16 +9878,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E271" t="str">
-        <v>16:00</v>
+        <v>16:45</v>
       </c>
       <c r="F271" t="str">
-        <v>18:00</v>
+        <v>18:45</v>
       </c>
       <c r="G271" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H271" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B272" t="str">
-        <v>Dip. linguistico</v>
+        <v>Dip. verticale artistico-motorio + musicale</v>
       </c>
       <c r="C272" t="str">
         <v>temporanea</v>
@@ -9913,16 +9913,16 @@
         <v>Mercoledì</v>
       </c>
       <c r="E272" t="str">
-        <v>16:00</v>
+        <v>16:45</v>
       </c>
       <c r="F272" t="str">
-        <v>18:00</v>
+        <v>18:45</v>
       </c>
       <c r="G272" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="H272" t="str">
-        <v>2027-05-12</v>
+        <v>2027-05-19</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9936,98 +9936,98 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B273" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Consigli di classe</v>
       </c>
       <c r="C273" t="str">
         <v>temporanea</v>
       </c>
       <c r="D273" t="str">
+        <v>Martedì</v>
+      </c>
+      <c r="E273" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="F273" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="G273" t="str">
+        <v>2027-05-25</v>
+      </c>
+      <c r="H273" t="str">
+        <v>2027-05-25</v>
+      </c>
+      <c r="I273" t="str">
+        <v/>
+      </c>
+      <c r="J273" t="str">
+        <v/>
+      </c>
+      <c r="K273" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>2</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Consigli di classe</v>
+      </c>
+      <c r="C274" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D274" t="str">
         <v>Mercoledì</v>
       </c>
-      <c r="E273" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="F273" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="G273" t="str">
-        <v>2027-05-12</v>
-      </c>
-      <c r="H273" t="str">
-        <v>2027-05-12</v>
-      </c>
-      <c r="I273" t="str">
-        <v/>
-      </c>
-      <c r="J273" t="str">
-        <v/>
-      </c>
-      <c r="K273" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v/>
-      </c>
-      <c r="B274" t="str">
-        <v>Collegio docenti</v>
-      </c>
-      <c r="C274" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D274" t="str">
-        <v>Giovedì</v>
-      </c>
       <c r="E274" t="str">
-        <v>17:00</v>
+        <v>14:00</v>
       </c>
       <c r="F274" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G274" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-26</v>
       </c>
       <c r="H274" t="str">
-        <v>2027-05-13</v>
+        <v>2027-05-26</v>
       </c>
       <c r="I274" t="str">
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K274" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B275" t="str">
-        <v>Dip. verticale umanistico</v>
+        <v>Consigli di classe</v>
       </c>
       <c r="C275" t="str">
         <v>temporanea</v>
       </c>
       <c r="D275" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E275" t="str">
-        <v>16:45</v>
+        <v>14:00</v>
       </c>
       <c r="F275" t="str">
-        <v>18:45</v>
+        <v>20:00</v>
       </c>
       <c r="G275" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-27</v>
       </c>
       <c r="H275" t="str">
-        <v>2027-05-19</v>
+        <v>2027-05-27</v>
       </c>
       <c r="I275" t="str">
         <v/>
@@ -10041,28 +10041,28 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B276" t="str">
-        <v>Dip. verticale matematico-scientifico</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C276" t="str">
         <v>temporanea</v>
       </c>
       <c r="D276" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E276" t="str">
-        <v>16:45</v>
+        <v>16:30</v>
       </c>
       <c r="F276" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G276" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H276" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I276" t="str">
         <v/>
@@ -10076,28 +10076,28 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B277" t="str">
-        <v>Dip. verticale linguistico</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C277" t="str">
         <v>temporanea</v>
       </c>
       <c r="D277" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E277" t="str">
-        <v>16:45</v>
+        <v>16:30</v>
       </c>
       <c r="F277" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G277" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H277" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -10111,28 +10111,28 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B278" t="str">
-        <v>Dip. verticale artistico-motorio + musicale</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C278" t="str">
         <v>temporanea</v>
       </c>
       <c r="D278" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E278" t="str">
-        <v>16:45</v>
+        <v>16:30</v>
       </c>
       <c r="F278" t="str">
-        <v>18:45</v>
+        <v>18:00</v>
       </c>
       <c r="G278" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H278" t="str">
-        <v>2027-05-19</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -10146,28 +10146,28 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B279" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C279" t="str">
         <v>temporanea</v>
       </c>
       <c r="D279" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E279" t="str">
-        <v>14:00</v>
+        <v>16:30</v>
       </c>
       <c r="F279" t="str">
-        <v>20:00</v>
+        <v>18:00</v>
       </c>
       <c r="G279" t="str">
-        <v>2027-05-25</v>
+        <v>2027-06-03</v>
       </c>
       <c r="H279" t="str">
-        <v>2027-05-25</v>
+        <v>2027-06-03</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -10181,28 +10181,28 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B280" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C280" t="str">
         <v>temporanea</v>
       </c>
       <c r="D280" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E280" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F280" t="str">
-        <v>20:00</v>
+        <v>16:30</v>
       </c>
       <c r="G280" t="str">
-        <v>2027-05-26</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H280" t="str">
-        <v>2027-05-26</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -10216,28 +10216,28 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B281" t="str">
-        <v>Consigli di classe</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C281" t="str">
         <v>temporanea</v>
       </c>
       <c r="D281" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E281" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F281" t="str">
-        <v>20:00</v>
+        <v>16:30</v>
       </c>
       <c r="G281" t="str">
-        <v>2027-05-27</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H281" t="str">
-        <v>2027-05-27</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -10251,28 +10251,28 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B282" t="str">
-        <v>Dip. umanistico</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C282" t="str">
         <v>temporanea</v>
       </c>
       <c r="D282" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E282" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="F282" t="str">
         <v>16:30</v>
       </c>
-      <c r="F282" t="str">
-        <v>18:00</v>
-      </c>
       <c r="G282" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H282" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I282" t="str">
         <v/>
@@ -10286,28 +10286,28 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B283" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Dip. artistico-motorio + musicale</v>
       </c>
       <c r="C283" t="str">
         <v>temporanea</v>
       </c>
       <c r="D283" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E283" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="F283" t="str">
         <v>16:30</v>
       </c>
-      <c r="F283" t="str">
-        <v>18:00</v>
-      </c>
       <c r="G283" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-04</v>
       </c>
       <c r="H283" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-04</v>
       </c>
       <c r="I283" t="str">
         <v/>
@@ -10321,28 +10321,28 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B284" t="str">
-        <v>Dip. linguistico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C284" t="str">
         <v>temporanea</v>
       </c>
       <c r="D284" t="str">
-        <v>Giovedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E284" t="str">
-        <v>16:30</v>
+        <v>09:30</v>
       </c>
       <c r="F284" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G284" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H284" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -10356,28 +10356,28 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B285" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Scrutini</v>
       </c>
       <c r="C285" t="str">
         <v>temporanea</v>
       </c>
       <c r="D285" t="str">
-        <v>Giovedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E285" t="str">
-        <v>16:30</v>
+        <v>09:30</v>
       </c>
       <c r="F285" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G285" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H285" t="str">
-        <v>2027-06-03</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -10391,28 +10391,28 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B286" t="str">
-        <v>Dip. umanistico</v>
+        <v>Scrutini</v>
       </c>
       <c r="C286" t="str">
         <v>temporanea</v>
       </c>
       <c r="D286" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E286" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F286" t="str">
-        <v>16:30</v>
+        <v>17:30</v>
       </c>
       <c r="G286" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H286" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -10425,11 +10425,11 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287">
-        <v>20</v>
+      <c r="A287" t="str">
+        <v/>
       </c>
       <c r="B287" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Esame: prova scritta italiano</v>
       </c>
       <c r="C287" t="str">
         <v>temporanea</v>
@@ -10438,86 +10438,86 @@
         <v>Venerdì</v>
       </c>
       <c r="E287" t="str">
-        <v>15:00</v>
+        <v>08:30</v>
       </c>
       <c r="F287" t="str">
-        <v>16:30</v>
+        <v>12:30</v>
       </c>
       <c r="G287" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-11</v>
       </c>
       <c r="H287" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-11</v>
       </c>
       <c r="I287" t="str">
         <v/>
       </c>
       <c r="J287" t="str">
-        <v/>
+        <v>Corridoi piano terra</v>
       </c>
       <c r="K287" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288">
-        <v>3</v>
+      <c r="A288" t="str">
+        <v/>
       </c>
       <c r="B288" t="str">
-        <v>Dip. linguistico</v>
+        <v>Esame: prova scritta matematica</v>
       </c>
       <c r="C288" t="str">
         <v>temporanea</v>
       </c>
       <c r="D288" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E288" t="str">
-        <v>15:00</v>
+        <v>08:30</v>
       </c>
       <c r="F288" t="str">
-        <v>16:30</v>
+        <v>12:30</v>
       </c>
       <c r="G288" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-14</v>
       </c>
       <c r="H288" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-14</v>
       </c>
       <c r="I288" t="str">
         <v/>
       </c>
       <c r="J288" t="str">
-        <v/>
+        <v>Corridoi piano terra</v>
       </c>
       <c r="K288" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B289" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Dip. umanistico</v>
       </c>
       <c r="C289" t="str">
         <v>temporanea</v>
       </c>
       <c r="D289" t="str">
-        <v>Venerdì</v>
+        <v>Martedì</v>
       </c>
       <c r="E289" t="str">
-        <v>15:00</v>
+        <v>16:30</v>
       </c>
       <c r="F289" t="str">
-        <v>16:30</v>
+        <v>18:00</v>
       </c>
       <c r="G289" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H289" t="str">
-        <v>2027-06-04</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10531,28 +10531,28 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B290" t="str">
-        <v>Scrutini</v>
+        <v>Dip. matematico-scientifico</v>
       </c>
       <c r="C290" t="str">
         <v>temporanea</v>
       </c>
       <c r="D290" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E290" t="str">
-        <v>09:30</v>
+        <v>16:30</v>
       </c>
       <c r="F290" t="str">
-        <v>17:30</v>
+        <v>18:00</v>
       </c>
       <c r="G290" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H290" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I290" t="str">
         <v/>
@@ -10566,10 +10566,10 @@
     </row>
     <row r="291">
       <c r="A291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B291" t="str">
-        <v>Scrutini</v>
+        <v>Dip. linguistico</v>
       </c>
       <c r="C291" t="str">
         <v>temporanea</v>
@@ -10578,16 +10578,16 @@
         <v>Martedì</v>
       </c>
       <c r="E291" t="str">
-        <v>09:30</v>
+        <v>16:30</v>
       </c>
       <c r="F291" t="str">
-        <v>17:30</v>
+        <v>18:00</v>
       </c>
       <c r="G291" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-15</v>
       </c>
       <c r="H291" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-15</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10601,115 +10601,115 @@
     </row>
     <row r="292">
       <c r="A292">
+        <v>5</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Dip. artistico-motorio + musicale</v>
+      </c>
+      <c r="C292" t="str">
+        <v>temporanea</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Martedì</v>
+      </c>
+      <c r="E292" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="F292" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="G292" t="str">
+        <v>2027-06-15</v>
+      </c>
+      <c r="H292" t="str">
+        <v>2027-06-15</v>
+      </c>
+      <c r="I292" t="str">
+        <v/>
+      </c>
+      <c r="J292" t="str">
+        <v/>
+      </c>
+      <c r="K292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
         <v>2</v>
       </c>
-      <c r="B292" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C292" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D292" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E292" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F292" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G292" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H292" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I292" t="str">
-        <v/>
-      </c>
-      <c r="J292" t="str">
-        <v/>
-      </c>
-      <c r="K292" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="str">
-        <v/>
-      </c>
       <c r="B293" t="str">
-        <v>Esame: prova scritta italiano</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C293" t="str">
         <v>temporanea</v>
       </c>
       <c r="D293" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E293" t="str">
         <v>08:30</v>
       </c>
       <c r="F293" t="str">
-        <v>12:30</v>
+        <v>17:30</v>
       </c>
       <c r="G293" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-17</v>
       </c>
       <c r="H293" t="str">
-        <v>2027-06-11</v>
+        <v>2027-06-17</v>
       </c>
       <c r="I293" t="str">
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K293" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="str">
-        <v/>
+      <c r="A294">
+        <v>2</v>
       </c>
       <c r="B294" t="str">
-        <v>Esame: prova scritta matematica</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C294" t="str">
         <v>temporanea</v>
       </c>
       <c r="D294" t="str">
-        <v>Lunedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E294" t="str">
         <v>08:30</v>
       </c>
       <c r="F294" t="str">
-        <v>12:30</v>
+        <v>17:30</v>
       </c>
       <c r="G294" t="str">
-        <v>2027-06-14</v>
+        <v>2027-06-18</v>
       </c>
       <c r="H294" t="str">
-        <v>2027-06-14</v>
+        <v>2027-06-18</v>
       </c>
       <c r="I294" t="str">
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K294" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="295">
-      <c r="A295">
-        <v>4</v>
+      <c r="A295" t="str">
+        <v/>
       </c>
       <c r="B295" t="str">
-        <v>Dip. umanistico</v>
+        <v>Esame: prova scritta lingue</v>
       </c>
       <c r="C295" t="str">
         <v>temporanea</v>
@@ -10718,10 +10718,10 @@
         <v>Martedì</v>
       </c>
       <c r="E295" t="str">
-        <v>16:30</v>
+        <v>08:30</v>
       </c>
       <c r="F295" t="str">
-        <v>18:00</v>
+        <v>12:30</v>
       </c>
       <c r="G295" t="str">
         <v>2027-06-15</v>
@@ -10733,36 +10733,36 @@
         <v/>
       </c>
       <c r="J295" t="str">
-        <v/>
+        <v>Corridoi piano terra</v>
       </c>
       <c r="K295" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B296" t="str">
-        <v>Dip. matematico-scientifico</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C296" t="str">
         <v>temporanea</v>
       </c>
       <c r="D296" t="str">
-        <v>Martedì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E296" t="str">
-        <v>16:30</v>
+        <v>08:30</v>
       </c>
       <c r="F296" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G296" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-21</v>
       </c>
       <c r="H296" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-21</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B297" t="str">
-        <v>Dip. linguistico</v>
+        <v>Esami: orali</v>
       </c>
       <c r="C297" t="str">
         <v>temporanea</v>
@@ -10788,16 +10788,16 @@
         <v>Martedì</v>
       </c>
       <c r="E297" t="str">
-        <v>16:30</v>
+        <v>08:30</v>
       </c>
       <c r="F297" t="str">
-        <v>18:00</v>
+        <v>17:30</v>
       </c>
       <c r="G297" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-22</v>
       </c>
       <c r="H297" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-22</v>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -10810,46 +10810,46 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298">
-        <v>5</v>
+      <c r="A298" t="str">
+        <v/>
       </c>
       <c r="B298" t="str">
-        <v>Dip. artistico-motorio + musicale</v>
+        <v>Collegio docenti</v>
       </c>
       <c r="C298" t="str">
         <v>temporanea</v>
       </c>
       <c r="D298" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E298" t="str">
-        <v>16:30</v>
+        <v>17:00</v>
       </c>
       <c r="F298" t="str">
-        <v>18:00</v>
+        <v>19:00</v>
       </c>
       <c r="G298" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-30</v>
       </c>
       <c r="H298" t="str">
-        <v>2027-06-15</v>
+        <v>2027-06-30</v>
       </c>
       <c r="I298" t="str">
         <v/>
       </c>
       <c r="J298" t="str">
-        <v/>
+        <v>Auditorium</v>
       </c>
       <c r="K298" t="str">
-        <v/>
+        <v>terra</v>
       </c>
     </row>
     <row r="299">
       <c r="A299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B299" t="str">
-        <v>Esami: orali</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C299" t="str">
         <v>temporanea</v>
@@ -10858,16 +10858,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E299" t="str">
-        <v>08:30</v>
+        <v>18:00</v>
       </c>
       <c r="F299" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G299" t="str">
-        <v>2027-06-17</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H299" t="str">
-        <v>2027-06-17</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10881,28 +10881,28 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B300" t="str">
-        <v>Esami: orali</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C300" t="str">
         <v>temporanea</v>
       </c>
       <c r="D300" t="str">
-        <v>Venerdì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E300" t="str">
-        <v>08:30</v>
+        <v>18:00</v>
       </c>
       <c r="F300" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G300" t="str">
-        <v>2027-06-18</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H300" t="str">
-        <v>2027-06-18</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I300" t="str">
         <v/>
@@ -10915,64 +10915,64 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="str">
-        <v/>
+      <c r="A301">
+        <v>4</v>
       </c>
       <c r="B301" t="str">
-        <v>Esame: prova scritta lingue</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C301" t="str">
         <v>temporanea</v>
       </c>
       <c r="D301" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E301" t="str">
-        <v>08:30</v>
+        <v>18:00</v>
       </c>
       <c r="F301" t="str">
-        <v>12:30</v>
+        <v>19:00</v>
       </c>
       <c r="G301" t="str">
-        <v>2027-06-15</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H301" t="str">
-        <v>2027-06-15</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I301" t="str">
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>Corridoi piano terra</v>
+        <v/>
       </c>
       <c r="K301" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B302" t="str">
-        <v>Esami: orali</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C302" t="str">
         <v>temporanea</v>
       </c>
       <c r="D302" t="str">
-        <v>Lunedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E302" t="str">
-        <v>08:30</v>
+        <v>18:00</v>
       </c>
       <c r="F302" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G302" t="str">
-        <v>2027-06-21</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H302" t="str">
-        <v>2027-06-21</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10986,28 +10986,28 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B303" t="str">
-        <v>Esami: orali</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C303" t="str">
         <v>temporanea</v>
       </c>
       <c r="D303" t="str">
-        <v>Martedì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E303" t="str">
-        <v>08:30</v>
+        <v>18:00</v>
       </c>
       <c r="F303" t="str">
-        <v>17:30</v>
+        <v>19:00</v>
       </c>
       <c r="G303" t="str">
-        <v>2027-06-22</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H303" t="str">
-        <v>2027-06-22</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I303" t="str">
         <v/>
@@ -11020,43 +11020,43 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="str">
-        <v/>
+      <c r="A304">
+        <v>7</v>
       </c>
       <c r="B304" t="str">
-        <v>Collegio docenti</v>
+        <v>Assemblea ed elezioni rappresentanti</v>
       </c>
       <c r="C304" t="str">
         <v>temporanea</v>
       </c>
       <c r="D304" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E304" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="F304" t="str">
         <v>19:00</v>
       </c>
       <c r="G304" t="str">
-        <v>2027-06-30</v>
+        <v>2026-10-22</v>
       </c>
       <c r="H304" t="str">
-        <v>2027-06-30</v>
+        <v>2026-10-22</v>
       </c>
       <c r="I304" t="str">
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>Auditorium</v>
+        <v/>
       </c>
       <c r="K304" t="str">
-        <v>terra</v>
+        <v/>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B305" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11091,7 +11091,7 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B306" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B307" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11161,7 +11161,7 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B308" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B309" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11231,7 +11231,7 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B310" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B311" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B312" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B313" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11371,7 +11371,7 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B314" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B315" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11441,7 +11441,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B316" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B317" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B318" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B319" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11581,7 +11581,7 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B320" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B321" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11651,7 +11651,7 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B322" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B323" t="str">
         <v>Assemblea ed elezioni rappresentanti</v>
@@ -11721,10 +11721,10 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B324" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C324" t="str">
         <v>temporanea</v>
@@ -11733,16 +11733,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E324" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F324" t="str">
         <v>19:00</v>
       </c>
       <c r="G324" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H324" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I324" t="str">
         <v/>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B325" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C325" t="str">
         <v>temporanea</v>
@@ -11768,16 +11768,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E325" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F325" t="str">
         <v>19:00</v>
       </c>
       <c r="G325" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H325" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I325" t="str">
         <v/>
@@ -11791,10 +11791,10 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B326" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C326" t="str">
         <v>temporanea</v>
@@ -11803,16 +11803,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E326" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F326" t="str">
         <v>19:00</v>
       </c>
       <c r="G326" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H326" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I326" t="str">
         <v/>
@@ -11826,10 +11826,10 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B327" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C327" t="str">
         <v>temporanea</v>
@@ -11838,16 +11838,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E327" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F327" t="str">
         <v>19:00</v>
       </c>
       <c r="G327" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H327" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I327" t="str">
         <v/>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B328" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C328" t="str">
         <v>temporanea</v>
@@ -11873,16 +11873,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E328" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F328" t="str">
         <v>19:00</v>
       </c>
       <c r="G328" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H328" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I328" t="str">
         <v/>
@@ -11896,10 +11896,10 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B329" t="str">
-        <v>Assemblea ed elezioni rappresentanti</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C329" t="str">
         <v>temporanea</v>
@@ -11908,16 +11908,16 @@
         <v>Giovedì</v>
       </c>
       <c r="E329" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="F329" t="str">
         <v>19:00</v>
       </c>
       <c r="G329" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="H329" t="str">
-        <v>2026-10-22</v>
+        <v>2026-12-10</v>
       </c>
       <c r="I329" t="str">
         <v/>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B330" t="str">
         <v>Colloqui con le famiglie</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B331" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12001,7 +12001,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B332" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B333" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12071,7 +12071,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B334" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B335" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12141,7 +12141,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B336" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B337" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12211,7 +12211,7 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B338" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B339" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B340" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B341" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12351,7 +12351,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B342" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B343" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12421,7 +12421,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B344" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B345" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12491,7 +12491,7 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B346" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B347" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12561,7 +12561,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B348" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B349" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12605,7 +12605,7 @@
         <v>temporanea</v>
       </c>
       <c r="D349" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E349" t="str">
         <v>15:00</v>
@@ -12614,10 +12614,10 @@
         <v>19:00</v>
       </c>
       <c r="G349" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H349" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I349" t="str">
         <v/>
@@ -12631,7 +12631,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B350" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12640,7 +12640,7 @@
         <v>temporanea</v>
       </c>
       <c r="D350" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E350" t="str">
         <v>15:00</v>
@@ -12649,10 +12649,10 @@
         <v>19:00</v>
       </c>
       <c r="G350" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H350" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I350" t="str">
         <v/>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B351" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12675,7 +12675,7 @@
         <v>temporanea</v>
       </c>
       <c r="D351" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E351" t="str">
         <v>15:00</v>
@@ -12684,10 +12684,10 @@
         <v>19:00</v>
       </c>
       <c r="G351" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H351" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I351" t="str">
         <v/>
@@ -12701,7 +12701,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B352" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12710,7 +12710,7 @@
         <v>temporanea</v>
       </c>
       <c r="D352" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E352" t="str">
         <v>15:00</v>
@@ -12719,10 +12719,10 @@
         <v>19:00</v>
       </c>
       <c r="G352" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H352" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B353" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12745,7 +12745,7 @@
         <v>temporanea</v>
       </c>
       <c r="D353" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E353" t="str">
         <v>15:00</v>
@@ -12754,10 +12754,10 @@
         <v>19:00</v>
       </c>
       <c r="G353" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H353" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12771,7 +12771,7 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B354" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12780,7 +12780,7 @@
         <v>temporanea</v>
       </c>
       <c r="D354" t="str">
-        <v>Giovedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E354" t="str">
         <v>15:00</v>
@@ -12789,10 +12789,10 @@
         <v>19:00</v>
       </c>
       <c r="G354" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="H354" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-09</v>
       </c>
       <c r="I354" t="str">
         <v/>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B355" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12841,7 +12841,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B356" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B357" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12911,7 +12911,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B358" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B359" t="str">
         <v>Colloqui con le famiglie</v>
@@ -12981,7 +12981,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B360" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B361" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B362" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B363" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B364" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B365" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13191,7 +13191,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B366" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B367" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13261,7 +13261,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B368" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B369" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13331,7 +13331,7 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B370" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B371" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13401,7 +13401,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B372" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B373" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13445,7 +13445,7 @@
         <v>temporanea</v>
       </c>
       <c r="D373" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E373" t="str">
         <v>15:00</v>
@@ -13454,10 +13454,10 @@
         <v>19:00</v>
       </c>
       <c r="G373" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H373" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I373" t="str">
         <v/>
@@ -13471,7 +13471,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B374" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13480,7 +13480,7 @@
         <v>temporanea</v>
       </c>
       <c r="D374" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E374" t="str">
         <v>15:00</v>
@@ -13489,10 +13489,10 @@
         <v>19:00</v>
       </c>
       <c r="G374" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H374" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I374" t="str">
         <v/>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B375" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13515,7 +13515,7 @@
         <v>temporanea</v>
       </c>
       <c r="D375" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E375" t="str">
         <v>15:00</v>
@@ -13524,10 +13524,10 @@
         <v>19:00</v>
       </c>
       <c r="G375" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H375" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I375" t="str">
         <v/>
@@ -13541,7 +13541,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B376" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13550,7 +13550,7 @@
         <v>temporanea</v>
       </c>
       <c r="D376" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E376" t="str">
         <v>15:00</v>
@@ -13559,10 +13559,10 @@
         <v>19:00</v>
       </c>
       <c r="G376" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H376" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I376" t="str">
         <v/>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B377" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13585,7 +13585,7 @@
         <v>temporanea</v>
       </c>
       <c r="D377" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E377" t="str">
         <v>15:00</v>
@@ -13594,10 +13594,10 @@
         <v>19:00</v>
       </c>
       <c r="G377" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H377" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I377" t="str">
         <v/>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B378" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13620,7 +13620,7 @@
         <v>temporanea</v>
       </c>
       <c r="D378" t="str">
-        <v>Mercoledì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E378" t="str">
         <v>15:00</v>
@@ -13629,10 +13629,10 @@
         <v>19:00</v>
       </c>
       <c r="G378" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="H378" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-11</v>
       </c>
       <c r="I378" t="str">
         <v/>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B379" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13681,7 +13681,7 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B380" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B381" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13751,7 +13751,7 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B382" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B383" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13821,7 +13821,7 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B384" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B385" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13891,7 +13891,7 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B386" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B387" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13961,7 +13961,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B388" t="str">
         <v>Colloqui con le famiglie</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B389" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14031,7 +14031,7 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B390" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B391" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14101,7 +14101,7 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B392" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B393" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14171,7 +14171,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B394" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B395" t="str">
         <v>Colloqui con le famiglie</v>
@@ -14241,28 +14241,28 @@
     </row>
     <row r="396">
       <c r="A396">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B396" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C396" t="str">
         <v>temporanea</v>
       </c>
       <c r="D396" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E396" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F396" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G396" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H396" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I396" t="str">
         <v/>
@@ -14276,28 +14276,28 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B397" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C397" t="str">
         <v>temporanea</v>
       </c>
       <c r="D397" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E397" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F397" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G397" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H397" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I397" t="str">
         <v/>
@@ -14311,28 +14311,28 @@
     </row>
     <row r="398">
       <c r="A398">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B398" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C398" t="str">
         <v>temporanea</v>
       </c>
       <c r="D398" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E398" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F398" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G398" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H398" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I398" t="str">
         <v/>
@@ -14346,28 +14346,28 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B399" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C399" t="str">
         <v>temporanea</v>
       </c>
       <c r="D399" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E399" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F399" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G399" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H399" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I399" t="str">
         <v/>
@@ -14381,28 +14381,28 @@
     </row>
     <row r="400">
       <c r="A400">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B400" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C400" t="str">
         <v>temporanea</v>
       </c>
       <c r="D400" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E400" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F400" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G400" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H400" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I400" t="str">
         <v/>
@@ -14416,28 +14416,28 @@
     </row>
     <row r="401">
       <c r="A401">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B401" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C401" t="str">
         <v>temporanea</v>
       </c>
       <c r="D401" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E401" t="str">
-        <v>15:00</v>
+        <v>14:00</v>
       </c>
       <c r="F401" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="G401" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="H401" t="str">
-        <v>2026-12-11</v>
+        <v>2027-02-03</v>
       </c>
       <c r="I401" t="str">
         <v/>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="402">
       <c r="A402">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B402" t="str">
         <v>Scrutini</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="403">
       <c r="A403">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B403" t="str">
         <v>Scrutini</v>
@@ -14521,7 +14521,7 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B404" t="str">
         <v>Scrutini</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B405" t="str">
         <v>Scrutini</v>
@@ -14591,7 +14591,7 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B406" t="str">
         <v>Scrutini</v>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="407">
       <c r="A407">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B407" t="str">
         <v>Scrutini</v>
@@ -14661,7 +14661,7 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B408" t="str">
         <v>Scrutini</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="409">
       <c r="A409">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B409" t="str">
         <v>Scrutini</v>
@@ -14731,7 +14731,7 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B410" t="str">
         <v>Scrutini</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B411" t="str">
         <v>Scrutini</v>
@@ -14801,7 +14801,7 @@
     </row>
     <row r="412">
       <c r="A412">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B412" t="str">
         <v>Scrutini</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B413" t="str">
         <v>Scrutini</v>
@@ -14871,7 +14871,7 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B414" t="str">
         <v>Scrutini</v>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="415">
       <c r="A415">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B415" t="str">
         <v>Scrutini</v>
@@ -14941,7 +14941,7 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B416" t="str">
         <v>Scrutini</v>
@@ -14976,7 +14976,7 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B417" t="str">
         <v>Scrutini</v>
@@ -15011,7 +15011,7 @@
     </row>
     <row r="418">
       <c r="A418">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B418" t="str">
         <v>Scrutini</v>
@@ -15046,7 +15046,7 @@
     </row>
     <row r="419">
       <c r="A419">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B419" t="str">
         <v>Scrutini</v>
@@ -15081,7 +15081,7 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B420" t="str">
         <v>Scrutini</v>
@@ -15116,7 +15116,7 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B421" t="str">
         <v>Scrutini</v>
@@ -15125,7 +15125,7 @@
         <v>temporanea</v>
       </c>
       <c r="D421" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E421" t="str">
         <v>14:00</v>
@@ -15134,10 +15134,10 @@
         <v>20:00</v>
       </c>
       <c r="G421" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H421" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I421" t="str">
         <v/>
@@ -15151,7 +15151,7 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B422" t="str">
         <v>Scrutini</v>
@@ -15160,7 +15160,7 @@
         <v>temporanea</v>
       </c>
       <c r="D422" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E422" t="str">
         <v>14:00</v>
@@ -15169,10 +15169,10 @@
         <v>20:00</v>
       </c>
       <c r="G422" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H422" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I422" t="str">
         <v/>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B423" t="str">
         <v>Scrutini</v>
@@ -15195,7 +15195,7 @@
         <v>temporanea</v>
       </c>
       <c r="D423" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E423" t="str">
         <v>14:00</v>
@@ -15204,10 +15204,10 @@
         <v>20:00</v>
       </c>
       <c r="G423" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H423" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I423" t="str">
         <v/>
@@ -15221,7 +15221,7 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B424" t="str">
         <v>Scrutini</v>
@@ -15230,7 +15230,7 @@
         <v>temporanea</v>
       </c>
       <c r="D424" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E424" t="str">
         <v>14:00</v>
@@ -15239,10 +15239,10 @@
         <v>20:00</v>
       </c>
       <c r="G424" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H424" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I424" t="str">
         <v/>
@@ -15256,7 +15256,7 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B425" t="str">
         <v>Scrutini</v>
@@ -15265,7 +15265,7 @@
         <v>temporanea</v>
       </c>
       <c r="D425" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E425" t="str">
         <v>14:00</v>
@@ -15274,10 +15274,10 @@
         <v>20:00</v>
       </c>
       <c r="G425" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H425" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I425" t="str">
         <v/>
@@ -15291,7 +15291,7 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B426" t="str">
         <v>Scrutini</v>
@@ -15300,7 +15300,7 @@
         <v>temporanea</v>
       </c>
       <c r="D426" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E426" t="str">
         <v>14:00</v>
@@ -15309,10 +15309,10 @@
         <v>20:00</v>
       </c>
       <c r="G426" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="H426" t="str">
-        <v>2027-02-03</v>
+        <v>2027-02-04</v>
       </c>
       <c r="I426" t="str">
         <v/>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="427">
       <c r="A427">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B427" t="str">
         <v>Scrutini</v>
@@ -15361,7 +15361,7 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B428" t="str">
         <v>Scrutini</v>
@@ -15396,7 +15396,7 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B429" t="str">
         <v>Scrutini</v>
@@ -15431,7 +15431,7 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B430" t="str">
         <v>Scrutini</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="431">
       <c r="A431">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B431" t="str">
         <v>Scrutini</v>
@@ -15501,7 +15501,7 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B432" t="str">
         <v>Scrutini</v>
@@ -15536,7 +15536,7 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B433" t="str">
         <v>Scrutini</v>
@@ -15571,7 +15571,7 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B434" t="str">
         <v>Scrutini</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B435" t="str">
         <v>Scrutini</v>
@@ -15641,7 +15641,7 @@
     </row>
     <row r="436">
       <c r="A436">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B436" t="str">
         <v>Scrutini</v>
@@ -15676,7 +15676,7 @@
     </row>
     <row r="437">
       <c r="A437">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B437" t="str">
         <v>Scrutini</v>
@@ -15711,7 +15711,7 @@
     </row>
     <row r="438">
       <c r="A438">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B438" t="str">
         <v>Scrutini</v>
@@ -15746,7 +15746,7 @@
     </row>
     <row r="439">
       <c r="A439">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B439" t="str">
         <v>Scrutini</v>
@@ -15781,7 +15781,7 @@
     </row>
     <row r="440">
       <c r="A440">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B440" t="str">
         <v>Scrutini</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="441">
       <c r="A441">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B441" t="str">
         <v>Scrutini</v>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="442">
       <c r="A442">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B442" t="str">
         <v>Scrutini</v>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="443">
       <c r="A443">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B443" t="str">
         <v>Scrutini</v>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="444">
       <c r="A444">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B444" t="str">
         <v>Scrutini</v>
@@ -15956,7 +15956,7 @@
     </row>
     <row r="445">
       <c r="A445">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B445" t="str">
         <v>Scrutini</v>
@@ -15991,7 +15991,7 @@
     </row>
     <row r="446">
       <c r="A446">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B446" t="str">
         <v>Scrutini</v>
@@ -16000,7 +16000,7 @@
         <v>temporanea</v>
       </c>
       <c r="D446" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E446" t="str">
         <v>14:00</v>
@@ -16009,10 +16009,10 @@
         <v>20:00</v>
       </c>
       <c r="G446" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H446" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I446" t="str">
         <v/>
@@ -16026,7 +16026,7 @@
     </row>
     <row r="447">
       <c r="A447">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B447" t="str">
         <v>Scrutini</v>
@@ -16035,7 +16035,7 @@
         <v>temporanea</v>
       </c>
       <c r="D447" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E447" t="str">
         <v>14:00</v>
@@ -16044,10 +16044,10 @@
         <v>20:00</v>
       </c>
       <c r="G447" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H447" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I447" t="str">
         <v/>
@@ -16061,7 +16061,7 @@
     </row>
     <row r="448">
       <c r="A448">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B448" t="str">
         <v>Scrutini</v>
@@ -16070,7 +16070,7 @@
         <v>temporanea</v>
       </c>
       <c r="D448" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E448" t="str">
         <v>14:00</v>
@@ -16079,10 +16079,10 @@
         <v>20:00</v>
       </c>
       <c r="G448" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H448" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I448" t="str">
         <v/>
@@ -16096,7 +16096,7 @@
     </row>
     <row r="449">
       <c r="A449">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B449" t="str">
         <v>Scrutini</v>
@@ -16105,7 +16105,7 @@
         <v>temporanea</v>
       </c>
       <c r="D449" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E449" t="str">
         <v>14:00</v>
@@ -16114,10 +16114,10 @@
         <v>20:00</v>
       </c>
       <c r="G449" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H449" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I449" t="str">
         <v/>
@@ -16131,7 +16131,7 @@
     </row>
     <row r="450">
       <c r="A450">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B450" t="str">
         <v>Scrutini</v>
@@ -16140,7 +16140,7 @@
         <v>temporanea</v>
       </c>
       <c r="D450" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E450" t="str">
         <v>14:00</v>
@@ -16149,10 +16149,10 @@
         <v>20:00</v>
       </c>
       <c r="G450" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H450" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I450" t="str">
         <v/>
@@ -16166,7 +16166,7 @@
     </row>
     <row r="451">
       <c r="A451">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B451" t="str">
         <v>Scrutini</v>
@@ -16175,7 +16175,7 @@
         <v>temporanea</v>
       </c>
       <c r="D451" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E451" t="str">
         <v>14:00</v>
@@ -16184,10 +16184,10 @@
         <v>20:00</v>
       </c>
       <c r="G451" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="H451" t="str">
-        <v>2027-02-04</v>
+        <v>2027-02-05</v>
       </c>
       <c r="I451" t="str">
         <v/>
@@ -16201,7 +16201,7 @@
     </row>
     <row r="452">
       <c r="A452">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B452" t="str">
         <v>Scrutini</v>
@@ -16236,7 +16236,7 @@
     </row>
     <row r="453">
       <c r="A453">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B453" t="str">
         <v>Scrutini</v>
@@ -16271,7 +16271,7 @@
     </row>
     <row r="454">
       <c r="A454">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B454" t="str">
         <v>Scrutini</v>
@@ -16306,7 +16306,7 @@
     </row>
     <row r="455">
       <c r="A455">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B455" t="str">
         <v>Scrutini</v>
@@ -16341,7 +16341,7 @@
     </row>
     <row r="456">
       <c r="A456">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B456" t="str">
         <v>Scrutini</v>
@@ -16376,7 +16376,7 @@
     </row>
     <row r="457">
       <c r="A457">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B457" t="str">
         <v>Scrutini</v>
@@ -16411,7 +16411,7 @@
     </row>
     <row r="458">
       <c r="A458">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B458" t="str">
         <v>Scrutini</v>
@@ -16446,7 +16446,7 @@
     </row>
     <row r="459">
       <c r="A459">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B459" t="str">
         <v>Scrutini</v>
@@ -16481,7 +16481,7 @@
     </row>
     <row r="460">
       <c r="A460">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B460" t="str">
         <v>Scrutini</v>
@@ -16516,7 +16516,7 @@
     </row>
     <row r="461">
       <c r="A461">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B461" t="str">
         <v>Scrutini</v>
@@ -16551,7 +16551,7 @@
     </row>
     <row r="462">
       <c r="A462">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B462" t="str">
         <v>Scrutini</v>
@@ -16586,7 +16586,7 @@
     </row>
     <row r="463">
       <c r="A463">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B463" t="str">
         <v>Scrutini</v>
@@ -16621,7 +16621,7 @@
     </row>
     <row r="464">
       <c r="A464">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B464" t="str">
         <v>Scrutini</v>
@@ -16656,7 +16656,7 @@
     </row>
     <row r="465">
       <c r="A465">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B465" t="str">
         <v>Scrutini</v>
@@ -16691,7 +16691,7 @@
     </row>
     <row r="466">
       <c r="A466">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B466" t="str">
         <v>Scrutini</v>
@@ -16726,7 +16726,7 @@
     </row>
     <row r="467">
       <c r="A467">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B467" t="str">
         <v>Scrutini</v>
@@ -16761,7 +16761,7 @@
     </row>
     <row r="468">
       <c r="A468">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B468" t="str">
         <v>Scrutini</v>
@@ -16796,7 +16796,7 @@
     </row>
     <row r="469">
       <c r="A469">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B469" t="str">
         <v>Scrutini</v>
@@ -16831,7 +16831,7 @@
     </row>
     <row r="470">
       <c r="A470">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B470" t="str">
         <v>Scrutini</v>
@@ -16866,28 +16866,28 @@
     </row>
     <row r="471">
       <c r="A471">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B471" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C471" t="str">
         <v>temporanea</v>
       </c>
       <c r="D471" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E471" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F471" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G471" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H471" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I471" t="str">
         <v/>
@@ -16901,28 +16901,28 @@
     </row>
     <row r="472">
       <c r="A472">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B472" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C472" t="str">
         <v>temporanea</v>
       </c>
       <c r="D472" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E472" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F472" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G472" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H472" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I472" t="str">
         <v/>
@@ -16936,28 +16936,28 @@
     </row>
     <row r="473">
       <c r="A473">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B473" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C473" t="str">
         <v>temporanea</v>
       </c>
       <c r="D473" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E473" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F473" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G473" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H473" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I473" t="str">
         <v/>
@@ -16971,28 +16971,28 @@
     </row>
     <row r="474">
       <c r="A474">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B474" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C474" t="str">
         <v>temporanea</v>
       </c>
       <c r="D474" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E474" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F474" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G474" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H474" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I474" t="str">
         <v/>
@@ -17006,28 +17006,28 @@
     </row>
     <row r="475">
       <c r="A475">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B475" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C475" t="str">
         <v>temporanea</v>
       </c>
       <c r="D475" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E475" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F475" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G475" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H475" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I475" t="str">
         <v/>
@@ -17041,28 +17041,28 @@
     </row>
     <row r="476">
       <c r="A476">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B476" t="str">
-        <v>Scrutini</v>
+        <v>Colloqui con le famiglie</v>
       </c>
       <c r="C476" t="str">
         <v>temporanea</v>
       </c>
       <c r="D476" t="str">
-        <v>Venerdì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E476" t="str">
-        <v>14:00</v>
+        <v>15:00</v>
       </c>
       <c r="F476" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="G476" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="H476" t="str">
-        <v>2027-02-05</v>
+        <v>2027-04-14</v>
       </c>
       <c r="I476" t="str">
         <v/>
@@ -17076,7 +17076,7 @@
     </row>
     <row r="477">
       <c r="A477">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B477" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17111,7 +17111,7 @@
     </row>
     <row r="478">
       <c r="A478">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B478" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17146,7 +17146,7 @@
     </row>
     <row r="479">
       <c r="A479">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B479" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17181,7 +17181,7 @@
     </row>
     <row r="480">
       <c r="A480">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B480" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17216,7 +17216,7 @@
     </row>
     <row r="481">
       <c r="A481">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B481" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17251,7 +17251,7 @@
     </row>
     <row r="482">
       <c r="A482">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B482" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17286,7 +17286,7 @@
     </row>
     <row r="483">
       <c r="A483">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B483" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17321,7 +17321,7 @@
     </row>
     <row r="484">
       <c r="A484">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B484" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17356,7 +17356,7 @@
     </row>
     <row r="485">
       <c r="A485">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B485" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17391,7 +17391,7 @@
     </row>
     <row r="486">
       <c r="A486">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B486" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17426,7 +17426,7 @@
     </row>
     <row r="487">
       <c r="A487">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B487" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17461,7 +17461,7 @@
     </row>
     <row r="488">
       <c r="A488">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B488" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="489">
       <c r="A489">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B489" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17531,7 +17531,7 @@
     </row>
     <row r="490">
       <c r="A490">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B490" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17566,7 +17566,7 @@
     </row>
     <row r="491">
       <c r="A491">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B491" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17601,7 +17601,7 @@
     </row>
     <row r="492">
       <c r="A492">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B492" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="493">
       <c r="A493">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B493" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17671,7 +17671,7 @@
     </row>
     <row r="494">
       <c r="A494">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B494" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17706,7 +17706,7 @@
     </row>
     <row r="495">
       <c r="A495">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B495" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17741,7 +17741,7 @@
     </row>
     <row r="496">
       <c r="A496">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B496" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17750,7 +17750,7 @@
         <v>temporanea</v>
       </c>
       <c r="D496" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E496" t="str">
         <v>15:00</v>
@@ -17759,10 +17759,10 @@
         <v>19:00</v>
       </c>
       <c r="G496" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H496" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I496" t="str">
         <v/>
@@ -17776,7 +17776,7 @@
     </row>
     <row r="497">
       <c r="A497">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B497" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17785,7 +17785,7 @@
         <v>temporanea</v>
       </c>
       <c r="D497" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E497" t="str">
         <v>15:00</v>
@@ -17794,10 +17794,10 @@
         <v>19:00</v>
       </c>
       <c r="G497" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H497" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I497" t="str">
         <v/>
@@ -17811,7 +17811,7 @@
     </row>
     <row r="498">
       <c r="A498">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B498" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17820,7 +17820,7 @@
         <v>temporanea</v>
       </c>
       <c r="D498" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E498" t="str">
         <v>15:00</v>
@@ -17829,10 +17829,10 @@
         <v>19:00</v>
       </c>
       <c r="G498" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H498" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I498" t="str">
         <v/>
@@ -17846,7 +17846,7 @@
     </row>
     <row r="499">
       <c r="A499">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B499" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17855,7 +17855,7 @@
         <v>temporanea</v>
       </c>
       <c r="D499" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E499" t="str">
         <v>15:00</v>
@@ -17864,10 +17864,10 @@
         <v>19:00</v>
       </c>
       <c r="G499" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H499" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I499" t="str">
         <v/>
@@ -17881,7 +17881,7 @@
     </row>
     <row r="500">
       <c r="A500">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B500" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17890,7 +17890,7 @@
         <v>temporanea</v>
       </c>
       <c r="D500" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E500" t="str">
         <v>15:00</v>
@@ -17899,10 +17899,10 @@
         <v>19:00</v>
       </c>
       <c r="G500" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H500" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I500" t="str">
         <v/>
@@ -17916,7 +17916,7 @@
     </row>
     <row r="501">
       <c r="A501">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B501" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17925,7 +17925,7 @@
         <v>temporanea</v>
       </c>
       <c r="D501" t="str">
-        <v>Mercoledì</v>
+        <v>Giovedì</v>
       </c>
       <c r="E501" t="str">
         <v>15:00</v>
@@ -17934,10 +17934,10 @@
         <v>19:00</v>
       </c>
       <c r="G501" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="H501" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-15</v>
       </c>
       <c r="I501" t="str">
         <v/>
@@ -17951,7 +17951,7 @@
     </row>
     <row r="502">
       <c r="A502">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B502" t="str">
         <v>Colloqui con le famiglie</v>
@@ -17986,7 +17986,7 @@
     </row>
     <row r="503">
       <c r="A503">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B503" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18021,7 +18021,7 @@
     </row>
     <row r="504">
       <c r="A504">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B504" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18056,7 +18056,7 @@
     </row>
     <row r="505">
       <c r="A505">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B505" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18091,7 +18091,7 @@
     </row>
     <row r="506">
       <c r="A506">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B506" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18126,7 +18126,7 @@
     </row>
     <row r="507">
       <c r="A507">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B507" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18161,7 +18161,7 @@
     </row>
     <row r="508">
       <c r="A508">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B508" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18196,7 +18196,7 @@
     </row>
     <row r="509">
       <c r="A509">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B509" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="510">
       <c r="A510">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B510" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18266,7 +18266,7 @@
     </row>
     <row r="511">
       <c r="A511">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B511" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="512">
       <c r="A512">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B512" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18336,7 +18336,7 @@
     </row>
     <row r="513">
       <c r="A513">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B513" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18371,7 +18371,7 @@
     </row>
     <row r="514">
       <c r="A514">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B514" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18406,7 +18406,7 @@
     </row>
     <row r="515">
       <c r="A515">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B515" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18441,7 +18441,7 @@
     </row>
     <row r="516">
       <c r="A516">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B516" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18476,7 +18476,7 @@
     </row>
     <row r="517">
       <c r="A517">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B517" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18511,7 +18511,7 @@
     </row>
     <row r="518">
       <c r="A518">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B518" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18546,7 +18546,7 @@
     </row>
     <row r="519">
       <c r="A519">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B519" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18581,7 +18581,7 @@
     </row>
     <row r="520">
       <c r="A520">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B520" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18616,7 +18616,7 @@
     </row>
     <row r="521">
       <c r="A521">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B521" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18625,7 +18625,7 @@
         <v>temporanea</v>
       </c>
       <c r="D521" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E521" t="str">
         <v>15:00</v>
@@ -18634,10 +18634,10 @@
         <v>19:00</v>
       </c>
       <c r="G521" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H521" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I521" t="str">
         <v/>
@@ -18651,7 +18651,7 @@
     </row>
     <row r="522">
       <c r="A522">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B522" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18660,7 +18660,7 @@
         <v>temporanea</v>
       </c>
       <c r="D522" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E522" t="str">
         <v>15:00</v>
@@ -18669,10 +18669,10 @@
         <v>19:00</v>
       </c>
       <c r="G522" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H522" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I522" t="str">
         <v/>
@@ -18686,7 +18686,7 @@
     </row>
     <row r="523">
       <c r="A523">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B523" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18695,7 +18695,7 @@
         <v>temporanea</v>
       </c>
       <c r="D523" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E523" t="str">
         <v>15:00</v>
@@ -18704,10 +18704,10 @@
         <v>19:00</v>
       </c>
       <c r="G523" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H523" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I523" t="str">
         <v/>
@@ -18721,7 +18721,7 @@
     </row>
     <row r="524">
       <c r="A524">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B524" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18730,7 +18730,7 @@
         <v>temporanea</v>
       </c>
       <c r="D524" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E524" t="str">
         <v>15:00</v>
@@ -18739,10 +18739,10 @@
         <v>19:00</v>
       </c>
       <c r="G524" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H524" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I524" t="str">
         <v/>
@@ -18756,7 +18756,7 @@
     </row>
     <row r="525">
       <c r="A525">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B525" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18765,7 +18765,7 @@
         <v>temporanea</v>
       </c>
       <c r="D525" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E525" t="str">
         <v>15:00</v>
@@ -18774,10 +18774,10 @@
         <v>19:00</v>
       </c>
       <c r="G525" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H525" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I525" t="str">
         <v/>
@@ -18791,7 +18791,7 @@
     </row>
     <row r="526">
       <c r="A526">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B526" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18800,7 +18800,7 @@
         <v>temporanea</v>
       </c>
       <c r="D526" t="str">
-        <v>Giovedì</v>
+        <v>Venerdì</v>
       </c>
       <c r="E526" t="str">
         <v>15:00</v>
@@ -18809,10 +18809,10 @@
         <v>19:00</v>
       </c>
       <c r="G526" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="H526" t="str">
-        <v>2027-04-15</v>
+        <v>2027-04-16</v>
       </c>
       <c r="I526" t="str">
         <v/>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="527">
       <c r="A527">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B527" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="528">
       <c r="A528">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B528" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18896,7 +18896,7 @@
     </row>
     <row r="529">
       <c r="A529">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B529" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18931,7 +18931,7 @@
     </row>
     <row r="530">
       <c r="A530">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B530" t="str">
         <v>Colloqui con le famiglie</v>
@@ -18966,7 +18966,7 @@
     </row>
     <row r="531">
       <c r="A531">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B531" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19001,7 +19001,7 @@
     </row>
     <row r="532">
       <c r="A532">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B532" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19036,7 +19036,7 @@
     </row>
     <row r="533">
       <c r="A533">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B533" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19071,7 +19071,7 @@
     </row>
     <row r="534">
       <c r="A534">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B534" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19106,7 +19106,7 @@
     </row>
     <row r="535">
       <c r="A535">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B535" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19141,7 +19141,7 @@
     </row>
     <row r="536">
       <c r="A536">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B536" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19176,7 +19176,7 @@
     </row>
     <row r="537">
       <c r="A537">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B537" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19211,7 +19211,7 @@
     </row>
     <row r="538">
       <c r="A538">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B538" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19246,7 +19246,7 @@
     </row>
     <row r="539">
       <c r="A539">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B539" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19281,7 +19281,7 @@
     </row>
     <row r="540">
       <c r="A540">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B540" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19316,7 +19316,7 @@
     </row>
     <row r="541">
       <c r="A541">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B541" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19351,7 +19351,7 @@
     </row>
     <row r="542">
       <c r="A542">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B542" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19386,7 +19386,7 @@
     </row>
     <row r="543">
       <c r="A543">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B543" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19421,7 +19421,7 @@
     </row>
     <row r="544">
       <c r="A544">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B544" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19456,7 +19456,7 @@
     </row>
     <row r="545">
       <c r="A545">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B545" t="str">
         <v>Colloqui con le famiglie</v>
@@ -19491,28 +19491,28 @@
     </row>
     <row r="546">
       <c r="A546">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B546" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C546" t="str">
         <v>temporanea</v>
       </c>
       <c r="D546" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E546" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F546" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G546" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H546" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I546" t="str">
         <v/>
@@ -19526,28 +19526,28 @@
     </row>
     <row r="547">
       <c r="A547">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B547" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C547" t="str">
         <v>temporanea</v>
       </c>
       <c r="D547" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E547" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F547" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G547" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H547" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I547" t="str">
         <v/>
@@ -19561,28 +19561,28 @@
     </row>
     <row r="548">
       <c r="A548">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B548" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C548" t="str">
         <v>temporanea</v>
       </c>
       <c r="D548" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E548" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F548" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G548" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H548" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I548" t="str">
         <v/>
@@ -19596,28 +19596,28 @@
     </row>
     <row r="549">
       <c r="A549">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B549" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C549" t="str">
         <v>temporanea</v>
       </c>
       <c r="D549" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E549" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F549" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G549" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H549" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I549" t="str">
         <v/>
@@ -19631,28 +19631,28 @@
     </row>
     <row r="550">
       <c r="A550">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B550" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C550" t="str">
         <v>temporanea</v>
       </c>
       <c r="D550" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E550" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F550" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G550" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H550" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I550" t="str">
         <v/>
@@ -19666,28 +19666,28 @@
     </row>
     <row r="551">
       <c r="A551">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B551" t="str">
-        <v>Colloqui con le famiglie</v>
+        <v>Scrutini</v>
       </c>
       <c r="C551" t="str">
         <v>temporanea</v>
       </c>
       <c r="D551" t="str">
-        <v>Venerdì</v>
+        <v>Lunedì</v>
       </c>
       <c r="E551" t="str">
-        <v>15:00</v>
+        <v>09:30</v>
       </c>
       <c r="F551" t="str">
-        <v>19:00</v>
+        <v>17:30</v>
       </c>
       <c r="G551" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="H551" t="str">
-        <v>2027-04-16</v>
+        <v>2027-06-07</v>
       </c>
       <c r="I551" t="str">
         <v/>
@@ -19701,7 +19701,7 @@
     </row>
     <row r="552">
       <c r="A552">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B552" t="str">
         <v>Scrutini</v>
@@ -19736,7 +19736,7 @@
     </row>
     <row r="553">
       <c r="A553">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B553" t="str">
         <v>Scrutini</v>
@@ -19771,7 +19771,7 @@
     </row>
     <row r="554">
       <c r="A554">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B554" t="str">
         <v>Scrutini</v>
@@ -19806,7 +19806,7 @@
     </row>
     <row r="555">
       <c r="A555">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B555" t="str">
         <v>Scrutini</v>
@@ -19841,7 +19841,7 @@
     </row>
     <row r="556">
       <c r="A556">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B556" t="str">
         <v>Scrutini</v>
@@ -19876,7 +19876,7 @@
     </row>
     <row r="557">
       <c r="A557">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B557" t="str">
         <v>Scrutini</v>
@@ -19911,7 +19911,7 @@
     </row>
     <row r="558">
       <c r="A558">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B558" t="str">
         <v>Scrutini</v>
@@ -19946,7 +19946,7 @@
     </row>
     <row r="559">
       <c r="A559">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B559" t="str">
         <v>Scrutini</v>
@@ -19981,7 +19981,7 @@
     </row>
     <row r="560">
       <c r="A560">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B560" t="str">
         <v>Scrutini</v>
@@ -20016,7 +20016,7 @@
     </row>
     <row r="561">
       <c r="A561">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B561" t="str">
         <v>Scrutini</v>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="562">
       <c r="A562">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B562" t="str">
         <v>Scrutini</v>
@@ -20086,7 +20086,7 @@
     </row>
     <row r="563">
       <c r="A563">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B563" t="str">
         <v>Scrutini</v>
@@ -20121,7 +20121,7 @@
     </row>
     <row r="564">
       <c r="A564">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B564" t="str">
         <v>Scrutini</v>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="565">
       <c r="A565">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B565" t="str">
         <v>Scrutini</v>
@@ -20191,7 +20191,7 @@
     </row>
     <row r="566">
       <c r="A566">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B566" t="str">
         <v>Scrutini</v>
@@ -20226,7 +20226,7 @@
     </row>
     <row r="567">
       <c r="A567">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B567" t="str">
         <v>Scrutini</v>
@@ -20261,7 +20261,7 @@
     </row>
     <row r="568">
       <c r="A568">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B568" t="str">
         <v>Scrutini</v>
@@ -20296,7 +20296,7 @@
     </row>
     <row r="569">
       <c r="A569">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B569" t="str">
         <v>Scrutini</v>
@@ -20331,7 +20331,7 @@
     </row>
     <row r="570">
       <c r="A570">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B570" t="str">
         <v>Scrutini</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="571">
       <c r="A571">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B571" t="str">
         <v>Scrutini</v>
@@ -20375,7 +20375,7 @@
         <v>temporanea</v>
       </c>
       <c r="D571" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E571" t="str">
         <v>09:30</v>
@@ -20384,10 +20384,10 @@
         <v>17:30</v>
       </c>
       <c r="G571" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H571" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I571" t="str">
         <v/>
@@ -20401,7 +20401,7 @@
     </row>
     <row r="572">
       <c r="A572">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B572" t="str">
         <v>Scrutini</v>
@@ -20410,7 +20410,7 @@
         <v>temporanea</v>
       </c>
       <c r="D572" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E572" t="str">
         <v>09:30</v>
@@ -20419,10 +20419,10 @@
         <v>17:30</v>
       </c>
       <c r="G572" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H572" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I572" t="str">
         <v/>
@@ -20436,7 +20436,7 @@
     </row>
     <row r="573">
       <c r="A573">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B573" t="str">
         <v>Scrutini</v>
@@ -20445,7 +20445,7 @@
         <v>temporanea</v>
       </c>
       <c r="D573" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E573" t="str">
         <v>09:30</v>
@@ -20454,10 +20454,10 @@
         <v>17:30</v>
       </c>
       <c r="G573" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H573" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I573" t="str">
         <v/>
@@ -20471,7 +20471,7 @@
     </row>
     <row r="574">
       <c r="A574">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B574" t="str">
         <v>Scrutini</v>
@@ -20480,7 +20480,7 @@
         <v>temporanea</v>
       </c>
       <c r="D574" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E574" t="str">
         <v>09:30</v>
@@ -20489,10 +20489,10 @@
         <v>17:30</v>
       </c>
       <c r="G574" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H574" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I574" t="str">
         <v/>
@@ -20506,7 +20506,7 @@
     </row>
     <row r="575">
       <c r="A575">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B575" t="str">
         <v>Scrutini</v>
@@ -20515,7 +20515,7 @@
         <v>temporanea</v>
       </c>
       <c r="D575" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E575" t="str">
         <v>09:30</v>
@@ -20524,10 +20524,10 @@
         <v>17:30</v>
       </c>
       <c r="G575" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H575" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I575" t="str">
         <v/>
@@ -20541,7 +20541,7 @@
     </row>
     <row r="576">
       <c r="A576">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B576" t="str">
         <v>Scrutini</v>
@@ -20550,7 +20550,7 @@
         <v>temporanea</v>
       </c>
       <c r="D576" t="str">
-        <v>Lunedì</v>
+        <v>Martedì</v>
       </c>
       <c r="E576" t="str">
         <v>09:30</v>
@@ -20559,10 +20559,10 @@
         <v>17:30</v>
       </c>
       <c r="G576" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="H576" t="str">
-        <v>2027-06-07</v>
+        <v>2027-06-08</v>
       </c>
       <c r="I576" t="str">
         <v/>
@@ -20576,7 +20576,7 @@
     </row>
     <row r="577">
       <c r="A577">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B577" t="str">
         <v>Scrutini</v>
@@ -20611,7 +20611,7 @@
     </row>
     <row r="578">
       <c r="A578">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B578" t="str">
         <v>Scrutini</v>
@@ -20646,7 +20646,7 @@
     </row>
     <row r="579">
       <c r="A579">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B579" t="str">
         <v>Scrutini</v>
@@ -20681,7 +20681,7 @@
     </row>
     <row r="580">
       <c r="A580">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B580" t="str">
         <v>Scrutini</v>
@@ -20716,7 +20716,7 @@
     </row>
     <row r="581">
       <c r="A581">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B581" t="str">
         <v>Scrutini</v>
@@ -20751,7 +20751,7 @@
     </row>
     <row r="582">
       <c r="A582">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B582" t="str">
         <v>Scrutini</v>
@@ -20786,7 +20786,7 @@
     </row>
     <row r="583">
       <c r="A583">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B583" t="str">
         <v>Scrutini</v>
@@ -20821,7 +20821,7 @@
     </row>
     <row r="584">
       <c r="A584">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B584" t="str">
         <v>Scrutini</v>
@@ -20856,7 +20856,7 @@
     </row>
     <row r="585">
       <c r="A585">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B585" t="str">
         <v>Scrutini</v>
@@ -20891,7 +20891,7 @@
     </row>
     <row r="586">
       <c r="A586">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B586" t="str">
         <v>Scrutini</v>
@@ -20926,7 +20926,7 @@
     </row>
     <row r="587">
       <c r="A587">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B587" t="str">
         <v>Scrutini</v>
@@ -20961,7 +20961,7 @@
     </row>
     <row r="588">
       <c r="A588">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B588" t="str">
         <v>Scrutini</v>
@@ -20996,7 +20996,7 @@
     </row>
     <row r="589">
       <c r="A589">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B589" t="str">
         <v>Scrutini</v>
@@ -21031,7 +21031,7 @@
     </row>
     <row r="590">
       <c r="A590">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B590" t="str">
         <v>Scrutini</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="591">
       <c r="A591">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B591" t="str">
         <v>Scrutini</v>
@@ -21101,7 +21101,7 @@
     </row>
     <row r="592">
       <c r="A592">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B592" t="str">
         <v>Scrutini</v>
@@ -21136,7 +21136,7 @@
     </row>
     <row r="593">
       <c r="A593">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B593" t="str">
         <v>Scrutini</v>
@@ -21171,7 +21171,7 @@
     </row>
     <row r="594">
       <c r="A594">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B594" t="str">
         <v>Scrutini</v>
@@ -21206,7 +21206,7 @@
     </row>
     <row r="595">
       <c r="A595">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B595" t="str">
         <v>Scrutini</v>
@@ -21241,7 +21241,7 @@
     </row>
     <row r="596">
       <c r="A596">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B596" t="str">
         <v>Scrutini</v>
@@ -21250,7 +21250,7 @@
         <v>temporanea</v>
       </c>
       <c r="D596" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E596" t="str">
         <v>09:30</v>
@@ -21259,10 +21259,10 @@
         <v>17:30</v>
       </c>
       <c r="G596" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H596" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I596" t="str">
         <v/>
@@ -21276,7 +21276,7 @@
     </row>
     <row r="597">
       <c r="A597">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B597" t="str">
         <v>Scrutini</v>
@@ -21285,7 +21285,7 @@
         <v>temporanea</v>
       </c>
       <c r="D597" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E597" t="str">
         <v>09:30</v>
@@ -21294,10 +21294,10 @@
         <v>17:30</v>
       </c>
       <c r="G597" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H597" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I597" t="str">
         <v/>
@@ -21311,7 +21311,7 @@
     </row>
     <row r="598">
       <c r="A598">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B598" t="str">
         <v>Scrutini</v>
@@ -21320,7 +21320,7 @@
         <v>temporanea</v>
       </c>
       <c r="D598" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E598" t="str">
         <v>09:30</v>
@@ -21329,10 +21329,10 @@
         <v>17:30</v>
       </c>
       <c r="G598" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H598" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I598" t="str">
         <v/>
@@ -21346,7 +21346,7 @@
     </row>
     <row r="599">
       <c r="A599">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B599" t="str">
         <v>Scrutini</v>
@@ -21355,7 +21355,7 @@
         <v>temporanea</v>
       </c>
       <c r="D599" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E599" t="str">
         <v>09:30</v>
@@ -21364,10 +21364,10 @@
         <v>17:30</v>
       </c>
       <c r="G599" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H599" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I599" t="str">
         <v/>
@@ -21381,7 +21381,7 @@
     </row>
     <row r="600">
       <c r="A600">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B600" t="str">
         <v>Scrutini</v>
@@ -21390,7 +21390,7 @@
         <v>temporanea</v>
       </c>
       <c r="D600" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E600" t="str">
         <v>09:30</v>
@@ -21399,10 +21399,10 @@
         <v>17:30</v>
       </c>
       <c r="G600" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H600" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I600" t="str">
         <v/>
@@ -21416,7 +21416,7 @@
     </row>
     <row r="601">
       <c r="A601">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B601" t="str">
         <v>Scrutini</v>
@@ -21425,7 +21425,7 @@
         <v>temporanea</v>
       </c>
       <c r="D601" t="str">
-        <v>Martedì</v>
+        <v>Mercoledì</v>
       </c>
       <c r="E601" t="str">
         <v>09:30</v>
@@ -21434,10 +21434,10 @@
         <v>17:30</v>
       </c>
       <c r="G601" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="H601" t="str">
-        <v>2027-06-08</v>
+        <v>2027-06-09</v>
       </c>
       <c r="I601" t="str">
         <v/>
@@ -21451,7 +21451,7 @@
     </row>
     <row r="602">
       <c r="A602">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B602" t="str">
         <v>Scrutini</v>
@@ -21486,7 +21486,7 @@
     </row>
     <row r="603">
       <c r="A603">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B603" t="str">
         <v>Scrutini</v>
@@ -21521,7 +21521,7 @@
     </row>
     <row r="604">
       <c r="A604">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B604" t="str">
         <v>Scrutini</v>
@@ -21556,7 +21556,7 @@
     </row>
     <row r="605">
       <c r="A605">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B605" t="str">
         <v>Scrutini</v>
@@ -21591,7 +21591,7 @@
     </row>
     <row r="606">
       <c r="A606">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B606" t="str">
         <v>Scrutini</v>
@@ -21626,7 +21626,7 @@
     </row>
     <row r="607">
       <c r="A607">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B607" t="str">
         <v>Scrutini</v>
@@ -21661,7 +21661,7 @@
     </row>
     <row r="608">
       <c r="A608">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B608" t="str">
         <v>Scrutini</v>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="609">
       <c r="A609">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B609" t="str">
         <v>Scrutini</v>
@@ -21731,7 +21731,7 @@
     </row>
     <row r="610">
       <c r="A610">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B610" t="str">
         <v>Scrutini</v>
@@ -21766,7 +21766,7 @@
     </row>
     <row r="611">
       <c r="A611">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B611" t="str">
         <v>Scrutini</v>
@@ -21801,7 +21801,7 @@
     </row>
     <row r="612">
       <c r="A612">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B612" t="str">
         <v>Scrutini</v>
@@ -21836,7 +21836,7 @@
     </row>
     <row r="613">
       <c r="A613">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B613" t="str">
         <v>Scrutini</v>
@@ -21871,7 +21871,7 @@
     </row>
     <row r="614">
       <c r="A614">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B614" t="str">
         <v>Scrutini</v>
@@ -21906,7 +21906,7 @@
     </row>
     <row r="615">
       <c r="A615">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B615" t="str">
         <v>Scrutini</v>
@@ -21941,7 +21941,7 @@
     </row>
     <row r="616">
       <c r="A616">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B616" t="str">
         <v>Scrutini</v>
@@ -21976,7 +21976,7 @@
     </row>
     <row r="617">
       <c r="A617">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B617" t="str">
         <v>Scrutini</v>
@@ -22011,7 +22011,7 @@
     </row>
     <row r="618">
       <c r="A618">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B618" t="str">
         <v>Scrutini</v>
@@ -22046,7 +22046,7 @@
     </row>
     <row r="619">
       <c r="A619">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B619" t="str">
         <v>Scrutini</v>
@@ -22081,7 +22081,7 @@
     </row>
     <row r="620">
       <c r="A620">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B620" t="str">
         <v>Scrutini</v>
@@ -22114,219 +22114,9 @@
         <v/>
       </c>
     </row>
-    <row r="621">
-      <c r="A621">
-        <v>21</v>
-      </c>
-      <c r="B621" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C621" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D621" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E621" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F621" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G621" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H621" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I621" t="str">
-        <v/>
-      </c>
-      <c r="J621" t="str">
-        <v/>
-      </c>
-      <c r="K621" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622">
-        <v>23</v>
-      </c>
-      <c r="B622" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C622" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D622" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E622" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F622" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G622" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H622" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I622" t="str">
-        <v/>
-      </c>
-      <c r="J622" t="str">
-        <v/>
-      </c>
-      <c r="K622" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623">
-        <v>24</v>
-      </c>
-      <c r="B623" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C623" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D623" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E623" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F623" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G623" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H623" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I623" t="str">
-        <v/>
-      </c>
-      <c r="J623" t="str">
-        <v/>
-      </c>
-      <c r="K623" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624">
-        <v>25</v>
-      </c>
-      <c r="B624" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C624" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D624" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E624" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F624" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G624" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H624" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I624" t="str">
-        <v/>
-      </c>
-      <c r="J624" t="str">
-        <v/>
-      </c>
-      <c r="K624" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625">
-        <v>26</v>
-      </c>
-      <c r="B625" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C625" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D625" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E625" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F625" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G625" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H625" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I625" t="str">
-        <v/>
-      </c>
-      <c r="J625" t="str">
-        <v/>
-      </c>
-      <c r="K625" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626">
-        <v>27</v>
-      </c>
-      <c r="B626" t="str">
-        <v>Scrutini</v>
-      </c>
-      <c r="C626" t="str">
-        <v>temporanea</v>
-      </c>
-      <c r="D626" t="str">
-        <v>Mercoledì</v>
-      </c>
-      <c r="E626" t="str">
-        <v>09:30</v>
-      </c>
-      <c r="F626" t="str">
-        <v>17:30</v>
-      </c>
-      <c r="G626" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="H626" t="str">
-        <v>2027-06-09</v>
-      </c>
-      <c r="I626" t="str">
-        <v/>
-      </c>
-      <c r="J626" t="str">
-        <v/>
-      </c>
-      <c r="K626" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K626"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K620"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -906,7 +906,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>AIRC · 3B</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B16" t="str">
         <v>AIRC · 3A</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B17" t="str">
         <v>AIRC · 3C</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B18" t="str">
         <v>AIRC · 1A</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B19" t="str">
         <v>AIRC · 2A</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B20" t="str">
         <v>AIRC · 2D</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B21" t="str">
         <v>AIRC · 2B</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B22" t="str">
         <v>AIRC · 3D</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B23" t="str">
         <v>AIRC · 1D</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B24" t="str">
         <v>AIRC · 2C</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B25" t="str">
         <v>AIRC · 1B</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B127" t="str">
         <v>Italiano L2 · Gruppo C (1C, 1D)</v>
@@ -4861,7 +4861,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B128" t="str">
         <v>Italiano L2 · Gruppo F (3C)</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B129" t="str">
         <v>Italiano L2 · Gruppo A (1B, 1D, 2A, 2D)</v>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B130" t="str">
         <v>Italiano L2 · Gruppo A (1B, 1D, 2A, 2D)</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B131" t="str">
         <v>Italiano L2 · Gruppo D (2B, 2C, 2D)</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B132" t="str">
         <v>Italiano L2 · Gruppo B (1A, 1B)</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B133" t="str">
         <v>Italiano L2 · Gruppo E (3A, 3B)</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B134" t="str">
         <v>Italiano L2 · Gruppo C (1C, 1D)</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B135" t="str">
         <v>Italiano L2 · Gruppo B (1A, 1B)</v>
@@ -5141,7 +5141,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B136" t="str">
         <v>Italiano L2 · Gruppo F (3C)</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B137" t="str">
         <v>Italiano L2 · Gruppo E (3A, 3B)</v>
@@ -5211,7 +5211,7 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B138" t="str">
         <v>Italiano L2 · Gruppo D (2B, 2C, 2D)</v>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -1186,7 +1186,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B23" t="str">
         <v>AIRC · 1D</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B24" t="str">
         <v>AIRC · 2C</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B25" t="str">
         <v>AIRC · 1B</v>

--- a/data/modello-assegnazioni-compilato.xlsx
+++ b/data/modello-assegnazioni-compilato.xlsx
@@ -1157,7 +1157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -23665,7 +23665,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -23750,7 +23749,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
